--- a/docs/reports/CEG.xlsx
+++ b/docs/reports/CEG.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Assumptions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="WACC" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Model" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="DCF" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Sensitivity" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="DDM" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="IS (reported)" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="BS (reported)" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="CF (reported)" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Financial Model" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SWS Valuation" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WACC" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCF" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IS (reported)" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS (reported)" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CF (reported)" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -33,7 +34,7 @@
     <numFmt numFmtId="168" formatCode="0.0"/>
     <numFmt numFmtId="169" formatCode="0.000"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -95,6 +96,12 @@
       <color rgb="00008000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="000000FF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -137,7 +144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -147,36 +154,40 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="9" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -559,7 +570,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Utilities · Utility (dividend-discount led) · generated 2026-07-07 · data: yfinance</t>
+          <t>Utilities · Standard (2-Stage FCFE) · generated 2026-07-08 · data: yfinance</t>
         </is>
       </c>
     </row>
@@ -603,7 +614,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>115.1129656565166</v>
+        <v>141.4355573432792</v>
       </c>
     </row>
     <row r="8">
@@ -665,6 +676,1534 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F84"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CEG — BS (reported)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>As reported by yfinance (USDmm). Hardcoded actuals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Ordinary Shares Number</t>
+        </is>
+      </c>
+      <c r="C5" s="29" t="n">
+        <v>327</v>
+      </c>
+      <c r="D5" s="29" t="n">
+        <v>317</v>
+      </c>
+      <c r="E5" s="29" t="n">
+        <v>312.838</v>
+      </c>
+      <c r="F5" s="29" t="n">
+        <v>312.29008</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Share Issued</t>
+        </is>
+      </c>
+      <c r="C6" s="29" t="n">
+        <v>327</v>
+      </c>
+      <c r="D6" s="29" t="n">
+        <v>317</v>
+      </c>
+      <c r="E6" s="29" t="n">
+        <v>312.838</v>
+      </c>
+      <c r="F6" s="29" t="n">
+        <v>312.29008</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Net Debt</t>
+        </is>
+      </c>
+      <c r="C7" s="29" t="n">
+        <v>5346</v>
+      </c>
+      <c r="D7" s="29" t="n">
+        <v>8893</v>
+      </c>
+      <c r="E7" s="29" t="n">
+        <v>5390</v>
+      </c>
+      <c r="F7" s="29" t="n">
+        <v>5351</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Total Debt</t>
+        </is>
+      </c>
+      <c r="C8" s="29" t="n">
+        <v>5768</v>
+      </c>
+      <c r="D8" s="29" t="n">
+        <v>9261</v>
+      </c>
+      <c r="E8" s="29" t="n">
+        <v>8412</v>
+      </c>
+      <c r="F8" s="29" t="n">
+        <v>8992</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Tangible Book Value</t>
+        </is>
+      </c>
+      <c r="C9" s="29" t="n">
+        <v>10971</v>
+      </c>
+      <c r="D9" s="29" t="n">
+        <v>10500</v>
+      </c>
+      <c r="E9" s="29" t="n">
+        <v>12746</v>
+      </c>
+      <c r="F9" s="29" t="n">
+        <v>14097</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Invested Capital</t>
+        </is>
+      </c>
+      <c r="C10" s="29" t="n">
+        <v>16786</v>
+      </c>
+      <c r="D10" s="29" t="n">
+        <v>20186</v>
+      </c>
+      <c r="E10" s="29" t="n">
+        <v>21578</v>
+      </c>
+      <c r="F10" s="29" t="n">
+        <v>23509</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+      <c r="C11" s="29" t="n">
+        <v>1521</v>
+      </c>
+      <c r="D11" s="29" t="n">
+        <v>1980</v>
+      </c>
+      <c r="E11" s="29" t="n">
+        <v>3930</v>
+      </c>
+      <c r="F11" s="29" t="n">
+        <v>4175</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Net Tangible Assets</t>
+        </is>
+      </c>
+      <c r="C12" s="29" t="n">
+        <v>10971</v>
+      </c>
+      <c r="D12" s="29" t="n">
+        <v>10500</v>
+      </c>
+      <c r="E12" s="29" t="n">
+        <v>12746</v>
+      </c>
+      <c r="F12" s="29" t="n">
+        <v>14097</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Common Stock Equity</t>
+        </is>
+      </c>
+      <c r="C13" s="29" t="n">
+        <v>11018</v>
+      </c>
+      <c r="D13" s="29" t="n">
+        <v>10925</v>
+      </c>
+      <c r="E13" s="29" t="n">
+        <v>13166</v>
+      </c>
+      <c r="F13" s="29" t="n">
+        <v>14517</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Total Capitalization</t>
+        </is>
+      </c>
+      <c r="C14" s="29" t="n">
+        <v>15484</v>
+      </c>
+      <c r="D14" s="29" t="n">
+        <v>18421</v>
+      </c>
+      <c r="E14" s="29" t="n">
+        <v>20550</v>
+      </c>
+      <c r="F14" s="29" t="n">
+        <v>21767</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Total Equity Gross Minority Interest</t>
+        </is>
+      </c>
+      <c r="C15" s="29" t="n">
+        <v>11372</v>
+      </c>
+      <c r="D15" s="29" t="n">
+        <v>11286</v>
+      </c>
+      <c r="E15" s="29" t="n">
+        <v>13539</v>
+      </c>
+      <c r="F15" s="29" t="n">
+        <v>14853</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Minority Interest</t>
+        </is>
+      </c>
+      <c r="C16" s="29" t="n">
+        <v>354</v>
+      </c>
+      <c r="D16" s="29" t="n">
+        <v>361</v>
+      </c>
+      <c r="E16" s="29" t="n">
+        <v>373</v>
+      </c>
+      <c r="F16" s="29" t="n">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Stockholders Equity</t>
+        </is>
+      </c>
+      <c r="C17" s="29" t="n">
+        <v>11018</v>
+      </c>
+      <c r="D17" s="29" t="n">
+        <v>10925</v>
+      </c>
+      <c r="E17" s="29" t="n">
+        <v>13166</v>
+      </c>
+      <c r="F17" s="29" t="n">
+        <v>14517</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Other Equity Interest</t>
+        </is>
+      </c>
+      <c r="B18" s="29" t="n">
+        <v>11250</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Gains Losses Not Affecting Retained Earnings</t>
+        </is>
+      </c>
+      <c r="C19" s="29" t="n">
+        <v>-1760</v>
+      </c>
+      <c r="D19" s="29" t="n">
+        <v>-2191</v>
+      </c>
+      <c r="E19" s="29" t="n">
+        <v>-2302</v>
+      </c>
+      <c r="F19" s="29" t="n">
+        <v>-2425</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Other Equity Adjustments</t>
+        </is>
+      </c>
+      <c r="C20" s="29" t="n">
+        <v>-1760</v>
+      </c>
+      <c r="D20" s="29" t="n">
+        <v>-2191</v>
+      </c>
+      <c r="E20" s="29" t="n">
+        <v>-2302</v>
+      </c>
+      <c r="F20" s="29" t="n">
+        <v>-2425</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="C21" s="29" t="n">
+        <v>-496</v>
+      </c>
+      <c r="D21" s="29" t="n">
+        <v>761</v>
+      </c>
+      <c r="E21" s="29" t="n">
+        <v>4066</v>
+      </c>
+      <c r="F21" s="29" t="n">
+        <v>5899</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Capital Stock</t>
+        </is>
+      </c>
+      <c r="C22" s="29" t="n">
+        <v>13274</v>
+      </c>
+      <c r="D22" s="29" t="n">
+        <v>12355</v>
+      </c>
+      <c r="E22" s="29" t="n">
+        <v>11402</v>
+      </c>
+      <c r="F22" s="29" t="n">
+        <v>11043</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="C23" s="29" t="n">
+        <v>13274</v>
+      </c>
+      <c r="D23" s="29" t="n">
+        <v>12355</v>
+      </c>
+      <c r="E23" s="29" t="n">
+        <v>11402</v>
+      </c>
+      <c r="F23" s="29" t="n">
+        <v>11043</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Total Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="C24" s="29" t="n">
+        <v>35537</v>
+      </c>
+      <c r="D24" s="29" t="n">
+        <v>39472</v>
+      </c>
+      <c r="E24" s="29" t="n">
+        <v>39387</v>
+      </c>
+      <c r="F24" s="29" t="n">
+        <v>42396</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Total Non Current Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="C25" s="29" t="n">
+        <v>27698</v>
+      </c>
+      <c r="D25" s="29" t="n">
+        <v>33153</v>
+      </c>
+      <c r="E25" s="29" t="n">
+        <v>32541</v>
+      </c>
+      <c r="F25" s="29" t="n">
+        <v>34452</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Other Non Current Liabilities</t>
+        </is>
+      </c>
+      <c r="C26" s="29" t="n">
+        <v>2408</v>
+      </c>
+      <c r="D26" s="29" t="n">
+        <v>2421</v>
+      </c>
+      <c r="E26" s="29" t="n">
+        <v>2585</v>
+      </c>
+      <c r="F26" s="29" t="n">
+        <v>2740</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Derivative Product Liabilities</t>
+        </is>
+      </c>
+      <c r="C27" s="29" t="n">
+        <v>983</v>
+      </c>
+      <c r="D27" s="29" t="n">
+        <v>419</v>
+      </c>
+      <c r="E27" s="29" t="n">
+        <v>399</v>
+      </c>
+      <c r="F27" s="29" t="n">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Employee Benefits</t>
+        </is>
+      </c>
+      <c r="C28" s="29" t="n">
+        <v>1214</v>
+      </c>
+      <c r="D28" s="29" t="n">
+        <v>1802</v>
+      </c>
+      <c r="E28" s="29" t="n">
+        <v>1875</v>
+      </c>
+      <c r="F28" s="29" t="n">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Non Current Pension And Other Postretirement Benefit Plans</t>
+        </is>
+      </c>
+      <c r="C29" s="29" t="n">
+        <v>1214</v>
+      </c>
+      <c r="D29" s="29" t="n">
+        <v>1802</v>
+      </c>
+      <c r="E29" s="29" t="n">
+        <v>1875</v>
+      </c>
+      <c r="F29" s="29" t="n">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Dueto Related Parties Non Current</t>
+        </is>
+      </c>
+      <c r="B30" s="29" t="n">
+        <v>3357</v>
+      </c>
+      <c r="C30" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Tradeand Other Payables Non Current</t>
+        </is>
+      </c>
+      <c r="C31" s="29" t="n">
+        <v>2897</v>
+      </c>
+      <c r="D31" s="29" t="n">
+        <v>3688</v>
+      </c>
+      <c r="E31" s="29" t="n">
+        <v>4518</v>
+      </c>
+      <c r="F31" s="29" t="n">
+        <v>5334</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="C32" s="29" t="n">
+        <v>3031</v>
+      </c>
+      <c r="D32" s="29" t="n">
+        <v>3209</v>
+      </c>
+      <c r="E32" s="29" t="n">
+        <v>3331</v>
+      </c>
+      <c r="F32" s="29" t="n">
+        <v>3544</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Liabilities</t>
+        </is>
+      </c>
+      <c r="C33" s="29" t="n">
+        <v>3031</v>
+      </c>
+      <c r="D33" s="29" t="n">
+        <v>3209</v>
+      </c>
+      <c r="E33" s="29" t="n">
+        <v>3331</v>
+      </c>
+      <c r="F33" s="29" t="n">
+        <v>3544</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Long Term Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="C34" s="29" t="n">
+        <v>4466</v>
+      </c>
+      <c r="D34" s="29" t="n">
+        <v>7496</v>
+      </c>
+      <c r="E34" s="29" t="n">
+        <v>7384</v>
+      </c>
+      <c r="F34" s="29" t="n">
+        <v>7250</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Long Term Debt</t>
+        </is>
+      </c>
+      <c r="C35" s="29" t="n">
+        <v>4466</v>
+      </c>
+      <c r="D35" s="29" t="n">
+        <v>7496</v>
+      </c>
+      <c r="E35" s="29" t="n">
+        <v>7384</v>
+      </c>
+      <c r="F35" s="29" t="n">
+        <v>7250</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Long Term Provisions</t>
+        </is>
+      </c>
+      <c r="C36" s="29" t="n">
+        <v>12699</v>
+      </c>
+      <c r="D36" s="29" t="n">
+        <v>14118</v>
+      </c>
+      <c r="E36" s="29" t="n">
+        <v>12449</v>
+      </c>
+      <c r="F36" s="29" t="n">
+        <v>13193</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="C37" s="29" t="n">
+        <v>7839</v>
+      </c>
+      <c r="D37" s="29" t="n">
+        <v>6319</v>
+      </c>
+      <c r="E37" s="29" t="n">
+        <v>6846</v>
+      </c>
+      <c r="F37" s="29" t="n">
+        <v>7944</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Other Current Liabilities</t>
+        </is>
+      </c>
+      <c r="C38" s="29" t="n">
+        <v>2803</v>
+      </c>
+      <c r="D38" s="29" t="n">
+        <v>1942</v>
+      </c>
+      <c r="E38" s="29" t="n">
+        <v>1875</v>
+      </c>
+      <c r="F38" s="29" t="n">
+        <v>1908</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Current Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="C39" s="29" t="n">
+        <v>1302</v>
+      </c>
+      <c r="D39" s="29" t="n">
+        <v>1765</v>
+      </c>
+      <c r="E39" s="29" t="n">
+        <v>1028</v>
+      </c>
+      <c r="F39" s="29" t="n">
+        <v>1742</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Current Debt</t>
+        </is>
+      </c>
+      <c r="C40" s="29" t="n">
+        <v>1302</v>
+      </c>
+      <c r="D40" s="29" t="n">
+        <v>1765</v>
+      </c>
+      <c r="E40" s="29" t="n">
+        <v>1028</v>
+      </c>
+      <c r="F40" s="29" t="n">
+        <v>1742</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Other Current Borrowings</t>
+        </is>
+      </c>
+      <c r="C41" s="29" t="n">
+        <v>1302</v>
+      </c>
+      <c r="D41" s="29" t="n">
+        <v>1765</v>
+      </c>
+      <c r="E41" s="29" t="n">
+        <v>1028</v>
+      </c>
+      <c r="F41" s="29" t="n">
+        <v>1742</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Pensionand Other Post Retirement Benefit Plans Current</t>
+        </is>
+      </c>
+      <c r="E42" s="29" t="n">
+        <v>907</v>
+      </c>
+      <c r="F42" s="29" t="n">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Payables And Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="C43" s="29" t="n">
+        <v>3734</v>
+      </c>
+      <c r="D43" s="29" t="n">
+        <v>2612</v>
+      </c>
+      <c r="E43" s="29" t="n">
+        <v>3036</v>
+      </c>
+      <c r="F43" s="29" t="n">
+        <v>3374</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Current Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B44" s="29" t="n">
+        <v>737</v>
+      </c>
+      <c r="C44" s="29" t="n">
+        <v>906</v>
+      </c>
+      <c r="E44" s="29" t="n">
+        <v>435</v>
+      </c>
+      <c r="F44" s="29" t="n">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Interest Payable</t>
+        </is>
+      </c>
+      <c r="E45" s="29" t="n">
+        <v>435</v>
+      </c>
+      <c r="F45" s="29" t="n">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="B46" s="29" t="n">
+        <v>1888</v>
+      </c>
+      <c r="C46" s="29" t="n">
+        <v>2828</v>
+      </c>
+      <c r="E46" s="29" t="n">
+        <v>2601</v>
+      </c>
+      <c r="F46" s="29" t="n">
+        <v>3059</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Dueto Related Parties Current</t>
+        </is>
+      </c>
+      <c r="B47" s="29" t="n">
+        <v>131</v>
+      </c>
+      <c r="C47" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Total Tax Payable</t>
+        </is>
+      </c>
+      <c r="E48" s="29" t="n">
+        <v>232</v>
+      </c>
+      <c r="F48" s="29" t="n">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="B49" s="29" t="n">
+        <v>1757</v>
+      </c>
+      <c r="C49" s="29" t="n">
+        <v>2828</v>
+      </c>
+      <c r="E49" s="29" t="n">
+        <v>2369</v>
+      </c>
+      <c r="F49" s="29" t="n">
+        <v>2813</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="C50" s="29" t="n">
+        <v>46909</v>
+      </c>
+      <c r="D50" s="29" t="n">
+        <v>50758</v>
+      </c>
+      <c r="E50" s="29" t="n">
+        <v>52926</v>
+      </c>
+      <c r="F50" s="29" t="n">
+        <v>57249</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Total Non Current Assets</t>
+        </is>
+      </c>
+      <c r="C51" s="29" t="n">
+        <v>37549</v>
+      </c>
+      <c r="D51" s="29" t="n">
+        <v>42459</v>
+      </c>
+      <c r="E51" s="29" t="n">
+        <v>42150</v>
+      </c>
+      <c r="F51" s="29" t="n">
+        <v>45130</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Other Non Current Assets</t>
+        </is>
+      </c>
+      <c r="C52" s="29" t="n">
+        <v>16173</v>
+      </c>
+      <c r="D52" s="29" t="n">
+        <v>18308</v>
+      </c>
+      <c r="E52" s="29" t="n">
+        <v>19483</v>
+      </c>
+      <c r="F52" s="29" t="n">
+        <v>21479</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Defined Pension Benefit</t>
+        </is>
+      </c>
+      <c r="B53" s="29" t="n">
+        <v>1683</v>
+      </c>
+      <c r="C53" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Assets</t>
+        </is>
+      </c>
+      <c r="B54" s="29" t="n">
+        <v>32</v>
+      </c>
+      <c r="C54" s="29" t="n">
+        <v>44</v>
+      </c>
+      <c r="D54" s="29" t="n">
+        <v>52</v>
+      </c>
+      <c r="E54" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Assets</t>
+        </is>
+      </c>
+      <c r="B55" s="29" t="n">
+        <v>32</v>
+      </c>
+      <c r="C55" s="29" t="n">
+        <v>44</v>
+      </c>
+      <c r="D55" s="29" t="n">
+        <v>52</v>
+      </c>
+      <c r="E55" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Financial Assets</t>
+        </is>
+      </c>
+      <c r="C56" s="29" t="n">
+        <v>1261</v>
+      </c>
+      <c r="D56" s="29" t="n">
+        <v>995</v>
+      </c>
+      <c r="E56" s="29" t="n">
+        <v>372</v>
+      </c>
+      <c r="F56" s="29" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Investments And Advances</t>
+        </is>
+      </c>
+      <c r="C57" s="29" t="n">
+        <v>202</v>
+      </c>
+      <c r="D57" s="29" t="n">
+        <v>563</v>
+      </c>
+      <c r="E57" s="29" t="n">
+        <v>640</v>
+      </c>
+      <c r="F57" s="29" t="n">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Other Investments</t>
+        </is>
+      </c>
+      <c r="C58" s="29" t="n">
+        <v>68</v>
+      </c>
+      <c r="D58" s="29" t="n">
+        <v>82</v>
+      </c>
+      <c r="E58" s="29" t="n">
+        <v>100</v>
+      </c>
+      <c r="F58" s="29" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>Investmentin Financial Assets</t>
+        </is>
+      </c>
+      <c r="C59" s="29" t="n">
+        <v>52</v>
+      </c>
+      <c r="D59" s="29" t="n">
+        <v>474</v>
+      </c>
+      <c r="E59" s="29" t="n">
+        <v>538</v>
+      </c>
+      <c r="F59" s="29" t="n">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>Available For Sale Securities</t>
+        </is>
+      </c>
+      <c r="C60" s="29" t="n">
+        <v>52</v>
+      </c>
+      <c r="D60" s="29" t="n">
+        <v>474</v>
+      </c>
+      <c r="E60" s="29" t="n">
+        <v>538</v>
+      </c>
+      <c r="F60" s="29" t="n">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>Long Term Equity Investment</t>
+        </is>
+      </c>
+      <c r="C61" s="29" t="n">
+        <v>82</v>
+      </c>
+      <c r="D61" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="E61" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F61" s="29" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>Goodwill And Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="C62" s="29" t="n">
+        <v>47</v>
+      </c>
+      <c r="D62" s="29" t="n">
+        <v>425</v>
+      </c>
+      <c r="E62" s="29" t="n">
+        <v>420</v>
+      </c>
+      <c r="F62" s="29" t="n">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="C63" s="29" t="n">
+        <v>47</v>
+      </c>
+      <c r="D63" s="29" t="n">
+        <v>425</v>
+      </c>
+      <c r="E63" s="29" t="n">
+        <v>420</v>
+      </c>
+      <c r="F63" s="29" t="n">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>Net PPE</t>
+        </is>
+      </c>
+      <c r="C64" s="29" t="n">
+        <v>19822</v>
+      </c>
+      <c r="D64" s="29" t="n">
+        <v>22116</v>
+      </c>
+      <c r="E64" s="29" t="n">
+        <v>21235</v>
+      </c>
+      <c r="F64" s="29" t="n">
+        <v>22474</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation</t>
+        </is>
+      </c>
+      <c r="C65" s="29" t="n">
+        <v>-16726</v>
+      </c>
+      <c r="D65" s="29" t="n">
+        <v>-17423</v>
+      </c>
+      <c r="E65" s="29" t="n">
+        <v>-18088</v>
+      </c>
+      <c r="F65" s="29" t="n">
+        <v>-19072</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>Gross PPE</t>
+        </is>
+      </c>
+      <c r="C66" s="29" t="n">
+        <v>36548</v>
+      </c>
+      <c r="D66" s="29" t="n">
+        <v>39539</v>
+      </c>
+      <c r="E66" s="29" t="n">
+        <v>39323</v>
+      </c>
+      <c r="F66" s="29" t="n">
+        <v>41546</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>Construction In Progress</t>
+        </is>
+      </c>
+      <c r="C67" s="29" t="n">
+        <v>630</v>
+      </c>
+      <c r="D67" s="29" t="n">
+        <v>1133</v>
+      </c>
+      <c r="E67" s="29" t="n">
+        <v>1273</v>
+      </c>
+      <c r="F67" s="29" t="n">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>Other Properties</t>
+        </is>
+      </c>
+      <c r="B68" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="C68" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="D68" s="29" t="n">
+        <v>14</v>
+      </c>
+      <c r="E68" s="29" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="B69" s="29" t="n">
+        <v>35076</v>
+      </c>
+      <c r="C69" s="29" t="n">
+        <v>35910</v>
+      </c>
+      <c r="D69" s="29" t="n">
+        <v>38392</v>
+      </c>
+      <c r="E69" s="29" t="n">
+        <v>38035</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="C70" s="29" t="n">
+        <v>9360</v>
+      </c>
+      <c r="D70" s="29" t="n">
+        <v>8299</v>
+      </c>
+      <c r="E70" s="29" t="n">
+        <v>10776</v>
+      </c>
+      <c r="F70" s="29" t="n">
+        <v>12119</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>Other Current Assets</t>
+        </is>
+      </c>
+      <c r="C71" s="29" t="n">
+        <v>1643</v>
+      </c>
+      <c r="D71" s="29" t="n">
+        <v>2315</v>
+      </c>
+      <c r="E71" s="29" t="n">
+        <v>1486</v>
+      </c>
+      <c r="F71" s="29" t="n">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>Hedging Assets Current</t>
+        </is>
+      </c>
+      <c r="C72" s="29" t="n">
+        <v>2368</v>
+      </c>
+      <c r="D72" s="29" t="n">
+        <v>1179</v>
+      </c>
+      <c r="E72" s="29" t="n">
+        <v>843</v>
+      </c>
+      <c r="F72" s="29" t="n">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>Assets Held For Sale Current</t>
+        </is>
+      </c>
+      <c r="B73" s="29" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>Restricted Cash</t>
+        </is>
+      </c>
+      <c r="C74" s="29" t="n">
+        <v>106</v>
+      </c>
+      <c r="D74" s="29" t="n">
+        <v>86</v>
+      </c>
+      <c r="E74" s="29" t="n">
+        <v>107</v>
+      </c>
+      <c r="F74" s="29" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="C75" s="29" t="n">
+        <v>1505</v>
+      </c>
+      <c r="D75" s="29" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E75" s="29" t="n">
+        <v>1600</v>
+      </c>
+      <c r="F75" s="29" t="n">
+        <v>1736</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>Raw Materials</t>
+        </is>
+      </c>
+      <c r="B76" s="29" t="n">
+        <v>1288</v>
+      </c>
+      <c r="C76" s="29" t="n">
+        <v>1505</v>
+      </c>
+      <c r="D76" s="29" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E76" s="29" t="n">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="C77" s="29" t="n">
+        <v>3316</v>
+      </c>
+      <c r="D77" s="29" t="n">
+        <v>2851</v>
+      </c>
+      <c r="E77" s="29" t="n">
+        <v>3718</v>
+      </c>
+      <c r="F77" s="29" t="n">
+        <v>4266</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>Other Receivables</t>
+        </is>
+      </c>
+      <c r="C78" s="29" t="n">
+        <v>731</v>
+      </c>
+      <c r="D78" s="29" t="n">
+        <v>917</v>
+      </c>
+      <c r="E78" s="29" t="n">
+        <v>602</v>
+      </c>
+      <c r="F78" s="29" t="n">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>Duefrom Related Parties Current</t>
+        </is>
+      </c>
+      <c r="B79" s="29" t="n">
+        <v>160</v>
+      </c>
+      <c r="C79" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="C80" s="29" t="n">
+        <v>2585</v>
+      </c>
+      <c r="D80" s="29" t="n">
+        <v>1934</v>
+      </c>
+      <c r="E80" s="29" t="n">
+        <v>3116</v>
+      </c>
+      <c r="F80" s="29" t="n">
+        <v>3577</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>Allowance For Doubtful Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="C81" s="29" t="n">
+        <v>-46</v>
+      </c>
+      <c r="D81" s="29" t="n">
+        <v>-56</v>
+      </c>
+      <c r="E81" s="29" t="n">
+        <v>-190</v>
+      </c>
+      <c r="F81" s="29" t="n">
+        <v>-158</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>Gross Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="C82" s="29" t="n">
+        <v>2631</v>
+      </c>
+      <c r="D82" s="29" t="n">
+        <v>1990</v>
+      </c>
+      <c r="E82" s="29" t="n">
+        <v>3306</v>
+      </c>
+      <c r="F82" s="29" t="n">
+        <v>3735</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>Cash Cash Equivalents And Short Term Investments</t>
+        </is>
+      </c>
+      <c r="C83" s="29" t="n">
+        <v>422</v>
+      </c>
+      <c r="D83" s="29" t="n">
+        <v>368</v>
+      </c>
+      <c r="E83" s="29" t="n">
+        <v>3022</v>
+      </c>
+      <c r="F83" s="29" t="n">
+        <v>3641</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>Cash And Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="C84" s="29" t="n">
+        <v>422</v>
+      </c>
+      <c r="D84" s="29" t="n">
+        <v>368</v>
+      </c>
+      <c r="E84" s="29" t="n">
+        <v>3022</v>
+      </c>
+      <c r="F84" s="29" t="n">
+        <v>3641</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -696,32 +2235,32 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Line item</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>FY2021</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="E4" s="16" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="F4" s="16" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -733,16 +2272,16 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="C5" s="21" t="n">
+      <c r="C5" s="29" t="n">
         <v>-4042</v>
       </c>
-      <c r="D5" s="21" t="n">
+      <c r="D5" s="29" t="n">
         <v>-7723</v>
       </c>
-      <c r="E5" s="21" t="n">
+      <c r="E5" s="29" t="n">
         <v>-5029</v>
       </c>
-      <c r="F5" s="21" t="n">
+      <c r="F5" s="29" t="n">
         <v>1288</v>
       </c>
     </row>
@@ -752,16 +2291,16 @@
           <t>Repurchase Of Capital Stock</t>
         </is>
       </c>
-      <c r="C6" s="21" t="n">
+      <c r="C6" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="21" t="n">
+      <c r="D6" s="29" t="n">
         <v>-992</v>
       </c>
-      <c r="E6" s="21" t="n">
+      <c r="E6" s="29" t="n">
         <v>-999</v>
       </c>
-      <c r="F6" s="21" t="n">
+      <c r="F6" s="29" t="n">
         <v>-400</v>
       </c>
     </row>
@@ -771,16 +2310,16 @@
           <t>Repayment Of Debt</t>
         </is>
       </c>
-      <c r="C7" s="21" t="n">
+      <c r="C7" s="29" t="n">
         <v>-2600</v>
       </c>
-      <c r="D7" s="21" t="n">
+      <c r="D7" s="29" t="n">
         <v>-368</v>
       </c>
-      <c r="E7" s="21" t="n">
+      <c r="E7" s="29" t="n">
         <v>-1965</v>
       </c>
-      <c r="F7" s="21" t="n">
+      <c r="F7" s="29" t="n">
         <v>-1076</v>
       </c>
     </row>
@@ -790,16 +2329,16 @@
           <t>Issuance Of Debt</t>
         </is>
       </c>
-      <c r="C8" s="21" t="n">
+      <c r="C8" s="29" t="n">
         <v>271</v>
       </c>
-      <c r="D8" s="21" t="n">
+      <c r="D8" s="29" t="n">
         <v>3880</v>
       </c>
-      <c r="E8" s="21" t="n">
+      <c r="E8" s="29" t="n">
         <v>1120</v>
       </c>
-      <c r="F8" s="21" t="n">
+      <c r="F8" s="29" t="n">
         <v>1650</v>
       </c>
     </row>
@@ -809,16 +2348,16 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="C9" s="21" t="n">
+      <c r="C9" s="29" t="n">
         <v>-1689</v>
       </c>
-      <c r="D9" s="21" t="n">
+      <c r="D9" s="29" t="n">
         <v>-2422</v>
       </c>
-      <c r="E9" s="21" t="n">
+      <c r="E9" s="29" t="n">
         <v>-2565</v>
       </c>
-      <c r="F9" s="21" t="n">
+      <c r="F9" s="29" t="n">
         <v>-2949</v>
       </c>
     </row>
@@ -828,16 +2367,16 @@
           <t>Interest Paid Supplemental Data</t>
         </is>
       </c>
-      <c r="C10" s="21" t="n">
+      <c r="C10" s="29" t="n">
         <v>230</v>
       </c>
-      <c r="D10" s="21" t="n">
+      <c r="D10" s="29" t="n">
         <v>264</v>
       </c>
-      <c r="E10" s="21" t="n">
+      <c r="E10" s="29" t="n">
         <v>375</v>
       </c>
-      <c r="F10" s="21" t="n">
+      <c r="F10" s="29" t="n">
         <v>412</v>
       </c>
     </row>
@@ -847,16 +2386,16 @@
           <t>Income Tax Paid Supplemental Data</t>
         </is>
       </c>
-      <c r="C11" s="21" t="n">
+      <c r="C11" s="29" t="n">
         <v>287</v>
       </c>
-      <c r="D11" s="21" t="n">
+      <c r="D11" s="29" t="n">
         <v>466</v>
       </c>
-      <c r="E11" s="21" t="n">
+      <c r="E11" s="29" t="n">
         <v>436</v>
       </c>
-      <c r="F11" s="21" t="n">
+      <c r="F11" s="29" t="n">
         <v>446</v>
       </c>
     </row>
@@ -866,16 +2405,16 @@
           <t>End Cash Position</t>
         </is>
       </c>
-      <c r="C12" s="21" t="n">
+      <c r="C12" s="29" t="n">
         <v>528</v>
       </c>
-      <c r="D12" s="21" t="n">
+      <c r="D12" s="29" t="n">
         <v>454</v>
       </c>
-      <c r="E12" s="21" t="n">
+      <c r="E12" s="29" t="n">
         <v>3129</v>
       </c>
-      <c r="F12" s="21" t="n">
+      <c r="F12" s="29" t="n">
         <v>3748</v>
       </c>
     </row>
@@ -885,16 +2424,16 @@
           <t>Beginning Cash Position</t>
         </is>
       </c>
-      <c r="C13" s="21" t="n">
+      <c r="C13" s="29" t="n">
         <v>576</v>
       </c>
-      <c r="D13" s="21" t="n">
+      <c r="D13" s="29" t="n">
         <v>528</v>
       </c>
-      <c r="E13" s="21" t="n">
+      <c r="E13" s="29" t="n">
         <v>454</v>
       </c>
-      <c r="F13" s="21" t="n">
+      <c r="F13" s="29" t="n">
         <v>3129</v>
       </c>
     </row>
@@ -904,16 +2443,16 @@
           <t>Changes In Cash</t>
         </is>
       </c>
-      <c r="C14" s="21" t="n">
+      <c r="C14" s="29" t="n">
         <v>-48</v>
       </c>
-      <c r="D14" s="21" t="n">
+      <c r="D14" s="29" t="n">
         <v>-74</v>
       </c>
-      <c r="E14" s="21" t="n">
+      <c r="E14" s="29" t="n">
         <v>2675</v>
       </c>
-      <c r="F14" s="21" t="n">
+      <c r="F14" s="29" t="n">
         <v>619</v>
       </c>
     </row>
@@ -923,16 +2462,16 @@
           <t>Financing Cash Flow</t>
         </is>
       </c>
-      <c r="C15" s="21" t="n">
+      <c r="C15" s="29" t="n">
         <v>-799</v>
       </c>
-      <c r="D15" s="21" t="n">
+      <c r="D15" s="29" t="n">
         <v>2196</v>
       </c>
-      <c r="E15" s="21" t="n">
+      <c r="E15" s="29" t="n">
         <v>-2289</v>
       </c>
-      <c r="F15" s="21" t="n">
+      <c r="F15" s="29" t="n">
         <v>-420</v>
       </c>
     </row>
@@ -942,16 +2481,16 @@
           <t>Cash Flow From Continuing Financing Activities</t>
         </is>
       </c>
-      <c r="C16" s="21" t="n">
+      <c r="C16" s="29" t="n">
         <v>-799</v>
       </c>
-      <c r="D16" s="21" t="n">
+      <c r="D16" s="29" t="n">
         <v>2196</v>
       </c>
-      <c r="E16" s="21" t="n">
+      <c r="E16" s="29" t="n">
         <v>-2289</v>
       </c>
-      <c r="F16" s="21" t="n">
+      <c r="F16" s="29" t="n">
         <v>-420</v>
       </c>
     </row>
@@ -961,16 +2500,16 @@
           <t>Net Other Financing Charges</t>
         </is>
       </c>
-      <c r="C17" s="21" t="n">
+      <c r="C17" s="29" t="n">
         <v>1715</v>
       </c>
-      <c r="D17" s="21" t="n">
+      <c r="D17" s="29" t="n">
         <v>42</v>
       </c>
-      <c r="E17" s="21" t="n">
+      <c r="E17" s="29" t="n">
         <v>-1</v>
       </c>
-      <c r="F17" s="21" t="n">
+      <c r="F17" s="29" t="n">
         <v>-108</v>
       </c>
     </row>
@@ -980,16 +2519,16 @@
           <t>Cash Dividends Paid</t>
         </is>
       </c>
-      <c r="C18" s="21" t="n">
+      <c r="C18" s="29" t="n">
         <v>-185</v>
       </c>
-      <c r="D18" s="21" t="n">
+      <c r="D18" s="29" t="n">
         <v>-366</v>
       </c>
-      <c r="E18" s="21" t="n">
+      <c r="E18" s="29" t="n">
         <v>-444</v>
       </c>
-      <c r="F18" s="21" t="n">
+      <c r="F18" s="29" t="n">
         <v>-486</v>
       </c>
     </row>
@@ -999,16 +2538,16 @@
           <t>Common Stock Dividend Paid</t>
         </is>
       </c>
-      <c r="C19" s="21" t="n">
+      <c r="C19" s="29" t="n">
         <v>-185</v>
       </c>
-      <c r="D19" s="21" t="n">
+      <c r="D19" s="29" t="n">
         <v>-366</v>
       </c>
-      <c r="E19" s="21" t="n">
+      <c r="E19" s="29" t="n">
         <v>-444</v>
       </c>
-      <c r="F19" s="21" t="n">
+      <c r="F19" s="29" t="n">
         <v>-486</v>
       </c>
     </row>
@@ -1018,16 +2557,16 @@
           <t>Net Common Stock Issuance</t>
         </is>
       </c>
-      <c r="C20" s="21" t="n">
+      <c r="C20" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="D20" s="21" t="n">
+      <c r="D20" s="29" t="n">
         <v>-992</v>
       </c>
-      <c r="E20" s="21" t="n">
+      <c r="E20" s="29" t="n">
         <v>-999</v>
       </c>
-      <c r="F20" s="21" t="n">
+      <c r="F20" s="29" t="n">
         <v>-400</v>
       </c>
     </row>
@@ -1037,16 +2576,16 @@
           <t>Common Stock Payments</t>
         </is>
       </c>
-      <c r="C21" s="21" t="n">
+      <c r="C21" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="D21" s="21" t="n">
+      <c r="D21" s="29" t="n">
         <v>-992</v>
       </c>
-      <c r="E21" s="21" t="n">
+      <c r="E21" s="29" t="n">
         <v>-999</v>
       </c>
-      <c r="F21" s="21" t="n">
+      <c r="F21" s="29" t="n">
         <v>-400</v>
       </c>
     </row>
@@ -1056,16 +2595,16 @@
           <t>Net Issuance Payments Of Debt</t>
         </is>
       </c>
-      <c r="C22" s="21" t="n">
+      <c r="C22" s="29" t="n">
         <v>-2329</v>
       </c>
-      <c r="D22" s="21" t="n">
+      <c r="D22" s="29" t="n">
         <v>3512</v>
       </c>
-      <c r="E22" s="21" t="n">
+      <c r="E22" s="29" t="n">
         <v>-845</v>
       </c>
-      <c r="F22" s="21" t="n">
+      <c r="F22" s="29" t="n">
         <v>574</v>
       </c>
     </row>
@@ -1075,16 +2614,16 @@
           <t>Net Short Term Debt Issuance</t>
         </is>
       </c>
-      <c r="C23" s="21" t="n">
+      <c r="C23" s="29" t="n">
         <v>-923</v>
       </c>
-      <c r="D23" s="21" t="n">
+      <c r="D23" s="29" t="n">
         <v>485</v>
       </c>
-      <c r="E23" s="21" t="n">
+      <c r="E23" s="29" t="n">
         <v>-1644</v>
       </c>
-      <c r="F23" s="21" t="n">
+      <c r="F23" s="29" t="n">
         <v>1650</v>
       </c>
     </row>
@@ -1094,16 +2633,16 @@
           <t>Short Term Debt Payments</t>
         </is>
       </c>
-      <c r="C24" s="21" t="n">
+      <c r="C24" s="29" t="n">
         <v>-1180</v>
       </c>
-      <c r="D24" s="21" t="n">
+      <c r="D24" s="29" t="n">
         <v>-200</v>
       </c>
-      <c r="E24" s="21" t="n">
+      <c r="E24" s="29" t="n">
         <v>-1844</v>
       </c>
-      <c r="F24" s="21" t="n">
+      <c r="F24" s="29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1113,16 +2652,16 @@
           <t>Short Term Debt Issuance</t>
         </is>
       </c>
-      <c r="C25" s="21" t="n">
+      <c r="C25" s="29" t="n">
         <v>257</v>
       </c>
-      <c r="D25" s="21" t="n">
+      <c r="D25" s="29" t="n">
         <v>685</v>
       </c>
-      <c r="E25" s="21" t="n">
+      <c r="E25" s="29" t="n">
         <v>200</v>
       </c>
-      <c r="F25" s="21" t="n">
+      <c r="F25" s="29" t="n">
         <v>1650</v>
       </c>
     </row>
@@ -1132,16 +2671,16 @@
           <t>Net Long Term Debt Issuance</t>
         </is>
       </c>
-      <c r="C26" s="21" t="n">
+      <c r="C26" s="29" t="n">
         <v>-1406</v>
       </c>
-      <c r="D26" s="21" t="n">
+      <c r="D26" s="29" t="n">
         <v>3027</v>
       </c>
-      <c r="E26" s="21" t="n">
+      <c r="E26" s="29" t="n">
         <v>799</v>
       </c>
-      <c r="F26" s="21" t="n">
+      <c r="F26" s="29" t="n">
         <v>-1076</v>
       </c>
     </row>
@@ -1151,16 +2690,16 @@
           <t>Long Term Debt Payments</t>
         </is>
       </c>
-      <c r="C27" s="21" t="n">
+      <c r="C27" s="29" t="n">
         <v>-1420</v>
       </c>
-      <c r="D27" s="21" t="n">
+      <c r="D27" s="29" t="n">
         <v>-168</v>
       </c>
-      <c r="E27" s="21" t="n">
+      <c r="E27" s="29" t="n">
         <v>-121</v>
       </c>
-      <c r="F27" s="21" t="n">
+      <c r="F27" s="29" t="n">
         <v>-1076</v>
       </c>
     </row>
@@ -1170,16 +2709,16 @@
           <t>Long Term Debt Issuance</t>
         </is>
       </c>
-      <c r="C28" s="21" t="n">
+      <c r="C28" s="29" t="n">
         <v>14</v>
       </c>
-      <c r="D28" s="21" t="n">
+      <c r="D28" s="29" t="n">
         <v>3195</v>
       </c>
-      <c r="E28" s="21" t="n">
+      <c r="E28" s="29" t="n">
         <v>920</v>
       </c>
-      <c r="F28" s="21" t="n">
+      <c r="F28" s="29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1189,16 +2728,16 @@
           <t>Investing Cash Flow</t>
         </is>
       </c>
-      <c r="C29" s="21" t="n">
+      <c r="C29" s="29" t="n">
         <v>3104</v>
       </c>
-      <c r="D29" s="21" t="n">
+      <c r="D29" s="29" t="n">
         <v>3031</v>
       </c>
-      <c r="E29" s="21" t="n">
+      <c r="E29" s="29" t="n">
         <v>7428</v>
       </c>
-      <c r="F29" s="21" t="n">
+      <c r="F29" s="29" t="n">
         <v>-3198</v>
       </c>
     </row>
@@ -1208,16 +2747,16 @@
           <t>Cash Flow From Continuing Investing Activities</t>
         </is>
       </c>
-      <c r="C30" s="21" t="n">
+      <c r="C30" s="29" t="n">
         <v>3104</v>
       </c>
-      <c r="D30" s="21" t="n">
+      <c r="D30" s="29" t="n">
         <v>3031</v>
       </c>
-      <c r="E30" s="21" t="n">
+      <c r="E30" s="29" t="n">
         <v>7428</v>
       </c>
-      <c r="F30" s="21" t="n">
+      <c r="F30" s="29" t="n">
         <v>-3198</v>
       </c>
     </row>
@@ -1227,16 +2766,16 @@
           <t>Net Other Investing Changes</t>
         </is>
       </c>
-      <c r="C31" s="21" t="n">
+      <c r="C31" s="29" t="n">
         <v>5014</v>
       </c>
-      <c r="D31" s="21" t="n">
+      <c r="D31" s="29" t="n">
         <v>5681</v>
       </c>
-      <c r="E31" s="21" t="n">
+      <c r="E31" s="29" t="n">
         <v>10270</v>
       </c>
-      <c r="F31" s="21" t="n">
+      <c r="F31" s="29" t="n">
         <v>89</v>
       </c>
     </row>
@@ -1246,16 +2785,16 @@
           <t>Net Investment Purchase And Sale</t>
         </is>
       </c>
-      <c r="C32" s="21" t="n">
+      <c r="C32" s="29" t="n">
         <v>-221</v>
       </c>
-      <c r="D32" s="21" t="n">
+      <c r="D32" s="29" t="n">
         <v>-228</v>
       </c>
-      <c r="E32" s="21" t="n">
+      <c r="E32" s="29" t="n">
         <v>-277</v>
       </c>
-      <c r="F32" s="21" t="n">
+      <c r="F32" s="29" t="n">
         <v>-338</v>
       </c>
     </row>
@@ -1265,16 +2804,16 @@
           <t>Sale Of Investment</t>
         </is>
       </c>
-      <c r="C33" s="21" t="n">
+      <c r="C33" s="29" t="n">
         <v>4050</v>
       </c>
-      <c r="D33" s="21" t="n">
+      <c r="D33" s="29" t="n">
         <v>5822</v>
       </c>
-      <c r="E33" s="21" t="n">
+      <c r="E33" s="29" t="n">
         <v>6005</v>
       </c>
-      <c r="F33" s="21" t="n">
+      <c r="F33" s="29" t="n">
         <v>6946</v>
       </c>
     </row>
@@ -1284,16 +2823,16 @@
           <t>Purchase Of Investment</t>
         </is>
       </c>
-      <c r="C34" s="21" t="n">
+      <c r="C34" s="29" t="n">
         <v>-4271</v>
       </c>
-      <c r="D34" s="21" t="n">
+      <c r="D34" s="29" t="n">
         <v>-6050</v>
       </c>
-      <c r="E34" s="21" t="n">
+      <c r="E34" s="29" t="n">
         <v>-6282</v>
       </c>
-      <c r="F34" s="21" t="n">
+      <c r="F34" s="29" t="n">
         <v>-7284</v>
       </c>
     </row>
@@ -1303,16 +2842,16 @@
           <t>Capital Expenditure Reported</t>
         </is>
       </c>
-      <c r="C35" s="21" t="n">
+      <c r="C35" s="29" t="n">
         <v>-1689</v>
       </c>
-      <c r="D35" s="21" t="n">
+      <c r="D35" s="29" t="n">
         <v>-2422</v>
       </c>
-      <c r="E35" s="21" t="n">
+      <c r="E35" s="29" t="n">
         <v>-2565</v>
       </c>
-      <c r="F35" s="21" t="n">
+      <c r="F35" s="29" t="n">
         <v>-2949</v>
       </c>
     </row>
@@ -1322,16 +2861,16 @@
           <t>Operating Cash Flow</t>
         </is>
       </c>
-      <c r="C36" s="21" t="n">
+      <c r="C36" s="29" t="n">
         <v>-2353</v>
       </c>
-      <c r="D36" s="21" t="n">
+      <c r="D36" s="29" t="n">
         <v>-5301</v>
       </c>
-      <c r="E36" s="21" t="n">
+      <c r="E36" s="29" t="n">
         <v>-2464</v>
       </c>
-      <c r="F36" s="21" t="n">
+      <c r="F36" s="29" t="n">
         <v>4237</v>
       </c>
     </row>
@@ -1341,16 +2880,16 @@
           <t>Cash Flow From Continuing Operating Activities</t>
         </is>
       </c>
-      <c r="C37" s="21" t="n">
+      <c r="C37" s="29" t="n">
         <v>-2353</v>
       </c>
-      <c r="D37" s="21" t="n">
+      <c r="D37" s="29" t="n">
         <v>-5301</v>
       </c>
-      <c r="E37" s="21" t="n">
+      <c r="E37" s="29" t="n">
         <v>-2464</v>
       </c>
-      <c r="F37" s="21" t="n">
+      <c r="F37" s="29" t="n">
         <v>4237</v>
       </c>
     </row>
@@ -1360,16 +2899,16 @@
           <t>Change In Working Capital</t>
         </is>
       </c>
-      <c r="C38" s="21" t="n">
+      <c r="C38" s="29" t="n">
         <v>-5246</v>
       </c>
-      <c r="D38" s="21" t="n">
+      <c r="D38" s="29" t="n">
         <v>-8355</v>
       </c>
-      <c r="E38" s="21" t="n">
+      <c r="E38" s="29" t="n">
         <v>-9168</v>
       </c>
-      <c r="F38" s="21" t="n">
+      <c r="F38" s="29" t="n">
         <v>-7</v>
       </c>
     </row>
@@ -1379,16 +2918,16 @@
           <t>Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="C39" s="21" t="n">
+      <c r="C39" s="29" t="n">
         <v>-5292</v>
       </c>
-      <c r="D39" s="21" t="n">
+      <c r="D39" s="29" t="n">
         <v>-7481</v>
       </c>
-      <c r="E39" s="21" t="n">
+      <c r="E39" s="29" t="n">
         <v>-10878</v>
       </c>
-      <c r="F39" s="21" t="n">
+      <c r="F39" s="29" t="n">
         <v>174</v>
       </c>
     </row>
@@ -1398,16 +2937,16 @@
           <t>Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="C40" s="21" t="n">
+      <c r="C40" s="29" t="n">
         <v>1142</v>
       </c>
-      <c r="D40" s="21" t="n">
+      <c r="D40" s="29" t="n">
         <v>-1330</v>
       </c>
-      <c r="E40" s="21" t="n">
+      <c r="E40" s="29" t="n">
         <v>1121</v>
       </c>
-      <c r="F40" s="21" t="n">
+      <c r="F40" s="29" t="n">
         <v>316</v>
       </c>
     </row>
@@ -1417,7 +2956,7 @@
           <t>Change In Payable</t>
         </is>
       </c>
-      <c r="B41" s="21" t="n">
+      <c r="B41" s="29" t="n">
         <v>346</v>
       </c>
     </row>
@@ -1427,7 +2966,7 @@
           <t>Change In Account Payable</t>
         </is>
       </c>
-      <c r="B42" s="21" t="n">
+      <c r="B42" s="29" t="n">
         <v>346</v>
       </c>
     </row>
@@ -1437,16 +2976,16 @@
           <t>Change In Inventory</t>
         </is>
       </c>
-      <c r="C43" s="21" t="n">
+      <c r="C43" s="29" t="n">
         <v>-228</v>
       </c>
-      <c r="D43" s="21" t="n">
+      <c r="D43" s="29" t="n">
         <v>60</v>
       </c>
-      <c r="E43" s="21" t="n">
+      <c r="E43" s="29" t="n">
         <v>-99</v>
       </c>
-      <c r="F43" s="21" t="n">
+      <c r="F43" s="29" t="n">
         <v>-134</v>
       </c>
     </row>
@@ -1456,16 +2995,16 @@
           <t>Change In Receivables</t>
         </is>
       </c>
-      <c r="C44" s="21" t="n">
+      <c r="C44" s="29" t="n">
         <v>-868</v>
       </c>
-      <c r="D44" s="21" t="n">
+      <c r="D44" s="29" t="n">
         <v>396</v>
       </c>
-      <c r="E44" s="21" t="n">
+      <c r="E44" s="29" t="n">
         <v>688</v>
       </c>
-      <c r="F44" s="21" t="n">
+      <c r="F44" s="29" t="n">
         <v>-363</v>
       </c>
     </row>
@@ -1475,16 +3014,16 @@
           <t>Changes In Account Receivables</t>
         </is>
       </c>
-      <c r="C45" s="21" t="n">
+      <c r="C45" s="29" t="n">
         <v>-868</v>
       </c>
-      <c r="D45" s="21" t="n">
+      <c r="D45" s="29" t="n">
         <v>396</v>
       </c>
-      <c r="E45" s="21" t="n">
+      <c r="E45" s="29" t="n">
         <v>688</v>
       </c>
-      <c r="F45" s="21" t="n">
+      <c r="F45" s="29" t="n">
         <v>-363</v>
       </c>
     </row>
@@ -1494,16 +3033,16 @@
           <t>Other Non Cash Items</t>
         </is>
       </c>
-      <c r="C46" s="21" t="n">
+      <c r="C46" s="29" t="n">
         <v>61</v>
       </c>
-      <c r="D46" s="21" t="n">
+      <c r="D46" s="29" t="n">
         <v>-870</v>
       </c>
-      <c r="E46" s="21" t="n">
+      <c r="E46" s="29" t="n">
         <v>2356</v>
       </c>
-      <c r="F46" s="21" t="n">
+      <c r="F46" s="29" t="n">
         <v>-505</v>
       </c>
     </row>
@@ -1513,7 +3052,7 @@
           <t>Unrealized Gain Loss On Investment Securities</t>
         </is>
       </c>
-      <c r="B47" s="21" t="n">
+      <c r="B47" s="29" t="n">
         <v>160</v>
       </c>
     </row>
@@ -1523,10 +3062,10 @@
           <t>Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B48" s="21" t="n">
+      <c r="B48" s="29" t="n">
         <v>545</v>
       </c>
-      <c r="C48" s="21" t="n">
+      <c r="C48" s="29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1536,16 +3075,16 @@
           <t>Deferred Tax</t>
         </is>
       </c>
-      <c r="C49" s="21" t="n">
+      <c r="C49" s="29" t="n">
         <v>-643</v>
       </c>
-      <c r="D49" s="21" t="n">
+      <c r="D49" s="29" t="n">
         <v>251</v>
       </c>
-      <c r="E49" s="21" t="n">
+      <c r="E49" s="29" t="n">
         <v>222</v>
       </c>
-      <c r="F49" s="21" t="n">
+      <c r="F49" s="29" t="n">
         <v>273</v>
       </c>
     </row>
@@ -1555,16 +3094,16 @@
           <t>Deferred Income Tax</t>
         </is>
       </c>
-      <c r="C50" s="21" t="n">
+      <c r="C50" s="29" t="n">
         <v>-643</v>
       </c>
-      <c r="D50" s="21" t="n">
+      <c r="D50" s="29" t="n">
         <v>251</v>
       </c>
-      <c r="E50" s="21" t="n">
+      <c r="E50" s="29" t="n">
         <v>222</v>
       </c>
-      <c r="F50" s="21" t="n">
+      <c r="F50" s="29" t="n">
         <v>273</v>
       </c>
     </row>
@@ -1574,16 +3113,16 @@
           <t>Depreciation Amortization Depletion</t>
         </is>
       </c>
-      <c r="C51" s="21" t="n">
+      <c r="C51" s="29" t="n">
         <v>1849</v>
       </c>
-      <c r="D51" s="21" t="n">
+      <c r="D51" s="29" t="n">
         <v>1883</v>
       </c>
-      <c r="E51" s="21" t="n">
+      <c r="E51" s="29" t="n">
         <v>2007</v>
       </c>
-      <c r="F51" s="21" t="n">
+      <c r="F51" s="29" t="n">
         <v>1937</v>
       </c>
     </row>
@@ -1593,16 +3132,16 @@
           <t>Depreciation And Amortization</t>
         </is>
       </c>
-      <c r="C52" s="21" t="n">
+      <c r="C52" s="29" t="n">
         <v>1849</v>
       </c>
-      <c r="D52" s="21" t="n">
+      <c r="D52" s="29" t="n">
         <v>1883</v>
       </c>
-      <c r="E52" s="21" t="n">
+      <c r="E52" s="29" t="n">
         <v>2007</v>
       </c>
-      <c r="F52" s="21" t="n">
+      <c r="F52" s="29" t="n">
         <v>1937</v>
       </c>
     </row>
@@ -1612,16 +3151,16 @@
           <t>Amortization Cash Flow</t>
         </is>
       </c>
-      <c r="C53" s="21" t="n">
+      <c r="C53" s="29" t="n">
         <v>26</v>
       </c>
-      <c r="D53" s="21" t="n">
+      <c r="D53" s="29" t="n">
         <v>23</v>
       </c>
-      <c r="E53" s="21" t="n">
+      <c r="E53" s="29" t="n">
         <v>22</v>
       </c>
-      <c r="F53" s="21" t="n">
+      <c r="F53" s="29" t="n">
         <v>18</v>
       </c>
     </row>
@@ -1631,16 +3170,16 @@
           <t>Amortization Of Intangibles</t>
         </is>
       </c>
-      <c r="C54" s="21" t="n">
+      <c r="C54" s="29" t="n">
         <v>26</v>
       </c>
-      <c r="D54" s="21" t="n">
+      <c r="D54" s="29" t="n">
         <v>23</v>
       </c>
-      <c r="E54" s="21" t="n">
+      <c r="E54" s="29" t="n">
         <v>22</v>
       </c>
-      <c r="F54" s="21" t="n">
+      <c r="F54" s="29" t="n">
         <v>18</v>
       </c>
     </row>
@@ -1650,16 +3189,16 @@
           <t>Depreciation</t>
         </is>
       </c>
-      <c r="C55" s="21" t="n">
+      <c r="C55" s="29" t="n">
         <v>1823</v>
       </c>
-      <c r="D55" s="21" t="n">
+      <c r="D55" s="29" t="n">
         <v>1860</v>
       </c>
-      <c r="E55" s="21" t="n">
+      <c r="E55" s="29" t="n">
         <v>1985</v>
       </c>
-      <c r="F55" s="21" t="n">
+      <c r="F55" s="29" t="n">
         <v>1919</v>
       </c>
     </row>
@@ -1669,16 +3208,16 @@
           <t>Operating Gains Losses</t>
         </is>
       </c>
-      <c r="C56" s="21" t="n">
+      <c r="C56" s="29" t="n">
         <v>1793</v>
       </c>
-      <c r="D56" s="21" t="n">
+      <c r="D56" s="29" t="n">
         <v>213</v>
       </c>
-      <c r="E56" s="21" t="n">
+      <c r="E56" s="29" t="n">
         <v>-1619</v>
       </c>
-      <c r="F56" s="21" t="n">
+      <c r="F56" s="29" t="n">
         <v>216</v>
       </c>
     </row>
@@ -1688,16 +3227,16 @@
           <t>Gain Loss On Investment Securities</t>
         </is>
       </c>
-      <c r="C57" s="21" t="n">
+      <c r="C57" s="29" t="n">
         <v>1793</v>
       </c>
-      <c r="D57" s="21" t="n">
+      <c r="D57" s="29" t="n">
         <v>213</v>
       </c>
-      <c r="E57" s="21" t="n">
+      <c r="E57" s="29" t="n">
         <v>-1619</v>
       </c>
-      <c r="F57" s="21" t="n">
+      <c r="F57" s="29" t="n">
         <v>216</v>
       </c>
     </row>
@@ -1707,16 +3246,16 @@
           <t>Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="C58" s="21" t="n">
+      <c r="C58" s="29" t="n">
         <v>-167</v>
       </c>
-      <c r="D58" s="21" t="n">
+      <c r="D58" s="29" t="n">
         <v>1577</v>
       </c>
-      <c r="E58" s="21" t="n">
+      <c r="E58" s="29" t="n">
         <v>3738</v>
       </c>
-      <c r="F58" s="21" t="n">
+      <c r="F58" s="29" t="n">
         <v>2323</v>
       </c>
     </row>
@@ -1731,7 +3270,879 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:K15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CEG — projected P&amp;L &amp; levered FCF (analyst-driven)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Blue = analyst estimates; black = live formulas. The Levered FCF row is the exact cash flow discounted on the 'SWS Valuation' sheet — P&amp;L, cash flow and fair value are one reconciled chain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>FY2026E</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>FY2027E</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>FY2028E</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>FY2029E</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>FY2030E</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>FY2031E</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>FY2032E</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>FY2033E</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>FY2034E</t>
+        </is>
+      </c>
+      <c r="K4" s="10" t="inlineStr">
+        <is>
+          <t>FY2035E</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Revenue (mn)</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="n">
+        <v>35617.88948</v>
+      </c>
+      <c r="C5" s="13" t="n">
+        <v>36686.4261644</v>
+      </c>
+      <c r="D5" s="13" t="n">
+        <v>37787.018949332</v>
+      </c>
+      <c r="E5" s="13" t="n">
+        <v>38920.62951781196</v>
+      </c>
+      <c r="F5" s="13" t="n">
+        <v>40088.24840334632</v>
+      </c>
+      <c r="G5" s="13" t="n">
+        <v>41290.89585544671</v>
+      </c>
+      <c r="H5" s="13" t="n">
+        <v>42529.62273111011</v>
+      </c>
+      <c r="I5" s="13" t="n">
+        <v>43805.51141304341</v>
+      </c>
+      <c r="J5" s="13" t="n">
+        <v>45119.67675543472</v>
+      </c>
+      <c r="K5" s="13" t="n">
+        <v>46473.26705809776</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Revenue growth</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C6" s="14">
+        <f>C5/B5-1</f>
+        <v/>
+      </c>
+      <c r="D6" s="14">
+        <f>D5/C5-1</f>
+        <v/>
+      </c>
+      <c r="E6" s="14">
+        <f>E5/D5-1</f>
+        <v/>
+      </c>
+      <c r="F6" s="14">
+        <f>F5/E5-1</f>
+        <v/>
+      </c>
+      <c r="G6" s="14">
+        <f>G5/F5-1</f>
+        <v/>
+      </c>
+      <c r="H6" s="14">
+        <f>H5/G5-1</f>
+        <v/>
+      </c>
+      <c r="I6" s="14">
+        <f>I5/H5-1</f>
+        <v/>
+      </c>
+      <c r="J6" s="14">
+        <f>J5/I5-1</f>
+        <v/>
+      </c>
+      <c r="K6" s="14">
+        <f>K5/J5-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>EBIT margin</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="n">
+        <v>0.1644146790428073</v>
+      </c>
+      <c r="C7" s="15" t="n">
+        <v>0.1644146790428073</v>
+      </c>
+      <c r="D7" s="15" t="n">
+        <v>0.1644146790428073</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>0.1644146790428073</v>
+      </c>
+      <c r="F7" s="15" t="n">
+        <v>0.1644146790428073</v>
+      </c>
+      <c r="G7" s="15" t="n">
+        <v>0.1644146790428073</v>
+      </c>
+      <c r="H7" s="15" t="n">
+        <v>0.1644146790428073</v>
+      </c>
+      <c r="I7" s="15" t="n">
+        <v>0.1644146790428073</v>
+      </c>
+      <c r="J7" s="15" t="n">
+        <v>0.1644146790428073</v>
+      </c>
+      <c r="K7" s="15" t="n">
+        <v>0.1644146790428073</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>EBIT (mn)</t>
+        </is>
+      </c>
+      <c r="B8" s="13">
+        <f>B5*B7</f>
+        <v/>
+      </c>
+      <c r="C8" s="13">
+        <f>C5*C7</f>
+        <v/>
+      </c>
+      <c r="D8" s="13">
+        <f>D5*D7</f>
+        <v/>
+      </c>
+      <c r="E8" s="13">
+        <f>E5*E7</f>
+        <v/>
+      </c>
+      <c r="F8" s="13">
+        <f>F5*F7</f>
+        <v/>
+      </c>
+      <c r="G8" s="13">
+        <f>G5*G7</f>
+        <v/>
+      </c>
+      <c r="H8" s="13">
+        <f>H5*H7</f>
+        <v/>
+      </c>
+      <c r="I8" s="13">
+        <f>I5*I7</f>
+        <v/>
+      </c>
+      <c r="J8" s="13">
+        <f>J5*J7</f>
+        <v/>
+      </c>
+      <c r="K8" s="13">
+        <f>K5*K7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Net income (mn)</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="n">
+        <v>4850.52740997151</v>
+      </c>
+      <c r="C9" s="13" t="n">
+        <v>3331.994762669628</v>
+      </c>
+      <c r="D9" s="13" t="n">
+        <v>3431.954605549717</v>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>3534.913243716208</v>
+      </c>
+      <c r="F9" s="13" t="n">
+        <v>3640.960641027694</v>
+      </c>
+      <c r="G9" s="13" t="n">
+        <v>3750.189460258525</v>
+      </c>
+      <c r="H9" s="13" t="n">
+        <v>3862.695144066281</v>
+      </c>
+      <c r="I9" s="13" t="n">
+        <v>3978.575998388269</v>
+      </c>
+      <c r="J9" s="13" t="n">
+        <v>4097.933278339917</v>
+      </c>
+      <c r="K9" s="13" t="n">
+        <v>4220.871276690114</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="B10" s="16">
+        <f>B9*1000000/357102017.0</f>
+        <v/>
+      </c>
+      <c r="C10" s="16">
+        <f>C9*1000000/357102017.0</f>
+        <v/>
+      </c>
+      <c r="D10" s="16">
+        <f>D9*1000000/357102017.0</f>
+        <v/>
+      </c>
+      <c r="E10" s="16">
+        <f>E9*1000000/357102017.0</f>
+        <v/>
+      </c>
+      <c r="F10" s="16">
+        <f>F9*1000000/357102017.0</f>
+        <v/>
+      </c>
+      <c r="G10" s="16">
+        <f>G9*1000000/357102017.0</f>
+        <v/>
+      </c>
+      <c r="H10" s="16">
+        <f>H9*1000000/357102017.0</f>
+        <v/>
+      </c>
+      <c r="I10" s="16">
+        <f>I9*1000000/357102017.0</f>
+        <v/>
+      </c>
+      <c r="J10" s="16">
+        <f>J9*1000000/357102017.0</f>
+        <v/>
+      </c>
+      <c r="K10" s="16">
+        <f>K9*1000000/357102017.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>Levered FCF (mn)</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="n">
+        <v>1493.3072</v>
+      </c>
+      <c r="C12" s="17" t="n">
+        <v>1710.699543715556</v>
+      </c>
+      <c r="D12" s="17" t="n">
+        <v>1936.093712486434</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>2164.423697645668</v>
+      </c>
+      <c r="F12" s="17" t="n">
+        <v>2389.764253722778</v>
+      </c>
+      <c r="G12" s="17" t="n">
+        <v>2605.533412897792</v>
+      </c>
+      <c r="H12" s="17" t="n">
+        <v>2804.76986787071</v>
+      </c>
+      <c r="I12" s="17" t="n">
+        <v>2980.473118037989</v>
+      </c>
+      <c r="J12" s="17" t="n">
+        <v>3125.986438934199</v>
+      </c>
+      <c r="K12" s="17" t="n">
+        <v>3235.395964296896</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>FCF margin</t>
+        </is>
+      </c>
+      <c r="B13" s="14">
+        <f>B12/B5</f>
+        <v/>
+      </c>
+      <c r="C13" s="14">
+        <f>C12/C5</f>
+        <v/>
+      </c>
+      <c r="D13" s="14">
+        <f>D12/D5</f>
+        <v/>
+      </c>
+      <c r="E13" s="14">
+        <f>E12/E5</f>
+        <v/>
+      </c>
+      <c r="F13" s="14">
+        <f>F12/F5</f>
+        <v/>
+      </c>
+      <c r="G13" s="14">
+        <f>G12/G5</f>
+        <v/>
+      </c>
+      <c r="H13" s="14">
+        <f>H12/H5</f>
+        <v/>
+      </c>
+      <c r="I13" s="14">
+        <f>I12/I5</f>
+        <v/>
+      </c>
+      <c r="J13" s="14">
+        <f>J12/J5</f>
+        <v/>
+      </c>
+      <c r="K13" s="14">
+        <f>K12/K5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>→ These Levered FCF figures feed the DCF on the 'SWS Valuation' sheet.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CEG — 2-Stage Free Cash Flow to Equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Simply Wall St methodology. Blue = analyst inputs you can change; black = live formulas. Discounted at the cost of equity. Every figure is traceable; change a blue cell and the model recalculates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Cost of equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Risk-free rate</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="n">
+        <v>0.036</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Equity risk premium</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="n">
+        <v>0.046</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Levered beta (clamped 0.8–2.0)</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Cost of equity = Rf + β·ERP</t>
+        </is>
+      </c>
+      <c r="B8" s="20">
+        <f>$B$5+$B$7*$B$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Perpetual growth (g)</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="n">
+        <v>0.025</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Shares outstanding (mn)</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="n">
+        <v>357.102017</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Stage 1 — 10-year cash-flow forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Cash flow (mn)</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>Discount factor</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>PV (mn)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="21" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B15" s="12" t="n">
+        <v>1493.3072</v>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Analyst</t>
+        </is>
+      </c>
+      <c r="D15" s="22">
+        <f>1/(1+$B$8)^1</f>
+        <v/>
+      </c>
+      <c r="E15" s="13">
+        <f>B15*D15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="21" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B16" s="12" t="n">
+        <v>1710.699543715556</v>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Analyst</t>
+        </is>
+      </c>
+      <c r="D16" s="22">
+        <f>1/(1+$B$8)^2</f>
+        <v/>
+      </c>
+      <c r="E16" s="13">
+        <f>B16*D16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="21" t="n">
+        <v>2028</v>
+      </c>
+      <c r="B17" s="12" t="n">
+        <v>1936.093712486434</v>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Analyst</t>
+        </is>
+      </c>
+      <c r="D17" s="22">
+        <f>1/(1+$B$8)^3</f>
+        <v/>
+      </c>
+      <c r="E17" s="13">
+        <f>B17*D17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="21" t="n">
+        <v>2029</v>
+      </c>
+      <c r="B18" s="12" t="n">
+        <v>2164.423697645668</v>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Analyst</t>
+        </is>
+      </c>
+      <c r="D18" s="22">
+        <f>1/(1+$B$8)^4</f>
+        <v/>
+      </c>
+      <c r="E18" s="13">
+        <f>B18*D18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="21" t="n">
+        <v>2030</v>
+      </c>
+      <c r="B19" s="12" t="n">
+        <v>2389.764253722778</v>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Analyst</t>
+        </is>
+      </c>
+      <c r="D19" s="22">
+        <f>1/(1+$B$8)^5</f>
+        <v/>
+      </c>
+      <c r="E19" s="13">
+        <f>B19*D19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="21" t="n">
+        <v>2031</v>
+      </c>
+      <c r="B20" s="12" t="n">
+        <v>2605.533412897792</v>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Analyst</t>
+        </is>
+      </c>
+      <c r="D20" s="22">
+        <f>1/(1+$B$8)^6</f>
+        <v/>
+      </c>
+      <c r="E20" s="13">
+        <f>B20*D20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="21" t="n">
+        <v>2032</v>
+      </c>
+      <c r="B21" s="12" t="n">
+        <v>2804.76986787071</v>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Analyst</t>
+        </is>
+      </c>
+      <c r="D21" s="22">
+        <f>1/(1+$B$8)^7</f>
+        <v/>
+      </c>
+      <c r="E21" s="13">
+        <f>B21*D21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="21" t="n">
+        <v>2033</v>
+      </c>
+      <c r="B22" s="12" t="n">
+        <v>2980.473118037989</v>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Analyst</t>
+        </is>
+      </c>
+      <c r="D22" s="22">
+        <f>1/(1+$B$8)^8</f>
+        <v/>
+      </c>
+      <c r="E22" s="13">
+        <f>B22*D22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="21" t="n">
+        <v>2034</v>
+      </c>
+      <c r="B23" s="12" t="n">
+        <v>3125.986438934199</v>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Analyst</t>
+        </is>
+      </c>
+      <c r="D23" s="22">
+        <f>1/(1+$B$8)^9</f>
+        <v/>
+      </c>
+      <c r="E23" s="13">
+        <f>B23*D23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="21" t="n">
+        <v>2035</v>
+      </c>
+      <c r="B24" s="12" t="n">
+        <v>3235.395964296896</v>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Analyst</t>
+        </is>
+      </c>
+      <c r="D24" s="22">
+        <f>1/(1+$B$8)^10</f>
+        <v/>
+      </c>
+      <c r="E24" s="13">
+        <f>B24*D24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>PV of next 10 years' cash flows</t>
+        </is>
+      </c>
+      <c r="B25" s="23">
+        <f>SUM(E15:E24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>Stage 2 — terminal value</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Terminal value = CFn·(1+g)/(Ke−g)</t>
+        </is>
+      </c>
+      <c r="B28" s="13">
+        <f>B24*(1+$B$10)/($B$8-$B$10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>PV of terminal value</t>
+        </is>
+      </c>
+      <c r="B29" s="13">
+        <f>$B$28/(1+$B$8)^10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>Total equity value</t>
+        </is>
+      </c>
+      <c r="B31" s="23">
+        <f>$B$25+$B$29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>Value per share</t>
+        </is>
+      </c>
+      <c r="B32" s="24">
+        <f>$B$31/$B$11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Current price</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n">
+        <v>242.1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Upside / (downside)</t>
+        </is>
+      </c>
+      <c r="B34" s="14">
+        <f>B32/$B$33-1</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1757,7 +4168,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Blue cells are inputs — change them and the whole model recalculates. Source: yfinance, retrieved 2026-07-07.</t>
+          <t>Blue cells are inputs — change them and the whole model recalculates. Source: yfinance, retrieved 2026-07-08.</t>
         </is>
       </c>
     </row>
@@ -1775,7 +4186,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>240.98</v>
+        <v>242.1</v>
       </c>
     </row>
     <row r="6">
@@ -1784,7 +4195,7 @@
           <t>Diluted shares (mn)</t>
         </is>
       </c>
-      <c r="B6" s="9" t="n">
+      <c r="B6" s="12" t="n">
         <v>357.102017</v>
       </c>
     </row>
@@ -1794,7 +4205,7 @@
           <t>Total debt (USDmm)</t>
         </is>
       </c>
-      <c r="B7" s="9" t="n">
+      <c r="B7" s="12" t="n">
         <v>8992</v>
       </c>
     </row>
@@ -1804,7 +4215,7 @@
           <t>Cash &amp; ST investments (USDmm)</t>
         </is>
       </c>
-      <c r="B8" s="9" t="n">
+      <c r="B8" s="12" t="n">
         <v>3641</v>
       </c>
     </row>
@@ -1814,7 +4225,7 @@
           <t>Minority interest (USDmm)</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n">
+      <c r="B9" s="12" t="n">
         <v>336</v>
       </c>
     </row>
@@ -1824,7 +4235,7 @@
           <t>Net debt (USDmm)</t>
         </is>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="13">
         <f>Assumptions!$B$7-Assumptions!$B$8</f>
         <v/>
       </c>
@@ -1842,7 +4253,7 @@
           <t>Risk-free rate (Rf)</t>
         </is>
       </c>
-      <c r="B13" s="11" t="n">
+      <c r="B13" s="25" t="n">
         <v>0.043</v>
       </c>
     </row>
@@ -1852,7 +4263,7 @@
           <t>Equity risk premium (ERP)</t>
         </is>
       </c>
-      <c r="B14" s="11" t="n">
+      <c r="B14" s="25" t="n">
         <v>0.046</v>
       </c>
     </row>
@@ -1862,7 +4273,7 @@
           <t>Country risk premium</t>
         </is>
       </c>
-      <c r="B15" s="12" t="n">
+      <c r="B15" s="18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1872,7 +4283,7 @@
           <t>Size premium</t>
         </is>
       </c>
-      <c r="B16" s="12" t="n">
+      <c r="B16" s="18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1882,7 +4293,7 @@
           <t>Beta (levered)</t>
         </is>
       </c>
-      <c r="B17" s="13" t="n">
+      <c r="B17" s="26" t="n">
         <v>1.12</v>
       </c>
     </row>
@@ -1892,7 +4303,7 @@
           <t>Pre-tax cost of debt</t>
         </is>
       </c>
-      <c r="B18" s="12" t="n">
+      <c r="B18" s="18" t="n">
         <v>0.051</v>
       </c>
     </row>
@@ -1902,7 +4313,7 @@
           <t>Tax rate</t>
         </is>
       </c>
-      <c r="B19" s="14" t="n">
+      <c r="B19" s="15" t="n">
         <v>0.286837674171915</v>
       </c>
     </row>
@@ -1919,7 +4330,7 @@
           <t>Terminal growth (g)</t>
         </is>
       </c>
-      <c r="B22" s="11" t="n">
+      <c r="B22" s="25" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -1931,44 +4342,34 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>Driver</t>
         </is>
       </c>
-      <c r="B25" s="16" t="inlineStr">
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t>FY2026E</t>
         </is>
       </c>
-      <c r="C25" s="16" t="inlineStr">
+      <c r="C25" s="10" t="inlineStr">
         <is>
           <t>FY2027E</t>
         </is>
       </c>
-      <c r="D25" s="16" t="inlineStr">
+      <c r="D25" s="10" t="inlineStr">
         <is>
           <t>FY2028E</t>
         </is>
       </c>
-      <c r="E25" s="16" t="inlineStr">
+      <c r="E25" s="10" t="inlineStr">
         <is>
           <t>FY2029E</t>
         </is>
       </c>
-      <c r="F25" s="16" t="inlineStr">
+      <c r="F25" s="10" t="inlineStr">
         <is>
           <t>FY2030E</t>
-        </is>
-      </c>
-      <c r="G25" s="16" t="inlineStr">
-        <is>
-          <t>FY2031E</t>
-        </is>
-      </c>
-      <c r="H25" s="16" t="inlineStr">
-        <is>
-          <t>FY2032E</t>
         </is>
       </c>
     </row>
@@ -1978,26 +4379,20 @@
           <t>Revenue growth</t>
         </is>
       </c>
-      <c r="B26" s="14" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="C26" s="14" t="n">
-        <v>0.2958333333333333</v>
-      </c>
-      <c r="D26" s="14" t="n">
-        <v>0.2416666666666666</v>
-      </c>
-      <c r="E26" s="14" t="n">
-        <v>0.1875</v>
-      </c>
-      <c r="F26" s="14" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="G26" s="14" t="n">
-        <v>0.07916666666666666</v>
-      </c>
-      <c r="H26" s="14" t="n">
-        <v>0.02500000000000002</v>
+      <c r="B26" s="15" t="n">
+        <v>0.01469039149633189</v>
+      </c>
+      <c r="C26" s="15" t="n">
+        <v>0.01594039149633189</v>
+      </c>
+      <c r="D26" s="15" t="n">
+        <v>0.01719039149633189</v>
+      </c>
+      <c r="E26" s="15" t="n">
+        <v>0.01844039149633189</v>
+      </c>
+      <c r="F26" s="15" t="n">
+        <v>0.01969039149633189</v>
       </c>
     </row>
     <row r="27">
@@ -2006,25 +4401,19 @@
           <t>EBIT margin</t>
         </is>
       </c>
-      <c r="B27" s="14" t="n">
+      <c r="B27" s="15" t="n">
         <v>0.1644146790428073</v>
       </c>
-      <c r="C27" s="14" t="n">
-        <v>0.1609399913684161</v>
-      </c>
-      <c r="D27" s="14" t="n">
-        <v>0.1574653036940248</v>
-      </c>
-      <c r="E27" s="14" t="n">
+      <c r="C27" s="15" t="n">
+        <v>0.1592026475312204</v>
+      </c>
+      <c r="D27" s="15" t="n">
         <v>0.1539906160196335</v>
       </c>
-      <c r="F27" s="14" t="n">
-        <v>0.1505159283452422</v>
-      </c>
-      <c r="G27" s="14" t="n">
-        <v>0.1470412406708509</v>
-      </c>
-      <c r="H27" s="14" t="n">
+      <c r="E27" s="15" t="n">
+        <v>0.1487785845080466</v>
+      </c>
+      <c r="F27" s="15" t="n">
         <v>0.1435665529964597</v>
       </c>
     </row>
@@ -2034,25 +4423,19 @@
           <t>D&amp;A % of revenue</t>
         </is>
       </c>
-      <c r="B28" s="14" t="n">
+      <c r="B28" s="15" t="n">
         <v>0.07806074434667941</v>
       </c>
-      <c r="C28" s="14" t="n">
+      <c r="C28" s="15" t="n">
         <v>0.07806074434667941</v>
       </c>
-      <c r="D28" s="14" t="n">
+      <c r="D28" s="15" t="n">
         <v>0.07806074434667941</v>
       </c>
-      <c r="E28" s="14" t="n">
+      <c r="E28" s="15" t="n">
         <v>0.07806074434667941</v>
       </c>
-      <c r="F28" s="14" t="n">
-        <v>0.07806074434667941</v>
-      </c>
-      <c r="G28" s="14" t="n">
-        <v>0.07806074434667941</v>
-      </c>
-      <c r="H28" s="14" t="n">
+      <c r="F28" s="15" t="n">
         <v>0.07806074434667941</v>
       </c>
     </row>
@@ -2062,25 +4445,19 @@
           <t>Capex % of revenue</t>
         </is>
       </c>
-      <c r="B29" s="14" t="n">
+      <c r="B29" s="15" t="n">
         <v>0.09765960882899036</v>
       </c>
-      <c r="C29" s="14" t="n">
+      <c r="C29" s="15" t="n">
         <v>0.09765960882899036</v>
       </c>
-      <c r="D29" s="14" t="n">
+      <c r="D29" s="15" t="n">
         <v>0.09765960882899036</v>
       </c>
-      <c r="E29" s="14" t="n">
+      <c r="E29" s="15" t="n">
         <v>0.09765960882899036</v>
       </c>
-      <c r="F29" s="14" t="n">
-        <v>0.09765960882899036</v>
-      </c>
-      <c r="G29" s="14" t="n">
-        <v>0.09765960882899036</v>
-      </c>
-      <c r="H29" s="14" t="n">
+      <c r="F29" s="15" t="n">
         <v>0.09765960882899036</v>
       </c>
     </row>
@@ -2090,7 +4467,7 @@
           <t>ΔNWC % of Δrevenue</t>
         </is>
       </c>
-      <c r="B30" s="14" t="n">
+      <c r="B30" s="15" t="n">
         <v>0.00356234096692112</v>
       </c>
     </row>
@@ -2099,7 +4476,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2154,7 +4531,7 @@
           <t>Market value of equity (mm)</t>
         </is>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="27">
         <f>Assumptions!$B$5*Assumptions!$B$6</f>
         <v/>
       </c>
@@ -2165,7 +4542,7 @@
           <t>Debt (book, mm)</t>
         </is>
       </c>
-      <c r="B7" s="17">
+      <c r="B7" s="27">
         <f>Assumptions!$B$7</f>
         <v/>
       </c>
@@ -2176,7 +4553,7 @@
           <t>Weight of equity</t>
         </is>
       </c>
-      <c r="B8" s="18">
+      <c r="B8" s="14">
         <f>WACC!$B$6/(WACC!$B$6+WACC!$B$7)</f>
         <v/>
       </c>
@@ -2187,18 +4564,18 @@
           <t>Weight of debt</t>
         </is>
       </c>
-      <c r="B9" s="18">
+      <c r="B9" s="14">
         <f>1-WACC!$B$8</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>WACC</t>
         </is>
       </c>
-      <c r="B10" s="20">
+      <c r="B10" s="28">
         <f>WACC!$B$8*WACC!$B$4+WACC!$B$9*WACC!$B$5</f>
         <v/>
       </c>
@@ -2208,13 +4585,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2227,8 +4604,6 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2246,64 +4621,54 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Line item</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>FY2022A</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>FY2023A</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>FY2024A</t>
         </is>
       </c>
-      <c r="E4" s="16" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>FY2025A</t>
         </is>
       </c>
-      <c r="F4" s="16" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>FY2026E</t>
         </is>
       </c>
-      <c r="G4" s="16" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>FY2027E</t>
         </is>
       </c>
-      <c r="H4" s="16" t="inlineStr">
+      <c r="H4" s="10" t="inlineStr">
         <is>
           <t>FY2028E</t>
         </is>
       </c>
-      <c r="I4" s="16" t="inlineStr">
+      <c r="I4" s="10" t="inlineStr">
         <is>
           <t>FY2029E</t>
         </is>
       </c>
-      <c r="J4" s="16" t="inlineStr">
+      <c r="J4" s="10" t="inlineStr">
         <is>
           <t>FY2030E</t>
-        </is>
-      </c>
-      <c r="K4" s="16" t="inlineStr">
-        <is>
-          <t>FY2031E</t>
-        </is>
-      </c>
-      <c r="L4" s="16" t="inlineStr">
-        <is>
-          <t>FY2032E</t>
         </is>
       </c>
     </row>
@@ -2313,44 +4678,36 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B5" s="21" t="n">
+      <c r="B5" s="29" t="n">
         <v>24440</v>
       </c>
-      <c r="C5" s="21" t="n">
+      <c r="C5" s="29" t="n">
         <v>24918</v>
       </c>
-      <c r="D5" s="21" t="n">
+      <c r="D5" s="29" t="n">
         <v>23568</v>
       </c>
-      <c r="E5" s="21" t="n">
+      <c r="E5" s="29" t="n">
         <v>25533</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="13">
         <f>E5*(1+Assumptions!B$26)</f>
         <v/>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="13">
         <f>F5*(1+Assumptions!C$26)</f>
         <v/>
       </c>
-      <c r="H5" s="10">
+      <c r="H5" s="13">
         <f>G5*(1+Assumptions!D$26)</f>
         <v/>
       </c>
-      <c r="I5" s="10">
+      <c r="I5" s="13">
         <f>H5*(1+Assumptions!E$26)</f>
         <v/>
       </c>
-      <c r="J5" s="10">
+      <c r="J5" s="13">
         <f>I5*(1+Assumptions!F$26)</f>
-        <v/>
-      </c>
-      <c r="K5" s="10">
-        <f>J5*(1+Assumptions!G$26)</f>
-        <v/>
-      </c>
-      <c r="L5" s="10">
-        <f>K5*(1+Assumptions!H$26)</f>
         <v/>
       </c>
     </row>
@@ -2360,44 +4717,36 @@
           <t xml:space="preserve">  growth %</t>
         </is>
       </c>
-      <c r="C6" s="22">
+      <c r="C6" s="30">
         <f>C5/B5-1</f>
         <v/>
       </c>
-      <c r="D6" s="22">
+      <c r="D6" s="30">
         <f>D5/C5-1</f>
         <v/>
       </c>
-      <c r="E6" s="22">
+      <c r="E6" s="30">
         <f>E5/D5-1</f>
         <v/>
       </c>
-      <c r="F6" s="18">
+      <c r="F6" s="14">
         <f>F5/E5-1</f>
         <v/>
       </c>
-      <c r="G6" s="18">
+      <c r="G6" s="14">
         <f>G5/F5-1</f>
         <v/>
       </c>
-      <c r="H6" s="18">
+      <c r="H6" s="14">
         <f>H5/G5-1</f>
         <v/>
       </c>
-      <c r="I6" s="18">
+      <c r="I6" s="14">
         <f>I5/H5-1</f>
         <v/>
       </c>
-      <c r="J6" s="18">
+      <c r="J6" s="14">
         <f>J5/I5-1</f>
-        <v/>
-      </c>
-      <c r="K6" s="18">
-        <f>K5/J5-1</f>
-        <v/>
-      </c>
-      <c r="L6" s="18">
-        <f>L5/K5-1</f>
         <v/>
       </c>
     </row>
@@ -2407,44 +4756,36 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B7" s="21" t="n">
+      <c r="B7" s="29" t="n">
         <v>-408</v>
       </c>
-      <c r="C7" s="21" t="n">
+      <c r="C7" s="29" t="n">
         <v>2386</v>
       </c>
-      <c r="D7" s="21" t="n">
+      <c r="D7" s="29" t="n">
         <v>4848</v>
       </c>
-      <c r="E7" s="21" t="n">
+      <c r="E7" s="29" t="n">
         <v>4198</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="13">
         <f>F5*Assumptions!B$27</f>
         <v/>
       </c>
-      <c r="G7" s="10">
+      <c r="G7" s="13">
         <f>G5*Assumptions!C$27</f>
         <v/>
       </c>
-      <c r="H7" s="10">
+      <c r="H7" s="13">
         <f>H5*Assumptions!D$27</f>
         <v/>
       </c>
-      <c r="I7" s="10">
+      <c r="I7" s="13">
         <f>I5*Assumptions!E$27</f>
         <v/>
       </c>
-      <c r="J7" s="10">
+      <c r="J7" s="13">
         <f>J5*Assumptions!F$27</f>
-        <v/>
-      </c>
-      <c r="K7" s="10">
-        <f>K5*Assumptions!G$27</f>
-        <v/>
-      </c>
-      <c r="L7" s="10">
-        <f>L5*Assumptions!H$27</f>
         <v/>
       </c>
     </row>
@@ -2454,48 +4795,40 @@
           <t xml:space="preserve">  EBIT margin %</t>
         </is>
       </c>
-      <c r="B8" s="22">
+      <c r="B8" s="30">
         <f>B7/B5</f>
         <v/>
       </c>
-      <c r="C8" s="22">
+      <c r="C8" s="30">
         <f>C7/C5</f>
         <v/>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="30">
         <f>D7/D5</f>
         <v/>
       </c>
-      <c r="E8" s="22">
+      <c r="E8" s="30">
         <f>E7/E5</f>
         <v/>
       </c>
-      <c r="F8" s="18">
+      <c r="F8" s="14">
         <f>F7/F5</f>
         <v/>
       </c>
-      <c r="G8" s="18">
+      <c r="G8" s="14">
         <f>G7/G5</f>
         <v/>
       </c>
-      <c r="H8" s="18">
+      <c r="H8" s="14">
         <f>H7/H5</f>
         <v/>
       </c>
-      <c r="I8" s="18">
+      <c r="I8" s="14">
         <f>I7/I5</f>
         <v/>
       </c>
-      <c r="J8" s="18">
+      <c r="J8" s="14">
         <f>J7/J5</f>
-        <v/>
-      </c>
-      <c r="K8" s="18">
-        <f>K7/K5</f>
-        <v/>
-      </c>
-      <c r="L8" s="18">
-        <f>L7/L5</f>
         <v/>
       </c>
     </row>
@@ -2505,44 +4838,36 @@
           <t>D&amp;A</t>
         </is>
       </c>
-      <c r="B9" s="21" t="n">
+      <c r="B9" s="29" t="n">
         <v>1849</v>
       </c>
-      <c r="C9" s="21" t="n">
+      <c r="C9" s="29" t="n">
         <v>1883</v>
       </c>
-      <c r="D9" s="21" t="n">
+      <c r="D9" s="29" t="n">
         <v>2007</v>
       </c>
-      <c r="E9" s="21" t="n">
+      <c r="E9" s="29" t="n">
         <v>1937</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="13">
         <f>F5*Assumptions!B$28</f>
         <v/>
       </c>
-      <c r="G9" s="10">
+      <c r="G9" s="13">
         <f>G5*Assumptions!C$28</f>
         <v/>
       </c>
-      <c r="H9" s="10">
+      <c r="H9" s="13">
         <f>H5*Assumptions!D$28</f>
         <v/>
       </c>
-      <c r="I9" s="10">
+      <c r="I9" s="13">
         <f>I5*Assumptions!E$28</f>
         <v/>
       </c>
-      <c r="J9" s="10">
+      <c r="J9" s="13">
         <f>J5*Assumptions!F$28</f>
-        <v/>
-      </c>
-      <c r="K9" s="10">
-        <f>K5*Assumptions!G$28</f>
-        <v/>
-      </c>
-      <c r="L9" s="10">
-        <f>L5*Assumptions!H$28</f>
         <v/>
       </c>
     </row>
@@ -2552,48 +4877,40 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B10" s="23">
+      <c r="B10" s="31">
         <f>B7+B9</f>
         <v/>
       </c>
-      <c r="C10" s="23">
+      <c r="C10" s="31">
         <f>C7+C9</f>
         <v/>
       </c>
-      <c r="D10" s="23">
+      <c r="D10" s="31">
         <f>D7+D9</f>
         <v/>
       </c>
-      <c r="E10" s="23">
+      <c r="E10" s="31">
         <f>E7+E9</f>
         <v/>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="13">
         <f>F7+F9</f>
         <v/>
       </c>
-      <c r="G10" s="10">
+      <c r="G10" s="13">
         <f>G7+G9</f>
         <v/>
       </c>
-      <c r="H10" s="10">
+      <c r="H10" s="13">
         <f>H7+H9</f>
         <v/>
       </c>
-      <c r="I10" s="10">
+      <c r="I10" s="13">
         <f>I7+I9</f>
         <v/>
       </c>
-      <c r="J10" s="10">
+      <c r="J10" s="13">
         <f>J7+J9</f>
-        <v/>
-      </c>
-      <c r="K10" s="10">
-        <f>K7+K9</f>
-        <v/>
-      </c>
-      <c r="L10" s="10">
-        <f>L7+L9</f>
         <v/>
       </c>
     </row>
@@ -2603,48 +4920,40 @@
           <t>NOPAT (EBIT×(1−t))</t>
         </is>
       </c>
-      <c r="B11" s="24">
+      <c r="B11" s="32">
         <f>B7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="32">
         <f>C7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="D11" s="24">
+      <c r="D11" s="32">
         <f>D7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="E11" s="24">
+      <c r="E11" s="32">
         <f>E7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="F11" s="17">
+      <c r="F11" s="27">
         <f>F7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="G11" s="17">
+      <c r="G11" s="27">
         <f>G7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="H11" s="17">
+      <c r="H11" s="27">
         <f>H7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="I11" s="17">
+      <c r="I11" s="27">
         <f>I7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="J11" s="17">
+      <c r="J11" s="27">
         <f>J7*(1-Assumptions!$B$19)</f>
-        <v/>
-      </c>
-      <c r="K11" s="17">
-        <f>K7*(1-Assumptions!$B$19)</f>
-        <v/>
-      </c>
-      <c r="L11" s="17">
-        <f>L7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
     </row>
@@ -2654,44 +4963,36 @@
           <t>Capex</t>
         </is>
       </c>
-      <c r="B12" s="21" t="n">
+      <c r="B12" s="29" t="n">
         <v>1689</v>
       </c>
-      <c r="C12" s="21" t="n">
+      <c r="C12" s="29" t="n">
         <v>2422</v>
       </c>
-      <c r="D12" s="21" t="n">
+      <c r="D12" s="29" t="n">
         <v>2565</v>
       </c>
-      <c r="E12" s="21" t="n">
+      <c r="E12" s="29" t="n">
         <v>2949</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F12" s="13">
         <f>F5*Assumptions!B$29</f>
         <v/>
       </c>
-      <c r="G12" s="10">
+      <c r="G12" s="13">
         <f>G5*Assumptions!C$29</f>
         <v/>
       </c>
-      <c r="H12" s="10">
+      <c r="H12" s="13">
         <f>H5*Assumptions!D$29</f>
         <v/>
       </c>
-      <c r="I12" s="10">
+      <c r="I12" s="13">
         <f>I5*Assumptions!E$29</f>
         <v/>
       </c>
-      <c r="J12" s="10">
+      <c r="J12" s="13">
         <f>J5*Assumptions!F$29</f>
-        <v/>
-      </c>
-      <c r="K12" s="10">
-        <f>K5*Assumptions!G$29</f>
-        <v/>
-      </c>
-      <c r="L12" s="10">
-        <f>L5*Assumptions!H$29</f>
         <v/>
       </c>
     </row>
@@ -2701,95 +5002,79 @@
           <t>Δ Net working capital</t>
         </is>
       </c>
-      <c r="B13" s="21" t="n">
+      <c r="B13" s="29" t="n">
         <v>5246</v>
       </c>
-      <c r="C13" s="21" t="n">
+      <c r="C13" s="29" t="n">
         <v>8355</v>
       </c>
-      <c r="D13" s="21" t="n">
+      <c r="D13" s="29" t="n">
         <v>9168</v>
       </c>
-      <c r="E13" s="21" t="n">
+      <c r="E13" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="F13" s="10">
+      <c r="F13" s="13">
         <f>(F5-E5)*Assumptions!$B$30</f>
         <v/>
       </c>
-      <c r="G13" s="10">
+      <c r="G13" s="13">
         <f>(G5-F5)*Assumptions!$B$30</f>
         <v/>
       </c>
-      <c r="H13" s="10">
+      <c r="H13" s="13">
         <f>(H5-G5)*Assumptions!$B$30</f>
         <v/>
       </c>
-      <c r="I13" s="10">
+      <c r="I13" s="13">
         <f>(I5-H5)*Assumptions!$B$30</f>
         <v/>
       </c>
-      <c r="J13" s="10">
+      <c r="J13" s="13">
         <f>(J5-I5)*Assumptions!$B$30</f>
         <v/>
       </c>
-      <c r="K13" s="10">
-        <f>(K5-J5)*Assumptions!$B$30</f>
-        <v/>
-      </c>
-      <c r="L13" s="10">
-        <f>(L5-K5)*Assumptions!$B$30</f>
-        <v/>
-      </c>
     </row>
     <row r="14">
-      <c r="A14" s="19" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>FCFF</t>
         </is>
       </c>
-      <c r="B14" s="25">
+      <c r="B14" s="33">
         <f>B11+B9-B12-B13</f>
         <v/>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="33">
         <f>C11+C9-C12-C13</f>
         <v/>
       </c>
-      <c r="D14" s="25">
+      <c r="D14" s="33">
         <f>D11+D9-D12-D13</f>
         <v/>
       </c>
-      <c r="E14" s="25">
+      <c r="E14" s="33">
         <f>E11+E9-E12-E13</f>
         <v/>
       </c>
-      <c r="F14" s="26">
+      <c r="F14" s="23">
         <f>F11+F9-F12-F13</f>
         <v/>
       </c>
-      <c r="G14" s="26">
+      <c r="G14" s="23">
         <f>G11+G9-G12-G13</f>
         <v/>
       </c>
-      <c r="H14" s="26">
+      <c r="H14" s="23">
         <f>H11+H9-H12-H13</f>
         <v/>
       </c>
-      <c r="I14" s="26">
+      <c r="I14" s="23">
         <f>I11+I9-I12-I13</f>
         <v/>
       </c>
-      <c r="J14" s="26">
+      <c r="J14" s="23">
         <f>J11+J9-J12-J13</f>
-        <v/>
-      </c>
-      <c r="K14" s="26">
-        <f>K11+K9-K12-K13</f>
-        <v/>
-      </c>
-      <c r="L14" s="26">
-        <f>L11+L9-L12-L13</f>
         <v/>
       </c>
     </row>
@@ -2798,13 +5083,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -2814,8 +5099,6 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2833,44 +5116,34 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>FY2026E</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>FY2027E</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>FY2028E</t>
         </is>
       </c>
-      <c r="E4" s="16" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>FY2029E</t>
         </is>
       </c>
-      <c r="F4" s="16" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>FY2030E</t>
-        </is>
-      </c>
-      <c r="G4" s="16" t="inlineStr">
-        <is>
-          <t>FY2031E</t>
-        </is>
-      </c>
-      <c r="H4" s="16" t="inlineStr">
-        <is>
-          <t>FY2032E</t>
         </is>
       </c>
     </row>
@@ -2880,32 +5153,24 @@
           <t>FCFF (from Model)</t>
         </is>
       </c>
-      <c r="B5" s="17">
+      <c r="B5" s="27">
         <f>Model!F14</f>
         <v/>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="27">
         <f>Model!G14</f>
         <v/>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="27">
         <f>Model!H14</f>
         <v/>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="27">
         <f>Model!I14</f>
         <v/>
       </c>
-      <c r="F5" s="17">
+      <c r="F5" s="27">
         <f>Model!J14</f>
-        <v/>
-      </c>
-      <c r="G5" s="17">
-        <f>Model!K14</f>
-        <v/>
-      </c>
-      <c r="H5" s="17">
-        <f>Model!L14</f>
         <v/>
       </c>
     </row>
@@ -2915,26 +5180,20 @@
           <t>Period (mid-year, t−0.5)</t>
         </is>
       </c>
-      <c r="B6" s="27" t="n">
+      <c r="B6" s="34" t="n">
         <v>0.5</v>
       </c>
-      <c r="C6" s="27" t="n">
+      <c r="C6" s="34" t="n">
         <v>1.5</v>
       </c>
-      <c r="D6" s="27" t="n">
+      <c r="D6" s="34" t="n">
         <v>2.5</v>
       </c>
-      <c r="E6" s="27" t="n">
+      <c r="E6" s="34" t="n">
         <v>3.5</v>
       </c>
-      <c r="F6" s="27" t="n">
+      <c r="F6" s="34" t="n">
         <v>4.5</v>
-      </c>
-      <c r="G6" s="27" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H6" s="27" t="n">
-        <v>6.5</v>
       </c>
     </row>
     <row r="7">
@@ -2943,32 +5202,24 @@
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="B7" s="28">
+      <c r="B7" s="35">
         <f>1/(1+WACC!$B$10)^B6</f>
         <v/>
       </c>
-      <c r="C7" s="28">
+      <c r="C7" s="35">
         <f>1/(1+WACC!$B$10)^C6</f>
         <v/>
       </c>
-      <c r="D7" s="28">
+      <c r="D7" s="35">
         <f>1/(1+WACC!$B$10)^D6</f>
         <v/>
       </c>
-      <c r="E7" s="28">
+      <c r="E7" s="35">
         <f>1/(1+WACC!$B$10)^E6</f>
         <v/>
       </c>
-      <c r="F7" s="28">
+      <c r="F7" s="35">
         <f>1/(1+WACC!$B$10)^F6</f>
-        <v/>
-      </c>
-      <c r="G7" s="28">
-        <f>1/(1+WACC!$B$10)^G6</f>
-        <v/>
-      </c>
-      <c r="H7" s="28">
-        <f>1/(1+WACC!$B$10)^H6</f>
         <v/>
       </c>
     </row>
@@ -2978,32 +5229,24 @@
           <t>PV of FCFF</t>
         </is>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="13">
         <f>B5*B7</f>
         <v/>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="13">
         <f>C5*C7</f>
         <v/>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="13">
         <f>D5*D7</f>
         <v/>
       </c>
-      <c r="E8" s="10">
+      <c r="E8" s="13">
         <f>E5*E7</f>
         <v/>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="13">
         <f>F5*F7</f>
-        <v/>
-      </c>
-      <c r="G8" s="10">
-        <f>G5*G7</f>
-        <v/>
-      </c>
-      <c r="H8" s="10">
-        <f>H5*H7</f>
         <v/>
       </c>
     </row>
@@ -3013,8 +5256,8 @@
           <t>PV of explicit FCFF</t>
         </is>
       </c>
-      <c r="B10" s="10">
-        <f>SUM(B8:H8)</f>
+      <c r="B10" s="13">
+        <f>SUM(B8:F8)</f>
         <v/>
       </c>
     </row>
@@ -3024,8 +5267,8 @@
           <t>Terminal NOPAT (FYn)</t>
         </is>
       </c>
-      <c r="B11" s="17">
-        <f>Model!L11</f>
+      <c r="B11" s="27">
+        <f>Model!J11</f>
         <v/>
       </c>
     </row>
@@ -3035,7 +5278,7 @@
           <t>Invested capital (mm)</t>
         </is>
       </c>
-      <c r="B12" s="9" t="n">
+      <c r="B12" s="12" t="n">
         <v>19868</v>
       </c>
     </row>
@@ -3045,8 +5288,8 @@
           <t>Terminal invested capital (scaled w/ revenue)</t>
         </is>
       </c>
-      <c r="B13" s="17">
-        <f>$B$12*Model!L5/Model!E5</f>
+      <c r="B13" s="27">
+        <f>$B$12*Model!J5/Model!E5</f>
         <v/>
       </c>
     </row>
@@ -3056,7 +5299,7 @@
           <t>Terminal ROIC</t>
         </is>
       </c>
-      <c r="B14" s="18">
+      <c r="B14" s="14">
         <f>MAX($B$11/$B$13,WACC!$B$10)</f>
         <v/>
       </c>
@@ -3067,7 +5310,7 @@
           <t>Terminal reinvestment rate (g/ROIC)</t>
         </is>
       </c>
-      <c r="B15" s="29">
+      <c r="B15" s="36">
         <f>Assumptions!$B$22/$B$14</f>
         <v/>
       </c>
@@ -3078,7 +5321,7 @@
           <t>Terminal value (Gordon)</t>
         </is>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="13">
         <f>$B$11*(1+Assumptions!$B$22)*(1-$B$15)/(WACC!$B$10-Assumptions!$B$22)</f>
         <v/>
       </c>
@@ -3089,8 +5332,8 @@
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="B17" s="10">
-        <f>$B$16/(1+WACC!$B$10)^(7-0.5)</f>
+      <c r="B17" s="13">
+        <f>$B$16/(1+WACC!$B$10)^(5-0.5)</f>
         <v/>
       </c>
     </row>
@@ -3100,18 +5343,18 @@
           <t>TV as % of EV</t>
         </is>
       </c>
-      <c r="B18" s="18">
+      <c r="B18" s="14">
         <f>$B$17/($B$10+$B$17)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="19" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="B20" s="26">
+      <c r="B20" s="23">
         <f>$B$10+$B$17</f>
         <v/>
       </c>
@@ -3122,7 +5365,7 @@
           <t>(−) Net debt</t>
         </is>
       </c>
-      <c r="B21" s="17">
+      <c r="B21" s="27">
         <f>-Assumptions!$B$10</f>
         <v/>
       </c>
@@ -3133,40 +5376,40 @@
           <t>(−) Minority interest</t>
         </is>
       </c>
-      <c r="B22" s="17">
+      <c r="B22" s="27">
         <f>-Assumptions!$B$9</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="19" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>Equity value</t>
         </is>
       </c>
-      <c r="B23" s="26">
+      <c r="B23" s="23">
         <f>$B$20-Assumptions!$B$10-Assumptions!$B$9</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="19" t="inlineStr">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>Value per share</t>
         </is>
       </c>
-      <c r="B24" s="30">
+      <c r="B24" s="37">
         <f>$B$23/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="19" t="inlineStr">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>Upside vs price</t>
         </is>
       </c>
-      <c r="B25" s="31">
+      <c r="B25" s="38">
         <f>$B$24/Assumptions!$B$5-1</f>
         <v/>
       </c>
@@ -3176,7 +5419,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3208,149 +5451,149 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="19" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>WACC \ g</t>
         </is>
       </c>
-      <c r="B4" s="14" t="n">
+      <c r="B4" s="15" t="n">
         <v>0.015</v>
       </c>
-      <c r="C4" s="14" t="n">
+      <c r="C4" s="15" t="n">
         <v>0.02</v>
       </c>
-      <c r="D4" s="14" t="n">
+      <c r="D4" s="15" t="n">
         <v>0.025</v>
       </c>
-      <c r="E4" s="14" t="n">
+      <c r="E4" s="15" t="n">
         <v>0.03</v>
       </c>
-      <c r="F4" s="14" t="n">
+      <c r="F4" s="15" t="n">
         <v>0.035</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="n">
-        <v>0.07406040813524868</v>
-      </c>
-      <c r="B5" s="32">
-        <f>(SUMPRODUCT(DCF!$B$5:$H$5,1/(1+$A$5)^DCF!$B$6:$H$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$5-B$4)/(1+$A$5)^(7-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
-        <v/>
-      </c>
-      <c r="C5" s="32">
-        <f>(SUMPRODUCT(DCF!$B$5:$H$5,1/(1+$A$5)^DCF!$B$6:$H$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$5-C$4)/(1+$A$5)^(7-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
-        <v/>
-      </c>
-      <c r="D5" s="32">
-        <f>(SUMPRODUCT(DCF!$B$5:$H$5,1/(1+$A$5)^DCF!$B$6:$H$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$5-D$4)/(1+$A$5)^(7-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
-        <v/>
-      </c>
-      <c r="E5" s="32">
-        <f>(SUMPRODUCT(DCF!$B$5:$H$5,1/(1+$A$5)^DCF!$B$6:$H$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$5-E$4)/(1+$A$5)^(7-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
-        <v/>
-      </c>
-      <c r="F5" s="32">
-        <f>(SUMPRODUCT(DCF!$B$5:$H$5,1/(1+$A$5)^DCF!$B$6:$H$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$5-F$4)/(1+$A$5)^(7-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+      <c r="A5" s="18" t="n">
+        <v>0.07408347873328337</v>
+      </c>
+      <c r="B5" s="16">
+        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$5)^DCF!$B$6:$F$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$5-B$4)/(1+$A$5)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <v/>
+      </c>
+      <c r="C5" s="16">
+        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$5)^DCF!$B$6:$F$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$5-C$4)/(1+$A$5)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <v/>
+      </c>
+      <c r="D5" s="16">
+        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$5)^DCF!$B$6:$F$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$5-D$4)/(1+$A$5)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <v/>
+      </c>
+      <c r="E5" s="16">
+        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$5)^DCF!$B$6:$F$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$5-E$4)/(1+$A$5)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <v/>
+      </c>
+      <c r="F5" s="16">
+        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$5)^DCF!$B$6:$F$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$5-F$4)/(1+$A$5)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="n">
-        <v>0.08156040813524867</v>
-      </c>
-      <c r="B6" s="32">
-        <f>(SUMPRODUCT(DCF!$B$5:$H$5,1/(1+$A$6)^DCF!$B$6:$H$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$6-B$4)/(1+$A$6)^(7-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
-        <v/>
-      </c>
-      <c r="C6" s="32">
-        <f>(SUMPRODUCT(DCF!$B$5:$H$5,1/(1+$A$6)^DCF!$B$6:$H$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$6-C$4)/(1+$A$6)^(7-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
-        <v/>
-      </c>
-      <c r="D6" s="32">
-        <f>(SUMPRODUCT(DCF!$B$5:$H$5,1/(1+$A$6)^DCF!$B$6:$H$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$6-D$4)/(1+$A$6)^(7-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
-        <v/>
-      </c>
-      <c r="E6" s="32">
-        <f>(SUMPRODUCT(DCF!$B$5:$H$5,1/(1+$A$6)^DCF!$B$6:$H$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$6-E$4)/(1+$A$6)^(7-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
-        <v/>
-      </c>
-      <c r="F6" s="32">
-        <f>(SUMPRODUCT(DCF!$B$5:$H$5,1/(1+$A$6)^DCF!$B$6:$H$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$6-F$4)/(1+$A$6)^(7-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+      <c r="A6" s="18" t="n">
+        <v>0.08158347873328337</v>
+      </c>
+      <c r="B6" s="16">
+        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$6)^DCF!$B$6:$F$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$6-B$4)/(1+$A$6)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <v/>
+      </c>
+      <c r="C6" s="16">
+        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$6)^DCF!$B$6:$F$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$6-C$4)/(1+$A$6)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <v/>
+      </c>
+      <c r="D6" s="16">
+        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$6)^DCF!$B$6:$F$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$6-D$4)/(1+$A$6)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <v/>
+      </c>
+      <c r="E6" s="16">
+        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$6)^DCF!$B$6:$F$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$6-E$4)/(1+$A$6)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <v/>
+      </c>
+      <c r="F6" s="16">
+        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$6)^DCF!$B$6:$F$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$6-F$4)/(1+$A$6)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="n">
-        <v>0.08906040813524868</v>
-      </c>
-      <c r="B7" s="32">
-        <f>(SUMPRODUCT(DCF!$B$5:$H$5,1/(1+$A$7)^DCF!$B$6:$H$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$7-B$4)/(1+$A$7)^(7-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
-        <v/>
-      </c>
-      <c r="C7" s="32">
-        <f>(SUMPRODUCT(DCF!$B$5:$H$5,1/(1+$A$7)^DCF!$B$6:$H$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$7-C$4)/(1+$A$7)^(7-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
-        <v/>
-      </c>
-      <c r="D7" s="32">
-        <f>(SUMPRODUCT(DCF!$B$5:$H$5,1/(1+$A$7)^DCF!$B$6:$H$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$7-D$4)/(1+$A$7)^(7-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
-        <v/>
-      </c>
-      <c r="E7" s="32">
-        <f>(SUMPRODUCT(DCF!$B$5:$H$5,1/(1+$A$7)^DCF!$B$6:$H$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$7-E$4)/(1+$A$7)^(7-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
-        <v/>
-      </c>
-      <c r="F7" s="32">
-        <f>(SUMPRODUCT(DCF!$B$5:$H$5,1/(1+$A$7)^DCF!$B$6:$H$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$7-F$4)/(1+$A$7)^(7-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+      <c r="A7" s="18" t="n">
+        <v>0.08908347873328337</v>
+      </c>
+      <c r="B7" s="16">
+        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$7)^DCF!$B$6:$F$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$7-B$4)/(1+$A$7)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <v/>
+      </c>
+      <c r="C7" s="16">
+        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$7)^DCF!$B$6:$F$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$7-C$4)/(1+$A$7)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <v/>
+      </c>
+      <c r="D7" s="16">
+        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$7)^DCF!$B$6:$F$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$7-D$4)/(1+$A$7)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <v/>
+      </c>
+      <c r="E7" s="16">
+        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$7)^DCF!$B$6:$F$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$7-E$4)/(1+$A$7)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <v/>
+      </c>
+      <c r="F7" s="16">
+        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$7)^DCF!$B$6:$F$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$7-F$4)/(1+$A$7)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="n">
-        <v>0.09656040813524869</v>
-      </c>
-      <c r="B8" s="32">
-        <f>(SUMPRODUCT(DCF!$B$5:$H$5,1/(1+$A$8)^DCF!$B$6:$H$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$8-B$4)/(1+$A$8)^(7-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
-        <v/>
-      </c>
-      <c r="C8" s="32">
-        <f>(SUMPRODUCT(DCF!$B$5:$H$5,1/(1+$A$8)^DCF!$B$6:$H$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$8-C$4)/(1+$A$8)^(7-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
-        <v/>
-      </c>
-      <c r="D8" s="32">
-        <f>(SUMPRODUCT(DCF!$B$5:$H$5,1/(1+$A$8)^DCF!$B$6:$H$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$8-D$4)/(1+$A$8)^(7-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
-        <v/>
-      </c>
-      <c r="E8" s="32">
-        <f>(SUMPRODUCT(DCF!$B$5:$H$5,1/(1+$A$8)^DCF!$B$6:$H$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$8-E$4)/(1+$A$8)^(7-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
-        <v/>
-      </c>
-      <c r="F8" s="32">
-        <f>(SUMPRODUCT(DCF!$B$5:$H$5,1/(1+$A$8)^DCF!$B$6:$H$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$8-F$4)/(1+$A$8)^(7-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+      <c r="A8" s="18" t="n">
+        <v>0.09658347873328338</v>
+      </c>
+      <c r="B8" s="16">
+        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$8)^DCF!$B$6:$F$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$8-B$4)/(1+$A$8)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <v/>
+      </c>
+      <c r="C8" s="16">
+        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$8)^DCF!$B$6:$F$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$8-C$4)/(1+$A$8)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <v/>
+      </c>
+      <c r="D8" s="16">
+        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$8)^DCF!$B$6:$F$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$8-D$4)/(1+$A$8)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <v/>
+      </c>
+      <c r="E8" s="16">
+        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$8)^DCF!$B$6:$F$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$8-E$4)/(1+$A$8)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <v/>
+      </c>
+      <c r="F8" s="16">
+        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$8)^DCF!$B$6:$F$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$8-F$4)/(1+$A$8)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="n">
-        <v>0.1040604081352487</v>
-      </c>
-      <c r="B9" s="32">
-        <f>(SUMPRODUCT(DCF!$B$5:$H$5,1/(1+$A$9)^DCF!$B$6:$H$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$9-B$4)/(1+$A$9)^(7-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
-        <v/>
-      </c>
-      <c r="C9" s="32">
-        <f>(SUMPRODUCT(DCF!$B$5:$H$5,1/(1+$A$9)^DCF!$B$6:$H$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$9-C$4)/(1+$A$9)^(7-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
-        <v/>
-      </c>
-      <c r="D9" s="32">
-        <f>(SUMPRODUCT(DCF!$B$5:$H$5,1/(1+$A$9)^DCF!$B$6:$H$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$9-D$4)/(1+$A$9)^(7-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
-        <v/>
-      </c>
-      <c r="E9" s="32">
-        <f>(SUMPRODUCT(DCF!$B$5:$H$5,1/(1+$A$9)^DCF!$B$6:$H$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$9-E$4)/(1+$A$9)^(7-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
-        <v/>
-      </c>
-      <c r="F9" s="32">
-        <f>(SUMPRODUCT(DCF!$B$5:$H$5,1/(1+$A$9)^DCF!$B$6:$H$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$9-F$4)/(1+$A$9)^(7-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+      <c r="A9" s="18" t="n">
+        <v>0.1040834787332834</v>
+      </c>
+      <c r="B9" s="16">
+        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$9)^DCF!$B$6:$F$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$9-B$4)/(1+$A$9)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <v/>
+      </c>
+      <c r="C9" s="16">
+        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$9)^DCF!$B$6:$F$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$9-C$4)/(1+$A$9)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <v/>
+      </c>
+      <c r="D9" s="16">
+        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$9)^DCF!$B$6:$F$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$9-D$4)/(1+$A$9)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <v/>
+      </c>
+      <c r="E9" s="16">
+        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$9)^DCF!$B$6:$F$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$9-E$4)/(1+$A$9)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <v/>
+      </c>
+      <c r="F9" s="16">
+        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$9)^DCF!$B$6:$F$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$9-F$4)/(1+$A$9)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
@@ -3359,243 +5602,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Multi-stage dividend discount</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Dividends fade from the retention-implied growth to terminal g, at Ke.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Current DPS (USD)</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>1.71</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Near-term dividend growth</t>
-        </is>
-      </c>
-      <c r="B5" s="33" t="n">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Terminal growth</t>
-        </is>
-      </c>
-      <c r="B6" s="29">
-        <f>Assumptions!$B$22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Cost of equity (Ke)</t>
-        </is>
-      </c>
-      <c r="B7" s="7">
-        <f>WACC!$B$4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="15" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>Y1</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>Y2</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>Y3</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>Y4</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>Y5</t>
-        </is>
-      </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>Y6</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Growth (fade)</t>
-        </is>
-      </c>
-      <c r="B10" s="18">
-        <f>$B$5+($B$6-$B$5)*0/5</f>
-        <v/>
-      </c>
-      <c r="C10" s="18">
-        <f>$B$5+($B$6-$B$5)*1/5</f>
-        <v/>
-      </c>
-      <c r="D10" s="18">
-        <f>$B$5+($B$6-$B$5)*2/5</f>
-        <v/>
-      </c>
-      <c r="E10" s="18">
-        <f>$B$5+($B$6-$B$5)*3/5</f>
-        <v/>
-      </c>
-      <c r="F10" s="18">
-        <f>$B$5+($B$6-$B$5)*4/5</f>
-        <v/>
-      </c>
-      <c r="G10" s="18">
-        <f>$B$5+($B$6-$B$5)*5/5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>DPS</t>
-        </is>
-      </c>
-      <c r="B11" s="32">
-        <f>$B$4*(1+B10)</f>
-        <v/>
-      </c>
-      <c r="C11" s="32">
-        <f>B11*(1+C10)</f>
-        <v/>
-      </c>
-      <c r="D11" s="32">
-        <f>C11*(1+D10)</f>
-        <v/>
-      </c>
-      <c r="E11" s="32">
-        <f>D11*(1+E10)</f>
-        <v/>
-      </c>
-      <c r="F11" s="32">
-        <f>E11*(1+F10)</f>
-        <v/>
-      </c>
-      <c r="G11" s="32">
-        <f>F11*(1+G10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>PV of DPS</t>
-        </is>
-      </c>
-      <c r="B12" s="32">
-        <f>B11/(1+$B$7)^1</f>
-        <v/>
-      </c>
-      <c r="C12" s="32">
-        <f>C11/(1+$B$7)^2</f>
-        <v/>
-      </c>
-      <c r="D12" s="32">
-        <f>D11/(1+$B$7)^3</f>
-        <v/>
-      </c>
-      <c r="E12" s="32">
-        <f>E11/(1+$B$7)^4</f>
-        <v/>
-      </c>
-      <c r="F12" s="32">
-        <f>F11/(1+$B$7)^5</f>
-        <v/>
-      </c>
-      <c r="G12" s="32">
-        <f>G11/(1+$B$7)^6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>PV explicit dividends</t>
-        </is>
-      </c>
-      <c r="B14" s="32">
-        <f>SUM(B12:G12)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>PV terminal value</t>
-        </is>
-      </c>
-      <c r="B15" s="32">
-        <f>G11*(1+$B$6)/($B$7-$B$6)/(1+$B$7)^6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>Value per share</t>
-        </is>
-      </c>
-      <c r="B16" s="34">
-        <f>$B$14+$B$15</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3627,32 +5634,32 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Line item</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>FY2021</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="E4" s="16" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="F4" s="16" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -3664,16 +5671,16 @@
           <t>Tax Effect Of Unusual Items</t>
         </is>
       </c>
-      <c r="C5" s="21" t="n">
+      <c r="C5" s="29" t="n">
         <v>-2.52</v>
       </c>
-      <c r="D5" s="21" t="n">
+      <c r="D5" s="29" t="n">
         <v>117.234</v>
       </c>
-      <c r="E5" s="21" t="n">
+      <c r="E5" s="29" t="n">
         <v>14.022</v>
       </c>
-      <c r="F5" s="21" t="n">
+      <c r="F5" s="29" t="n">
         <v>-102.752</v>
       </c>
     </row>
@@ -3683,16 +5690,16 @@
           <t>Tax Rate For Calcs</t>
         </is>
       </c>
-      <c r="C6" s="21" t="n">
+      <c r="C6" s="29" t="n">
         <v>2.1e-07</v>
       </c>
-      <c r="D6" s="21" t="n">
+      <c r="D6" s="29" t="n">
         <v>3.51e-07</v>
       </c>
-      <c r="E6" s="21" t="n">
+      <c r="E6" s="29" t="n">
         <v>1.71e-07</v>
       </c>
-      <c r="F6" s="21" t="n">
+      <c r="F6" s="29" t="n">
         <v>3.38e-07</v>
       </c>
     </row>
@@ -3702,16 +5709,16 @@
           <t>Normalized EBITDA</t>
         </is>
       </c>
-      <c r="C7" s="21" t="n">
+      <c r="C7" s="29" t="n">
         <v>1570</v>
       </c>
-      <c r="D7" s="21" t="n">
+      <c r="D7" s="29" t="n">
         <v>4427</v>
       </c>
-      <c r="E7" s="21" t="n">
+      <c r="E7" s="29" t="n">
         <v>6947</v>
       </c>
-      <c r="F7" s="21" t="n">
+      <c r="F7" s="29" t="n">
         <v>6263</v>
       </c>
     </row>
@@ -3721,16 +5728,16 @@
           <t>Total Unusual Items</t>
         </is>
       </c>
-      <c r="C8" s="21" t="n">
+      <c r="C8" s="29" t="n">
         <v>-12</v>
       </c>
-      <c r="D8" s="21" t="n">
+      <c r="D8" s="29" t="n">
         <v>334</v>
       </c>
-      <c r="E8" s="21" t="n">
+      <c r="E8" s="29" t="n">
         <v>82</v>
       </c>
-      <c r="F8" s="21" t="n">
+      <c r="F8" s="29" t="n">
         <v>-304</v>
       </c>
     </row>
@@ -3740,16 +5747,16 @@
           <t>Total Unusual Items Excluding Goodwill</t>
         </is>
       </c>
-      <c r="C9" s="21" t="n">
+      <c r="C9" s="29" t="n">
         <v>-12</v>
       </c>
-      <c r="D9" s="21" t="n">
+      <c r="D9" s="29" t="n">
         <v>334</v>
       </c>
-      <c r="E9" s="21" t="n">
+      <c r="E9" s="29" t="n">
         <v>82</v>
       </c>
-      <c r="F9" s="21" t="n">
+      <c r="F9" s="29" t="n">
         <v>-304</v>
       </c>
     </row>
@@ -3759,16 +5766,16 @@
           <t>Net Income From Continuing Operation Net Minority Interest</t>
         </is>
       </c>
-      <c r="C10" s="21" t="n">
+      <c r="C10" s="29" t="n">
         <v>-160</v>
       </c>
-      <c r="D10" s="21" t="n">
+      <c r="D10" s="29" t="n">
         <v>1623</v>
       </c>
-      <c r="E10" s="21" t="n">
+      <c r="E10" s="29" t="n">
         <v>3749</v>
       </c>
-      <c r="F10" s="21" t="n">
+      <c r="F10" s="29" t="n">
         <v>2319</v>
       </c>
     </row>
@@ -3778,16 +5785,16 @@
           <t>Reconciled Depreciation</t>
         </is>
       </c>
-      <c r="C11" s="21" t="n">
+      <c r="C11" s="29" t="n">
         <v>1849</v>
       </c>
-      <c r="D11" s="21" t="n">
+      <c r="D11" s="29" t="n">
         <v>1883</v>
       </c>
-      <c r="E11" s="21" t="n">
+      <c r="E11" s="29" t="n">
         <v>2007</v>
       </c>
-      <c r="F11" s="21" t="n">
+      <c r="F11" s="29" t="n">
         <v>1937</v>
       </c>
     </row>
@@ -3797,16 +5804,16 @@
           <t>Reconciled Cost Of Revenue</t>
         </is>
       </c>
-      <c r="C12" s="21" t="n">
+      <c r="C12" s="29" t="n">
         <v>21545</v>
       </c>
-      <c r="D12" s="21" t="n">
+      <c r="D12" s="29" t="n">
         <v>20899</v>
       </c>
-      <c r="E12" s="21" t="n">
+      <c r="E12" s="29" t="n">
         <v>16694</v>
       </c>
-      <c r="F12" s="21" t="n">
+      <c r="F12" s="29" t="n">
         <v>19888</v>
       </c>
     </row>
@@ -3816,16 +5823,16 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="C13" s="21" t="n">
+      <c r="C13" s="29" t="n">
         <v>1558</v>
       </c>
-      <c r="D13" s="21" t="n">
+      <c r="D13" s="29" t="n">
         <v>4761</v>
       </c>
-      <c r="E13" s="21" t="n">
+      <c r="E13" s="29" t="n">
         <v>7029</v>
       </c>
-      <c r="F13" s="21" t="n">
+      <c r="F13" s="29" t="n">
         <v>5959</v>
       </c>
     </row>
@@ -3835,16 +5842,16 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="C14" s="21" t="n">
+      <c r="C14" s="29" t="n">
         <v>-291</v>
       </c>
-      <c r="D14" s="21" t="n">
+      <c r="D14" s="29" t="n">
         <v>2878</v>
       </c>
-      <c r="E14" s="21" t="n">
+      <c r="E14" s="29" t="n">
         <v>5022</v>
       </c>
-      <c r="F14" s="21" t="n">
+      <c r="F14" s="29" t="n">
         <v>4022</v>
       </c>
     </row>
@@ -3854,16 +5861,16 @@
           <t>Net Interest Income</t>
         </is>
       </c>
-      <c r="C15" s="21" t="n">
+      <c r="C15" s="29" t="n">
         <v>-251</v>
       </c>
-      <c r="D15" s="21" t="n">
+      <c r="D15" s="29" t="n">
         <v>-431</v>
       </c>
-      <c r="E15" s="21" t="n">
+      <c r="E15" s="29" t="n">
         <v>-506</v>
       </c>
-      <c r="F15" s="21" t="n">
+      <c r="F15" s="29" t="n">
         <v>-511</v>
       </c>
     </row>
@@ -3873,16 +5880,16 @@
           <t>Interest Expense</t>
         </is>
       </c>
-      <c r="C16" s="21" t="n">
+      <c r="C16" s="29" t="n">
         <v>251</v>
       </c>
-      <c r="D16" s="21" t="n">
+      <c r="D16" s="29" t="n">
         <v>431</v>
       </c>
-      <c r="E16" s="21" t="n">
+      <c r="E16" s="29" t="n">
         <v>506</v>
       </c>
-      <c r="F16" s="21" t="n">
+      <c r="F16" s="29" t="n">
         <v>511</v>
       </c>
     </row>
@@ -3892,10 +5899,10 @@
           <t>Interest Income</t>
         </is>
       </c>
-      <c r="B17" s="21" t="n">
+      <c r="B17" s="29" t="n">
         <v>98</v>
       </c>
-      <c r="C17" s="21" t="n">
+      <c r="C17" s="29" t="n">
         <v>93</v>
       </c>
     </row>
@@ -3905,16 +5912,16 @@
           <t>Normalized Income</t>
         </is>
       </c>
-      <c r="C18" s="21" t="n">
+      <c r="C18" s="29" t="n">
         <v>-150.52</v>
       </c>
-      <c r="D18" s="21" t="n">
+      <c r="D18" s="29" t="n">
         <v>1406.234</v>
       </c>
-      <c r="E18" s="21" t="n">
+      <c r="E18" s="29" t="n">
         <v>3681.022</v>
       </c>
-      <c r="F18" s="21" t="n">
+      <c r="F18" s="29" t="n">
         <v>2520.248</v>
       </c>
     </row>
@@ -3924,16 +5931,16 @@
           <t>Net Income From Continuing And Discontinued Operation</t>
         </is>
       </c>
-      <c r="C19" s="21" t="n">
+      <c r="C19" s="29" t="n">
         <v>-160</v>
       </c>
-      <c r="D19" s="21" t="n">
+      <c r="D19" s="29" t="n">
         <v>1623</v>
       </c>
-      <c r="E19" s="21" t="n">
+      <c r="E19" s="29" t="n">
         <v>3749</v>
       </c>
-      <c r="F19" s="21" t="n">
+      <c r="F19" s="29" t="n">
         <v>2319</v>
       </c>
     </row>
@@ -3943,16 +5950,16 @@
           <t>Total Expenses</t>
         </is>
       </c>
-      <c r="C20" s="21" t="n">
+      <c r="C20" s="29" t="n">
         <v>24848</v>
       </c>
-      <c r="D20" s="21" t="n">
+      <c r="D20" s="29" t="n">
         <v>22532</v>
       </c>
-      <c r="E20" s="21" t="n">
+      <c r="E20" s="29" t="n">
         <v>18720</v>
       </c>
-      <c r="F20" s="21" t="n">
+      <c r="F20" s="29" t="n">
         <v>21335</v>
       </c>
     </row>
@@ -3962,16 +5969,16 @@
           <t>Total Operating Income As Reported</t>
         </is>
       </c>
-      <c r="C21" s="21" t="n">
+      <c r="C21" s="29" t="n">
         <v>495</v>
       </c>
-      <c r="D21" s="21" t="n">
+      <c r="D21" s="29" t="n">
         <v>1610</v>
       </c>
-      <c r="E21" s="21" t="n">
+      <c r="E21" s="29" t="n">
         <v>4352</v>
       </c>
-      <c r="F21" s="21" t="n">
+      <c r="F21" s="29" t="n">
         <v>3086</v>
       </c>
     </row>
@@ -3981,16 +5988,16 @@
           <t>Diluted Average Shares</t>
         </is>
       </c>
-      <c r="C22" s="21" t="n">
+      <c r="C22" s="29" t="n">
         <v>327</v>
       </c>
-      <c r="D22" s="21" t="n">
+      <c r="D22" s="29" t="n">
         <v>324</v>
       </c>
-      <c r="E22" s="21" t="n">
+      <c r="E22" s="29" t="n">
         <v>315</v>
       </c>
-      <c r="F22" s="21" t="n">
+      <c r="F22" s="29" t="n">
         <v>314</v>
       </c>
     </row>
@@ -4000,16 +6007,16 @@
           <t>Basic Average Shares</t>
         </is>
       </c>
-      <c r="C23" s="21" t="n">
+      <c r="C23" s="29" t="n">
         <v>327</v>
       </c>
-      <c r="D23" s="21" t="n">
+      <c r="D23" s="29" t="n">
         <v>323</v>
       </c>
-      <c r="E23" s="21" t="n">
+      <c r="E23" s="29" t="n">
         <v>315</v>
       </c>
-      <c r="F23" s="21" t="n">
+      <c r="F23" s="29" t="n">
         <v>313</v>
       </c>
     </row>
@@ -4019,16 +6026,16 @@
           <t>Diluted EPS</t>
         </is>
       </c>
-      <c r="C24" s="21" t="n">
+      <c r="C24" s="29" t="n">
         <v>-4.892969999999999e-07</v>
       </c>
-      <c r="D24" s="21" t="n">
+      <c r="D24" s="29" t="n">
         <v>5.009999999999999e-06</v>
       </c>
-      <c r="E24" s="21" t="n">
+      <c r="E24" s="29" t="n">
         <v>1.189e-05</v>
       </c>
-      <c r="F24" s="21" t="n">
+      <c r="F24" s="29" t="n">
         <v>7.4e-06</v>
       </c>
     </row>
@@ -4038,16 +6045,16 @@
           <t>Basic EPS</t>
         </is>
       </c>
-      <c r="C25" s="21" t="n">
+      <c r="C25" s="29" t="n">
         <v>-4.892969999999999e-07</v>
       </c>
-      <c r="D25" s="21" t="n">
+      <c r="D25" s="29" t="n">
         <v>5.019999999999999e-06</v>
       </c>
-      <c r="E25" s="21" t="n">
+      <c r="E25" s="29" t="n">
         <v>1.191e-05</v>
       </c>
-      <c r="F25" s="21" t="n">
+      <c r="F25" s="29" t="n">
         <v>7.4e-06</v>
       </c>
     </row>
@@ -4057,16 +6064,16 @@
           <t>Diluted NI Availto Com Stockholders</t>
         </is>
       </c>
-      <c r="C26" s="21" t="n">
+      <c r="C26" s="29" t="n">
         <v>-160</v>
       </c>
-      <c r="D26" s="21" t="n">
+      <c r="D26" s="29" t="n">
         <v>1623</v>
       </c>
-      <c r="E26" s="21" t="n">
+      <c r="E26" s="29" t="n">
         <v>3749</v>
       </c>
-      <c r="F26" s="21" t="n">
+      <c r="F26" s="29" t="n">
         <v>2319</v>
       </c>
     </row>
@@ -4076,16 +6083,16 @@
           <t>Net Income Common Stockholders</t>
         </is>
       </c>
-      <c r="C27" s="21" t="n">
+      <c r="C27" s="29" t="n">
         <v>-160</v>
       </c>
-      <c r="D27" s="21" t="n">
+      <c r="D27" s="29" t="n">
         <v>1623</v>
       </c>
-      <c r="E27" s="21" t="n">
+      <c r="E27" s="29" t="n">
         <v>3749</v>
       </c>
-      <c r="F27" s="21" t="n">
+      <c r="F27" s="29" t="n">
         <v>2319</v>
       </c>
     </row>
@@ -4095,16 +6102,16 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="C28" s="21" t="n">
+      <c r="C28" s="29" t="n">
         <v>-160</v>
       </c>
-      <c r="D28" s="21" t="n">
+      <c r="D28" s="29" t="n">
         <v>1623</v>
       </c>
-      <c r="E28" s="21" t="n">
+      <c r="E28" s="29" t="n">
         <v>3749</v>
       </c>
-      <c r="F28" s="21" t="n">
+      <c r="F28" s="29" t="n">
         <v>2319</v>
       </c>
     </row>
@@ -4114,16 +6121,16 @@
           <t>Minority Interests</t>
         </is>
       </c>
-      <c r="C29" s="21" t="n">
+      <c r="C29" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="D29" s="21" t="n">
+      <c r="D29" s="29" t="n">
         <v>46</v>
       </c>
-      <c r="E29" s="21" t="n">
+      <c r="E29" s="29" t="n">
         <v>11</v>
       </c>
-      <c r="F29" s="21" t="n">
+      <c r="F29" s="29" t="n">
         <v>-4</v>
       </c>
     </row>
@@ -4133,16 +6140,16 @@
           <t>Net Income Including Noncontrolling Interests</t>
         </is>
       </c>
-      <c r="C30" s="21" t="n">
+      <c r="C30" s="29" t="n">
         <v>-167</v>
       </c>
-      <c r="D30" s="21" t="n">
+      <c r="D30" s="29" t="n">
         <v>1577</v>
       </c>
-      <c r="E30" s="21" t="n">
+      <c r="E30" s="29" t="n">
         <v>3738</v>
       </c>
-      <c r="F30" s="21" t="n">
+      <c r="F30" s="29" t="n">
         <v>2323</v>
       </c>
     </row>
@@ -4152,16 +6159,16 @@
           <t>Net Income Continuous Operations</t>
         </is>
       </c>
-      <c r="C31" s="21" t="n">
+      <c r="C31" s="29" t="n">
         <v>-167</v>
       </c>
-      <c r="D31" s="21" t="n">
+      <c r="D31" s="29" t="n">
         <v>1577</v>
       </c>
-      <c r="E31" s="21" t="n">
+      <c r="E31" s="29" t="n">
         <v>3738</v>
       </c>
-      <c r="F31" s="21" t="n">
+      <c r="F31" s="29" t="n">
         <v>2323</v>
       </c>
     </row>
@@ -4171,16 +6178,16 @@
           <t>Earnings From Equity Interest Net Of Tax</t>
         </is>
       </c>
-      <c r="C32" s="21" t="n">
+      <c r="C32" s="29" t="n">
         <v>-13</v>
       </c>
-      <c r="D32" s="21" t="n">
+      <c r="D32" s="29" t="n">
         <v>-11</v>
       </c>
-      <c r="E32" s="21" t="n">
+      <c r="E32" s="29" t="n">
         <v>-4</v>
       </c>
-      <c r="F32" s="21" t="n">
+      <c r="F32" s="29" t="n">
         <v>-1</v>
       </c>
     </row>
@@ -4190,16 +6197,16 @@
           <t>Tax Provision</t>
         </is>
       </c>
-      <c r="C33" s="21" t="n">
+      <c r="C33" s="29" t="n">
         <v>-388</v>
       </c>
-      <c r="D33" s="21" t="n">
+      <c r="D33" s="29" t="n">
         <v>859</v>
       </c>
-      <c r="E33" s="21" t="n">
+      <c r="E33" s="29" t="n">
         <v>774</v>
       </c>
-      <c r="F33" s="21" t="n">
+      <c r="F33" s="29" t="n">
         <v>1187</v>
       </c>
     </row>
@@ -4209,16 +6216,16 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="C34" s="21" t="n">
+      <c r="C34" s="29" t="n">
         <v>-542</v>
       </c>
-      <c r="D34" s="21" t="n">
+      <c r="D34" s="29" t="n">
         <v>2447</v>
       </c>
-      <c r="E34" s="21" t="n">
+      <c r="E34" s="29" t="n">
         <v>4516</v>
       </c>
-      <c r="F34" s="21" t="n">
+      <c r="F34" s="29" t="n">
         <v>3511</v>
       </c>
     </row>
@@ -4228,16 +6235,16 @@
           <t>Other Income Expense</t>
         </is>
       </c>
-      <c r="C35" s="21" t="n">
+      <c r="C35" s="29" t="n">
         <v>117</v>
       </c>
-      <c r="D35" s="21" t="n">
+      <c r="D35" s="29" t="n">
         <v>492</v>
       </c>
-      <c r="E35" s="21" t="n">
+      <c r="E35" s="29" t="n">
         <v>174</v>
       </c>
-      <c r="F35" s="21" t="n">
+      <c r="F35" s="29" t="n">
         <v>-176</v>
       </c>
     </row>
@@ -4247,16 +6254,16 @@
           <t>Other Non Operating Income Expenses</t>
         </is>
       </c>
-      <c r="C36" s="21" t="n">
+      <c r="C36" s="29" t="n">
         <v>129</v>
       </c>
-      <c r="D36" s="21" t="n">
+      <c r="D36" s="29" t="n">
         <v>158</v>
       </c>
-      <c r="E36" s="21" t="n">
+      <c r="E36" s="29" t="n">
         <v>92</v>
       </c>
-      <c r="F36" s="21" t="n">
+      <c r="F36" s="29" t="n">
         <v>128</v>
       </c>
     </row>
@@ -4266,16 +6273,16 @@
           <t>Special Income Charges</t>
         </is>
       </c>
-      <c r="C37" s="21" t="n">
+      <c r="C37" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="D37" s="21" t="n">
+      <c r="D37" s="29" t="n">
         <v>27</v>
       </c>
-      <c r="E37" s="21" t="n">
+      <c r="E37" s="29" t="n">
         <v>71</v>
       </c>
-      <c r="F37" s="21" t="n">
+      <c r="F37" s="29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4285,16 +6292,16 @@
           <t>Gain On Sale Of Ppe</t>
         </is>
       </c>
-      <c r="C38" s="21" t="n">
+      <c r="C38" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="D38" s="21" t="n">
+      <c r="D38" s="29" t="n">
         <v>27</v>
       </c>
-      <c r="E38" s="21" t="n">
+      <c r="E38" s="29" t="n">
         <v>71</v>
       </c>
-      <c r="F38" s="21" t="n">
+      <c r="F38" s="29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4304,16 +6311,16 @@
           <t>Gain On Sale Of Security</t>
         </is>
       </c>
-      <c r="C39" s="21" t="n">
+      <c r="C39" s="29" t="n">
         <v>-13</v>
       </c>
-      <c r="D39" s="21" t="n">
+      <c r="D39" s="29" t="n">
         <v>307</v>
       </c>
-      <c r="E39" s="21" t="n">
+      <c r="E39" s="29" t="n">
         <v>11</v>
       </c>
-      <c r="F39" s="21" t="n">
+      <c r="F39" s="29" t="n">
         <v>-304</v>
       </c>
     </row>
@@ -4323,16 +6330,16 @@
           <t>Net Non Operating Interest Income Expense</t>
         </is>
       </c>
-      <c r="C40" s="21" t="n">
+      <c r="C40" s="29" t="n">
         <v>-251</v>
       </c>
-      <c r="D40" s="21" t="n">
+      <c r="D40" s="29" t="n">
         <v>-431</v>
       </c>
-      <c r="E40" s="21" t="n">
+      <c r="E40" s="29" t="n">
         <v>-506</v>
       </c>
-      <c r="F40" s="21" t="n">
+      <c r="F40" s="29" t="n">
         <v>-511</v>
       </c>
     </row>
@@ -4342,16 +6349,16 @@
           <t>Interest Expense Non Operating</t>
         </is>
       </c>
-      <c r="C41" s="21" t="n">
+      <c r="C41" s="29" t="n">
         <v>251</v>
       </c>
-      <c r="D41" s="21" t="n">
+      <c r="D41" s="29" t="n">
         <v>431</v>
       </c>
-      <c r="E41" s="21" t="n">
+      <c r="E41" s="29" t="n">
         <v>506</v>
       </c>
-      <c r="F41" s="21" t="n">
+      <c r="F41" s="29" t="n">
         <v>511</v>
       </c>
     </row>
@@ -4361,10 +6368,10 @@
           <t>Interest Income Non Operating</t>
         </is>
       </c>
-      <c r="B42" s="21" t="n">
+      <c r="B42" s="29" t="n">
         <v>98</v>
       </c>
-      <c r="C42" s="21" t="n">
+      <c r="C42" s="29" t="n">
         <v>93</v>
       </c>
     </row>
@@ -4374,16 +6381,16 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="C43" s="21" t="n">
+      <c r="C43" s="29" t="n">
         <v>-408</v>
       </c>
-      <c r="D43" s="21" t="n">
+      <c r="D43" s="29" t="n">
         <v>2386</v>
       </c>
-      <c r="E43" s="21" t="n">
+      <c r="E43" s="29" t="n">
         <v>4848</v>
       </c>
-      <c r="F43" s="21" t="n">
+      <c r="F43" s="29" t="n">
         <v>4198</v>
       </c>
     </row>
@@ -4393,16 +6400,16 @@
           <t>Operating Expense</t>
         </is>
       </c>
-      <c r="C44" s="21" t="n">
+      <c r="C44" s="29" t="n">
         <v>2545</v>
       </c>
-      <c r="D44" s="21" t="n">
+      <c r="D44" s="29" t="n">
         <v>846</v>
       </c>
-      <c r="E44" s="21" t="n">
+      <c r="E44" s="29" t="n">
         <v>1142</v>
       </c>
-      <c r="F44" s="21" t="n">
+      <c r="F44" s="29" t="n">
         <v>495</v>
       </c>
     </row>
@@ -4412,16 +6419,16 @@
           <t>Other Operating Expenses</t>
         </is>
       </c>
-      <c r="C45" s="21" t="n">
+      <c r="C45" s="29" t="n">
         <v>902</v>
       </c>
-      <c r="D45" s="21" t="n">
+      <c r="D45" s="29" t="n">
         <v>-803</v>
       </c>
-      <c r="E45" s="21" t="n">
+      <c r="E45" s="29" t="n">
         <v>-567</v>
       </c>
-      <c r="F45" s="21" t="n">
+      <c r="F45" s="29" t="n">
         <v>-1112</v>
       </c>
     </row>
@@ -4431,16 +6438,16 @@
           <t>Other Taxes</t>
         </is>
       </c>
-      <c r="C46" s="21" t="n">
+      <c r="C46" s="29" t="n">
         <v>552</v>
       </c>
-      <c r="D46" s="21" t="n">
+      <c r="D46" s="29" t="n">
         <v>553</v>
       </c>
-      <c r="E46" s="21" t="n">
+      <c r="E46" s="29" t="n">
         <v>586</v>
       </c>
-      <c r="F46" s="21" t="n">
+      <c r="F46" s="29" t="n">
         <v>622</v>
       </c>
     </row>
@@ -4450,16 +6457,16 @@
           <t>Depreciation Amortization Depletion Income Statement</t>
         </is>
       </c>
-      <c r="C47" s="21" t="n">
+      <c r="C47" s="29" t="n">
         <v>1091</v>
       </c>
-      <c r="D47" s="21" t="n">
+      <c r="D47" s="29" t="n">
         <v>1096</v>
       </c>
-      <c r="E47" s="21" t="n">
+      <c r="E47" s="29" t="n">
         <v>1123</v>
       </c>
-      <c r="F47" s="21" t="n">
+      <c r="F47" s="29" t="n">
         <v>985</v>
       </c>
     </row>
@@ -4469,16 +6476,16 @@
           <t>Depreciation And Amortization In Income Statement</t>
         </is>
       </c>
-      <c r="C48" s="21" t="n">
+      <c r="C48" s="29" t="n">
         <v>1091</v>
       </c>
-      <c r="D48" s="21" t="n">
+      <c r="D48" s="29" t="n">
         <v>1096</v>
       </c>
-      <c r="E48" s="21" t="n">
+      <c r="E48" s="29" t="n">
         <v>1123</v>
       </c>
-      <c r="F48" s="21" t="n">
+      <c r="F48" s="29" t="n">
         <v>985</v>
       </c>
     </row>
@@ -4488,13 +6495,13 @@
           <t>Selling General And Administration</t>
         </is>
       </c>
-      <c r="B49" s="21" t="n">
+      <c r="B49" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="C49" s="21" t="n">
+      <c r="C49" s="29" t="n">
         <v>-110</v>
       </c>
-      <c r="D49" s="21" t="n">
+      <c r="D49" s="29" t="n">
         <v>-54</v>
       </c>
     </row>
@@ -4504,10 +6511,10 @@
           <t>General And Administrative Expense</t>
         </is>
       </c>
-      <c r="C50" s="21" t="n">
+      <c r="C50" s="29" t="n">
         <v>-110</v>
       </c>
-      <c r="D50" s="21" t="n">
+      <c r="D50" s="29" t="n">
         <v>-54</v>
       </c>
     </row>
@@ -4517,13 +6524,13 @@
           <t>Salaries And Wages</t>
         </is>
       </c>
-      <c r="B51" s="21" t="n">
+      <c r="B51" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="C51" s="21" t="n">
+      <c r="C51" s="29" t="n">
         <v>-110</v>
       </c>
-      <c r="D51" s="21" t="n">
+      <c r="D51" s="29" t="n">
         <v>-54</v>
       </c>
     </row>
@@ -4533,16 +6540,16 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="C52" s="21" t="n">
+      <c r="C52" s="29" t="n">
         <v>2137</v>
       </c>
-      <c r="D52" s="21" t="n">
+      <c r="D52" s="29" t="n">
         <v>3232</v>
       </c>
-      <c r="E52" s="21" t="n">
+      <c r="E52" s="29" t="n">
         <v>5990</v>
       </c>
-      <c r="F52" s="21" t="n">
+      <c r="F52" s="29" t="n">
         <v>4693</v>
       </c>
     </row>
@@ -4552,16 +6559,16 @@
           <t>Cost Of Revenue</t>
         </is>
       </c>
-      <c r="C53" s="21" t="n">
+      <c r="C53" s="29" t="n">
         <v>22303</v>
       </c>
-      <c r="D53" s="21" t="n">
+      <c r="D53" s="29" t="n">
         <v>21686</v>
       </c>
-      <c r="E53" s="21" t="n">
+      <c r="E53" s="29" t="n">
         <v>17578</v>
       </c>
-      <c r="F53" s="21" t="n">
+      <c r="F53" s="29" t="n">
         <v>20840</v>
       </c>
     </row>
@@ -4571,16 +6578,16 @@
           <t>Total Revenue</t>
         </is>
       </c>
-      <c r="C54" s="21" t="n">
+      <c r="C54" s="29" t="n">
         <v>24440</v>
       </c>
-      <c r="D54" s="21" t="n">
+      <c r="D54" s="29" t="n">
         <v>24918</v>
       </c>
-      <c r="E54" s="21" t="n">
+      <c r="E54" s="29" t="n">
         <v>23568</v>
       </c>
-      <c r="F54" s="21" t="n">
+      <c r="F54" s="29" t="n">
         <v>25533</v>
       </c>
     </row>
@@ -4590,1545 +6597,17 @@
           <t>Operating Revenue</t>
         </is>
       </c>
-      <c r="C55" s="21" t="n">
+      <c r="C55" s="29" t="n">
         <v>24440</v>
       </c>
-      <c r="D55" s="21" t="n">
+      <c r="D55" s="29" t="n">
         <v>24918</v>
       </c>
-      <c r="E55" s="21" t="n">
+      <c r="E55" s="29" t="n">
         <v>23568</v>
       </c>
-      <c r="F55" s="21" t="n">
+      <c r="F55" s="29" t="n">
         <v>25533</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F84"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>CEG — BS (reported)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>As reported by yfinance (USDmm). Hardcoded actuals.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="15" t="inlineStr">
-        <is>
-          <t>Line item</t>
-        </is>
-      </c>
-      <c r="B4" s="16" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="C4" s="16" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="D4" s="16" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E4" s="16" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="F4" s="16" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Ordinary Shares Number</t>
-        </is>
-      </c>
-      <c r="C5" s="21" t="n">
-        <v>327</v>
-      </c>
-      <c r="D5" s="21" t="n">
-        <v>317</v>
-      </c>
-      <c r="E5" s="21" t="n">
-        <v>312.838</v>
-      </c>
-      <c r="F5" s="21" t="n">
-        <v>312.29008</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Share Issued</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="n">
-        <v>327</v>
-      </c>
-      <c r="D6" s="21" t="n">
-        <v>317</v>
-      </c>
-      <c r="E6" s="21" t="n">
-        <v>312.838</v>
-      </c>
-      <c r="F6" s="21" t="n">
-        <v>312.29008</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Net Debt</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="n">
-        <v>5346</v>
-      </c>
-      <c r="D7" s="21" t="n">
-        <v>8893</v>
-      </c>
-      <c r="E7" s="21" t="n">
-        <v>5390</v>
-      </c>
-      <c r="F7" s="21" t="n">
-        <v>5351</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Total Debt</t>
-        </is>
-      </c>
-      <c r="C8" s="21" t="n">
-        <v>5768</v>
-      </c>
-      <c r="D8" s="21" t="n">
-        <v>9261</v>
-      </c>
-      <c r="E8" s="21" t="n">
-        <v>8412</v>
-      </c>
-      <c r="F8" s="21" t="n">
-        <v>8992</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Tangible Book Value</t>
-        </is>
-      </c>
-      <c r="C9" s="21" t="n">
-        <v>10971</v>
-      </c>
-      <c r="D9" s="21" t="n">
-        <v>10500</v>
-      </c>
-      <c r="E9" s="21" t="n">
-        <v>12746</v>
-      </c>
-      <c r="F9" s="21" t="n">
-        <v>14097</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Invested Capital</t>
-        </is>
-      </c>
-      <c r="C10" s="21" t="n">
-        <v>16786</v>
-      </c>
-      <c r="D10" s="21" t="n">
-        <v>20186</v>
-      </c>
-      <c r="E10" s="21" t="n">
-        <v>21578</v>
-      </c>
-      <c r="F10" s="21" t="n">
-        <v>23509</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Working Capital</t>
-        </is>
-      </c>
-      <c r="C11" s="21" t="n">
-        <v>1521</v>
-      </c>
-      <c r="D11" s="21" t="n">
-        <v>1980</v>
-      </c>
-      <c r="E11" s="21" t="n">
-        <v>3930</v>
-      </c>
-      <c r="F11" s="21" t="n">
-        <v>4175</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Net Tangible Assets</t>
-        </is>
-      </c>
-      <c r="C12" s="21" t="n">
-        <v>10971</v>
-      </c>
-      <c r="D12" s="21" t="n">
-        <v>10500</v>
-      </c>
-      <c r="E12" s="21" t="n">
-        <v>12746</v>
-      </c>
-      <c r="F12" s="21" t="n">
-        <v>14097</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Common Stock Equity</t>
-        </is>
-      </c>
-      <c r="C13" s="21" t="n">
-        <v>11018</v>
-      </c>
-      <c r="D13" s="21" t="n">
-        <v>10925</v>
-      </c>
-      <c r="E13" s="21" t="n">
-        <v>13166</v>
-      </c>
-      <c r="F13" s="21" t="n">
-        <v>14517</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Total Capitalization</t>
-        </is>
-      </c>
-      <c r="C14" s="21" t="n">
-        <v>15484</v>
-      </c>
-      <c r="D14" s="21" t="n">
-        <v>18421</v>
-      </c>
-      <c r="E14" s="21" t="n">
-        <v>20550</v>
-      </c>
-      <c r="F14" s="21" t="n">
-        <v>21767</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Total Equity Gross Minority Interest</t>
-        </is>
-      </c>
-      <c r="C15" s="21" t="n">
-        <v>11372</v>
-      </c>
-      <c r="D15" s="21" t="n">
-        <v>11286</v>
-      </c>
-      <c r="E15" s="21" t="n">
-        <v>13539</v>
-      </c>
-      <c r="F15" s="21" t="n">
-        <v>14853</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Minority Interest</t>
-        </is>
-      </c>
-      <c r="C16" s="21" t="n">
-        <v>354</v>
-      </c>
-      <c r="D16" s="21" t="n">
-        <v>361</v>
-      </c>
-      <c r="E16" s="21" t="n">
-        <v>373</v>
-      </c>
-      <c r="F16" s="21" t="n">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Stockholders Equity</t>
-        </is>
-      </c>
-      <c r="C17" s="21" t="n">
-        <v>11018</v>
-      </c>
-      <c r="D17" s="21" t="n">
-        <v>10925</v>
-      </c>
-      <c r="E17" s="21" t="n">
-        <v>13166</v>
-      </c>
-      <c r="F17" s="21" t="n">
-        <v>14517</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>Other Equity Interest</t>
-        </is>
-      </c>
-      <c r="B18" s="21" t="n">
-        <v>11250</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Gains Losses Not Affecting Retained Earnings</t>
-        </is>
-      </c>
-      <c r="C19" s="21" t="n">
-        <v>-1760</v>
-      </c>
-      <c r="D19" s="21" t="n">
-        <v>-2191</v>
-      </c>
-      <c r="E19" s="21" t="n">
-        <v>-2302</v>
-      </c>
-      <c r="F19" s="21" t="n">
-        <v>-2425</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Other Equity Adjustments</t>
-        </is>
-      </c>
-      <c r="C20" s="21" t="n">
-        <v>-1760</v>
-      </c>
-      <c r="D20" s="21" t="n">
-        <v>-2191</v>
-      </c>
-      <c r="E20" s="21" t="n">
-        <v>-2302</v>
-      </c>
-      <c r="F20" s="21" t="n">
-        <v>-2425</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>Retained Earnings</t>
-        </is>
-      </c>
-      <c r="C21" s="21" t="n">
-        <v>-496</v>
-      </c>
-      <c r="D21" s="21" t="n">
-        <v>761</v>
-      </c>
-      <c r="E21" s="21" t="n">
-        <v>4066</v>
-      </c>
-      <c r="F21" s="21" t="n">
-        <v>5899</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>Capital Stock</t>
-        </is>
-      </c>
-      <c r="C22" s="21" t="n">
-        <v>13274</v>
-      </c>
-      <c r="D22" s="21" t="n">
-        <v>12355</v>
-      </c>
-      <c r="E22" s="21" t="n">
-        <v>11402</v>
-      </c>
-      <c r="F22" s="21" t="n">
-        <v>11043</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>Common Stock</t>
-        </is>
-      </c>
-      <c r="C23" s="21" t="n">
-        <v>13274</v>
-      </c>
-      <c r="D23" s="21" t="n">
-        <v>12355</v>
-      </c>
-      <c r="E23" s="21" t="n">
-        <v>11402</v>
-      </c>
-      <c r="F23" s="21" t="n">
-        <v>11043</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>Total Liabilities Net Minority Interest</t>
-        </is>
-      </c>
-      <c r="C24" s="21" t="n">
-        <v>35537</v>
-      </c>
-      <c r="D24" s="21" t="n">
-        <v>39472</v>
-      </c>
-      <c r="E24" s="21" t="n">
-        <v>39387</v>
-      </c>
-      <c r="F24" s="21" t="n">
-        <v>42396</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>Total Non Current Liabilities Net Minority Interest</t>
-        </is>
-      </c>
-      <c r="C25" s="21" t="n">
-        <v>27698</v>
-      </c>
-      <c r="D25" s="21" t="n">
-        <v>33153</v>
-      </c>
-      <c r="E25" s="21" t="n">
-        <v>32541</v>
-      </c>
-      <c r="F25" s="21" t="n">
-        <v>34452</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>Other Non Current Liabilities</t>
-        </is>
-      </c>
-      <c r="C26" s="21" t="n">
-        <v>2408</v>
-      </c>
-      <c r="D26" s="21" t="n">
-        <v>2421</v>
-      </c>
-      <c r="E26" s="21" t="n">
-        <v>2585</v>
-      </c>
-      <c r="F26" s="21" t="n">
-        <v>2740</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>Derivative Product Liabilities</t>
-        </is>
-      </c>
-      <c r="C27" s="21" t="n">
-        <v>983</v>
-      </c>
-      <c r="D27" s="21" t="n">
-        <v>419</v>
-      </c>
-      <c r="E27" s="21" t="n">
-        <v>399</v>
-      </c>
-      <c r="F27" s="21" t="n">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>Employee Benefits</t>
-        </is>
-      </c>
-      <c r="C28" s="21" t="n">
-        <v>1214</v>
-      </c>
-      <c r="D28" s="21" t="n">
-        <v>1802</v>
-      </c>
-      <c r="E28" s="21" t="n">
-        <v>1875</v>
-      </c>
-      <c r="F28" s="21" t="n">
-        <v>1977</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>Non Current Pension And Other Postretirement Benefit Plans</t>
-        </is>
-      </c>
-      <c r="C29" s="21" t="n">
-        <v>1214</v>
-      </c>
-      <c r="D29" s="21" t="n">
-        <v>1802</v>
-      </c>
-      <c r="E29" s="21" t="n">
-        <v>1875</v>
-      </c>
-      <c r="F29" s="21" t="n">
-        <v>1977</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>Dueto Related Parties Non Current</t>
-        </is>
-      </c>
-      <c r="B30" s="21" t="n">
-        <v>3357</v>
-      </c>
-      <c r="C30" s="21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>Tradeand Other Payables Non Current</t>
-        </is>
-      </c>
-      <c r="C31" s="21" t="n">
-        <v>2897</v>
-      </c>
-      <c r="D31" s="21" t="n">
-        <v>3688</v>
-      </c>
-      <c r="E31" s="21" t="n">
-        <v>4518</v>
-      </c>
-      <c r="F31" s="21" t="n">
-        <v>5334</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>Non Current Deferred Liabilities</t>
-        </is>
-      </c>
-      <c r="C32" s="21" t="n">
-        <v>3031</v>
-      </c>
-      <c r="D32" s="21" t="n">
-        <v>3209</v>
-      </c>
-      <c r="E32" s="21" t="n">
-        <v>3331</v>
-      </c>
-      <c r="F32" s="21" t="n">
-        <v>3544</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>Non Current Deferred Taxes Liabilities</t>
-        </is>
-      </c>
-      <c r="C33" s="21" t="n">
-        <v>3031</v>
-      </c>
-      <c r="D33" s="21" t="n">
-        <v>3209</v>
-      </c>
-      <c r="E33" s="21" t="n">
-        <v>3331</v>
-      </c>
-      <c r="F33" s="21" t="n">
-        <v>3544</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>Long Term Debt And Capital Lease Obligation</t>
-        </is>
-      </c>
-      <c r="C34" s="21" t="n">
-        <v>4466</v>
-      </c>
-      <c r="D34" s="21" t="n">
-        <v>7496</v>
-      </c>
-      <c r="E34" s="21" t="n">
-        <v>7384</v>
-      </c>
-      <c r="F34" s="21" t="n">
-        <v>7250</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>Long Term Debt</t>
-        </is>
-      </c>
-      <c r="C35" s="21" t="n">
-        <v>4466</v>
-      </c>
-      <c r="D35" s="21" t="n">
-        <v>7496</v>
-      </c>
-      <c r="E35" s="21" t="n">
-        <v>7384</v>
-      </c>
-      <c r="F35" s="21" t="n">
-        <v>7250</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>Long Term Provisions</t>
-        </is>
-      </c>
-      <c r="C36" s="21" t="n">
-        <v>12699</v>
-      </c>
-      <c r="D36" s="21" t="n">
-        <v>14118</v>
-      </c>
-      <c r="E36" s="21" t="n">
-        <v>12449</v>
-      </c>
-      <c r="F36" s="21" t="n">
-        <v>13193</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>Current Liabilities</t>
-        </is>
-      </c>
-      <c r="C37" s="21" t="n">
-        <v>7839</v>
-      </c>
-      <c r="D37" s="21" t="n">
-        <v>6319</v>
-      </c>
-      <c r="E37" s="21" t="n">
-        <v>6846</v>
-      </c>
-      <c r="F37" s="21" t="n">
-        <v>7944</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>Other Current Liabilities</t>
-        </is>
-      </c>
-      <c r="C38" s="21" t="n">
-        <v>2803</v>
-      </c>
-      <c r="D38" s="21" t="n">
-        <v>1942</v>
-      </c>
-      <c r="E38" s="21" t="n">
-        <v>1875</v>
-      </c>
-      <c r="F38" s="21" t="n">
-        <v>1908</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>Current Debt And Capital Lease Obligation</t>
-        </is>
-      </c>
-      <c r="C39" s="21" t="n">
-        <v>1302</v>
-      </c>
-      <c r="D39" s="21" t="n">
-        <v>1765</v>
-      </c>
-      <c r="E39" s="21" t="n">
-        <v>1028</v>
-      </c>
-      <c r="F39" s="21" t="n">
-        <v>1742</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>Current Debt</t>
-        </is>
-      </c>
-      <c r="C40" s="21" t="n">
-        <v>1302</v>
-      </c>
-      <c r="D40" s="21" t="n">
-        <v>1765</v>
-      </c>
-      <c r="E40" s="21" t="n">
-        <v>1028</v>
-      </c>
-      <c r="F40" s="21" t="n">
-        <v>1742</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>Other Current Borrowings</t>
-        </is>
-      </c>
-      <c r="C41" s="21" t="n">
-        <v>1302</v>
-      </c>
-      <c r="D41" s="21" t="n">
-        <v>1765</v>
-      </c>
-      <c r="E41" s="21" t="n">
-        <v>1028</v>
-      </c>
-      <c r="F41" s="21" t="n">
-        <v>1742</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>Pensionand Other Post Retirement Benefit Plans Current</t>
-        </is>
-      </c>
-      <c r="E42" s="21" t="n">
-        <v>907</v>
-      </c>
-      <c r="F42" s="21" t="n">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>Payables And Accrued Expenses</t>
-        </is>
-      </c>
-      <c r="C43" s="21" t="n">
-        <v>3734</v>
-      </c>
-      <c r="D43" s="21" t="n">
-        <v>2612</v>
-      </c>
-      <c r="E43" s="21" t="n">
-        <v>3036</v>
-      </c>
-      <c r="F43" s="21" t="n">
-        <v>3374</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>Current Accrued Expenses</t>
-        </is>
-      </c>
-      <c r="B44" s="21" t="n">
-        <v>737</v>
-      </c>
-      <c r="C44" s="21" t="n">
-        <v>906</v>
-      </c>
-      <c r="E44" s="21" t="n">
-        <v>435</v>
-      </c>
-      <c r="F44" s="21" t="n">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>Interest Payable</t>
-        </is>
-      </c>
-      <c r="E45" s="21" t="n">
-        <v>435</v>
-      </c>
-      <c r="F45" s="21" t="n">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>Payables</t>
-        </is>
-      </c>
-      <c r="B46" s="21" t="n">
-        <v>1888</v>
-      </c>
-      <c r="C46" s="21" t="n">
-        <v>2828</v>
-      </c>
-      <c r="E46" s="21" t="n">
-        <v>2601</v>
-      </c>
-      <c r="F46" s="21" t="n">
-        <v>3059</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>Dueto Related Parties Current</t>
-        </is>
-      </c>
-      <c r="B47" s="21" t="n">
-        <v>131</v>
-      </c>
-      <c r="C47" s="21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>Total Tax Payable</t>
-        </is>
-      </c>
-      <c r="E48" s="21" t="n">
-        <v>232</v>
-      </c>
-      <c r="F48" s="21" t="n">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>Accounts Payable</t>
-        </is>
-      </c>
-      <c r="B49" s="21" t="n">
-        <v>1757</v>
-      </c>
-      <c r="C49" s="21" t="n">
-        <v>2828</v>
-      </c>
-      <c r="E49" s="21" t="n">
-        <v>2369</v>
-      </c>
-      <c r="F49" s="21" t="n">
-        <v>2813</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>Total Assets</t>
-        </is>
-      </c>
-      <c r="C50" s="21" t="n">
-        <v>46909</v>
-      </c>
-      <c r="D50" s="21" t="n">
-        <v>50758</v>
-      </c>
-      <c r="E50" s="21" t="n">
-        <v>52926</v>
-      </c>
-      <c r="F50" s="21" t="n">
-        <v>57249</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>Total Non Current Assets</t>
-        </is>
-      </c>
-      <c r="C51" s="21" t="n">
-        <v>37549</v>
-      </c>
-      <c r="D51" s="21" t="n">
-        <v>42459</v>
-      </c>
-      <c r="E51" s="21" t="n">
-        <v>42150</v>
-      </c>
-      <c r="F51" s="21" t="n">
-        <v>45130</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>Other Non Current Assets</t>
-        </is>
-      </c>
-      <c r="C52" s="21" t="n">
-        <v>16173</v>
-      </c>
-      <c r="D52" s="21" t="n">
-        <v>18308</v>
-      </c>
-      <c r="E52" s="21" t="n">
-        <v>19483</v>
-      </c>
-      <c r="F52" s="21" t="n">
-        <v>21479</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>Defined Pension Benefit</t>
-        </is>
-      </c>
-      <c r="B53" s="21" t="n">
-        <v>1683</v>
-      </c>
-      <c r="C53" s="21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>Non Current Deferred Assets</t>
-        </is>
-      </c>
-      <c r="B54" s="21" t="n">
-        <v>32</v>
-      </c>
-      <c r="C54" s="21" t="n">
-        <v>44</v>
-      </c>
-      <c r="D54" s="21" t="n">
-        <v>52</v>
-      </c>
-      <c r="E54" s="21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>Non Current Deferred Taxes Assets</t>
-        </is>
-      </c>
-      <c r="B55" s="21" t="n">
-        <v>32</v>
-      </c>
-      <c r="C55" s="21" t="n">
-        <v>44</v>
-      </c>
-      <c r="D55" s="21" t="n">
-        <v>52</v>
-      </c>
-      <c r="E55" s="21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>Financial Assets</t>
-        </is>
-      </c>
-      <c r="C56" s="21" t="n">
-        <v>1261</v>
-      </c>
-      <c r="D56" s="21" t="n">
-        <v>995</v>
-      </c>
-      <c r="E56" s="21" t="n">
-        <v>372</v>
-      </c>
-      <c r="F56" s="21" t="n">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>Investments And Advances</t>
-        </is>
-      </c>
-      <c r="C57" s="21" t="n">
-        <v>202</v>
-      </c>
-      <c r="D57" s="21" t="n">
-        <v>563</v>
-      </c>
-      <c r="E57" s="21" t="n">
-        <v>640</v>
-      </c>
-      <c r="F57" s="21" t="n">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>Other Investments</t>
-        </is>
-      </c>
-      <c r="C58" s="21" t="n">
-        <v>68</v>
-      </c>
-      <c r="D58" s="21" t="n">
-        <v>82</v>
-      </c>
-      <c r="E58" s="21" t="n">
-        <v>100</v>
-      </c>
-      <c r="F58" s="21" t="n">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>Investmentin Financial Assets</t>
-        </is>
-      </c>
-      <c r="C59" s="21" t="n">
-        <v>52</v>
-      </c>
-      <c r="D59" s="21" t="n">
-        <v>474</v>
-      </c>
-      <c r="E59" s="21" t="n">
-        <v>538</v>
-      </c>
-      <c r="F59" s="21" t="n">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t>Available For Sale Securities</t>
-        </is>
-      </c>
-      <c r="C60" s="21" t="n">
-        <v>52</v>
-      </c>
-      <c r="D60" s="21" t="n">
-        <v>474</v>
-      </c>
-      <c r="E60" s="21" t="n">
-        <v>538</v>
-      </c>
-      <c r="F60" s="21" t="n">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>Long Term Equity Investment</t>
-        </is>
-      </c>
-      <c r="C61" s="21" t="n">
-        <v>82</v>
-      </c>
-      <c r="D61" s="21" t="n">
-        <v>7</v>
-      </c>
-      <c r="E61" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="F61" s="21" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t>Goodwill And Other Intangible Assets</t>
-        </is>
-      </c>
-      <c r="C62" s="21" t="n">
-        <v>47</v>
-      </c>
-      <c r="D62" s="21" t="n">
-        <v>425</v>
-      </c>
-      <c r="E62" s="21" t="n">
-        <v>420</v>
-      </c>
-      <c r="F62" s="21" t="n">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="3" t="inlineStr">
-        <is>
-          <t>Goodwill</t>
-        </is>
-      </c>
-      <c r="C63" s="21" t="n">
-        <v>47</v>
-      </c>
-      <c r="D63" s="21" t="n">
-        <v>425</v>
-      </c>
-      <c r="E63" s="21" t="n">
-        <v>420</v>
-      </c>
-      <c r="F63" s="21" t="n">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t>Net PPE</t>
-        </is>
-      </c>
-      <c r="C64" s="21" t="n">
-        <v>19822</v>
-      </c>
-      <c r="D64" s="21" t="n">
-        <v>22116</v>
-      </c>
-      <c r="E64" s="21" t="n">
-        <v>21235</v>
-      </c>
-      <c r="F64" s="21" t="n">
-        <v>22474</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="3" t="inlineStr">
-        <is>
-          <t>Accumulated Depreciation</t>
-        </is>
-      </c>
-      <c r="C65" s="21" t="n">
-        <v>-16726</v>
-      </c>
-      <c r="D65" s="21" t="n">
-        <v>-17423</v>
-      </c>
-      <c r="E65" s="21" t="n">
-        <v>-18088</v>
-      </c>
-      <c r="F65" s="21" t="n">
-        <v>-19072</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="inlineStr">
-        <is>
-          <t>Gross PPE</t>
-        </is>
-      </c>
-      <c r="C66" s="21" t="n">
-        <v>36548</v>
-      </c>
-      <c r="D66" s="21" t="n">
-        <v>39539</v>
-      </c>
-      <c r="E66" s="21" t="n">
-        <v>39323</v>
-      </c>
-      <c r="F66" s="21" t="n">
-        <v>41546</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t>Construction In Progress</t>
-        </is>
-      </c>
-      <c r="C67" s="21" t="n">
-        <v>630</v>
-      </c>
-      <c r="D67" s="21" t="n">
-        <v>1133</v>
-      </c>
-      <c r="E67" s="21" t="n">
-        <v>1273</v>
-      </c>
-      <c r="F67" s="21" t="n">
-        <v>1995</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="inlineStr">
-        <is>
-          <t>Other Properties</t>
-        </is>
-      </c>
-      <c r="B68" s="21" t="n">
-        <v>10</v>
-      </c>
-      <c r="C68" s="21" t="n">
-        <v>8</v>
-      </c>
-      <c r="D68" s="21" t="n">
-        <v>14</v>
-      </c>
-      <c r="E68" s="21" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t>Properties</t>
-        </is>
-      </c>
-      <c r="B69" s="21" t="n">
-        <v>35076</v>
-      </c>
-      <c r="C69" s="21" t="n">
-        <v>35910</v>
-      </c>
-      <c r="D69" s="21" t="n">
-        <v>38392</v>
-      </c>
-      <c r="E69" s="21" t="n">
-        <v>38035</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="3" t="inlineStr">
-        <is>
-          <t>Current Assets</t>
-        </is>
-      </c>
-      <c r="C70" s="21" t="n">
-        <v>9360</v>
-      </c>
-      <c r="D70" s="21" t="n">
-        <v>8299</v>
-      </c>
-      <c r="E70" s="21" t="n">
-        <v>10776</v>
-      </c>
-      <c r="F70" s="21" t="n">
-        <v>12119</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="3" t="inlineStr">
-        <is>
-          <t>Other Current Assets</t>
-        </is>
-      </c>
-      <c r="C71" s="21" t="n">
-        <v>1643</v>
-      </c>
-      <c r="D71" s="21" t="n">
-        <v>2315</v>
-      </c>
-      <c r="E71" s="21" t="n">
-        <v>1486</v>
-      </c>
-      <c r="F71" s="21" t="n">
-        <v>1424</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="3" t="inlineStr">
-        <is>
-          <t>Hedging Assets Current</t>
-        </is>
-      </c>
-      <c r="C72" s="21" t="n">
-        <v>2368</v>
-      </c>
-      <c r="D72" s="21" t="n">
-        <v>1179</v>
-      </c>
-      <c r="E72" s="21" t="n">
-        <v>843</v>
-      </c>
-      <c r="F72" s="21" t="n">
-        <v>945</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="inlineStr">
-        <is>
-          <t>Assets Held For Sale Current</t>
-        </is>
-      </c>
-      <c r="B73" s="21" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="3" t="inlineStr">
-        <is>
-          <t>Restricted Cash</t>
-        </is>
-      </c>
-      <c r="C74" s="21" t="n">
-        <v>106</v>
-      </c>
-      <c r="D74" s="21" t="n">
-        <v>86</v>
-      </c>
-      <c r="E74" s="21" t="n">
-        <v>107</v>
-      </c>
-      <c r="F74" s="21" t="n">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="3" t="inlineStr">
-        <is>
-          <t>Inventory</t>
-        </is>
-      </c>
-      <c r="C75" s="21" t="n">
-        <v>1505</v>
-      </c>
-      <c r="D75" s="21" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E75" s="21" t="n">
-        <v>1600</v>
-      </c>
-      <c r="F75" s="21" t="n">
-        <v>1736</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="3" t="inlineStr">
-        <is>
-          <t>Raw Materials</t>
-        </is>
-      </c>
-      <c r="B76" s="21" t="n">
-        <v>1288</v>
-      </c>
-      <c r="C76" s="21" t="n">
-        <v>1505</v>
-      </c>
-      <c r="D76" s="21" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E76" s="21" t="n">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="3" t="inlineStr">
-        <is>
-          <t>Receivables</t>
-        </is>
-      </c>
-      <c r="C77" s="21" t="n">
-        <v>3316</v>
-      </c>
-      <c r="D77" s="21" t="n">
-        <v>2851</v>
-      </c>
-      <c r="E77" s="21" t="n">
-        <v>3718</v>
-      </c>
-      <c r="F77" s="21" t="n">
-        <v>4266</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="3" t="inlineStr">
-        <is>
-          <t>Other Receivables</t>
-        </is>
-      </c>
-      <c r="C78" s="21" t="n">
-        <v>731</v>
-      </c>
-      <c r="D78" s="21" t="n">
-        <v>917</v>
-      </c>
-      <c r="E78" s="21" t="n">
-        <v>602</v>
-      </c>
-      <c r="F78" s="21" t="n">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="3" t="inlineStr">
-        <is>
-          <t>Duefrom Related Parties Current</t>
-        </is>
-      </c>
-      <c r="B79" s="21" t="n">
-        <v>160</v>
-      </c>
-      <c r="C79" s="21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="3" t="inlineStr">
-        <is>
-          <t>Accounts Receivable</t>
-        </is>
-      </c>
-      <c r="C80" s="21" t="n">
-        <v>2585</v>
-      </c>
-      <c r="D80" s="21" t="n">
-        <v>1934</v>
-      </c>
-      <c r="E80" s="21" t="n">
-        <v>3116</v>
-      </c>
-      <c r="F80" s="21" t="n">
-        <v>3577</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="3" t="inlineStr">
-        <is>
-          <t>Allowance For Doubtful Accounts Receivable</t>
-        </is>
-      </c>
-      <c r="C81" s="21" t="n">
-        <v>-46</v>
-      </c>
-      <c r="D81" s="21" t="n">
-        <v>-56</v>
-      </c>
-      <c r="E81" s="21" t="n">
-        <v>-190</v>
-      </c>
-      <c r="F81" s="21" t="n">
-        <v>-158</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="3" t="inlineStr">
-        <is>
-          <t>Gross Accounts Receivable</t>
-        </is>
-      </c>
-      <c r="C82" s="21" t="n">
-        <v>2631</v>
-      </c>
-      <c r="D82" s="21" t="n">
-        <v>1990</v>
-      </c>
-      <c r="E82" s="21" t="n">
-        <v>3306</v>
-      </c>
-      <c r="F82" s="21" t="n">
-        <v>3735</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="3" t="inlineStr">
-        <is>
-          <t>Cash Cash Equivalents And Short Term Investments</t>
-        </is>
-      </c>
-      <c r="C83" s="21" t="n">
-        <v>422</v>
-      </c>
-      <c r="D83" s="21" t="n">
-        <v>368</v>
-      </c>
-      <c r="E83" s="21" t="n">
-        <v>3022</v>
-      </c>
-      <c r="F83" s="21" t="n">
-        <v>3641</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="3" t="inlineStr">
-        <is>
-          <t>Cash And Cash Equivalents</t>
-        </is>
-      </c>
-      <c r="C84" s="21" t="n">
-        <v>422</v>
-      </c>
-      <c r="D84" s="21" t="n">
-        <v>368</v>
-      </c>
-      <c r="E84" s="21" t="n">
-        <v>3022</v>
-      </c>
-      <c r="F84" s="21" t="n">
-        <v>3641</v>
       </c>
     </row>
   </sheetData>

--- a/docs/reports/CEG.xlsx
+++ b/docs/reports/CEG.xlsx
@@ -161,10 +161,10 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="11" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>141.4355573432792</v>
+        <v>169.3480035875697</v>
       </c>
     </row>
     <row r="8">
@@ -3364,34 +3364,34 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>35617.88948</v>
-      </c>
-      <c r="C5" s="13" t="n">
-        <v>36686.4261644</v>
-      </c>
-      <c r="D5" s="13" t="n">
-        <v>37787.018949332</v>
-      </c>
-      <c r="E5" s="13" t="n">
-        <v>38920.62951781196</v>
-      </c>
-      <c r="F5" s="13" t="n">
-        <v>40088.24840334632</v>
-      </c>
-      <c r="G5" s="13" t="n">
-        <v>41290.89585544671</v>
-      </c>
-      <c r="H5" s="13" t="n">
-        <v>42529.62273111011</v>
-      </c>
-      <c r="I5" s="13" t="n">
-        <v>43805.51141304341</v>
-      </c>
-      <c r="J5" s="13" t="n">
-        <v>45119.67675543472</v>
-      </c>
-      <c r="K5" s="13" t="n">
-        <v>46473.26705809776</v>
+        <v>26298.99</v>
+      </c>
+      <c r="C5" s="12" t="n">
+        <v>27087.9597</v>
+      </c>
+      <c r="D5" s="12" t="n">
+        <v>27900.598491</v>
+      </c>
+      <c r="E5" s="12" t="n">
+        <v>28737.61644573</v>
+      </c>
+      <c r="F5" s="12" t="n">
+        <v>29599.7449391019</v>
+      </c>
+      <c r="G5" s="12" t="n">
+        <v>30487.73728727496</v>
+      </c>
+      <c r="H5" s="12" t="n">
+        <v>31402.36940589321</v>
+      </c>
+      <c r="I5" s="12" t="n">
+        <v>32344.44048807</v>
+      </c>
+      <c r="J5" s="12" t="n">
+        <v>33314.7737027121</v>
+      </c>
+      <c r="K5" s="12" t="n">
+        <v>34314.21691379347</v>
       </c>
     </row>
     <row r="6">
@@ -3405,39 +3405,39 @@
           <t>—</t>
         </is>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="13">
         <f>C5/B5-1</f>
         <v/>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="13">
         <f>D5/C5-1</f>
         <v/>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="13">
         <f>E5/D5-1</f>
         <v/>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="13">
         <f>F5/E5-1</f>
         <v/>
       </c>
-      <c r="G6" s="14">
+      <c r="G6" s="13">
         <f>G5/F5-1</f>
         <v/>
       </c>
-      <c r="H6" s="14">
+      <c r="H6" s="13">
         <f>H5/G5-1</f>
         <v/>
       </c>
-      <c r="I6" s="14">
+      <c r="I6" s="13">
         <f>I5/H5-1</f>
         <v/>
       </c>
-      <c r="J6" s="14">
+      <c r="J6" s="13">
         <f>J5/I5-1</f>
         <v/>
       </c>
-      <c r="K6" s="14">
+      <c r="K6" s="13">
         <f>K5/J5-1</f>
         <v/>
       </c>
@@ -3448,34 +3448,34 @@
           <t>EBIT margin</t>
         </is>
       </c>
-      <c r="B7" s="15" t="n">
+      <c r="B7" s="14" t="n">
         <v>0.1644146790428073</v>
       </c>
-      <c r="C7" s="15" t="n">
+      <c r="C7" s="14" t="n">
         <v>0.1644146790428073</v>
       </c>
-      <c r="D7" s="15" t="n">
+      <c r="D7" s="14" t="n">
         <v>0.1644146790428073</v>
       </c>
-      <c r="E7" s="15" t="n">
+      <c r="E7" s="14" t="n">
         <v>0.1644146790428073</v>
       </c>
-      <c r="F7" s="15" t="n">
+      <c r="F7" s="14" t="n">
         <v>0.1644146790428073</v>
       </c>
-      <c r="G7" s="15" t="n">
+      <c r="G7" s="14" t="n">
         <v>0.1644146790428073</v>
       </c>
-      <c r="H7" s="15" t="n">
+      <c r="H7" s="14" t="n">
         <v>0.1644146790428073</v>
       </c>
-      <c r="I7" s="15" t="n">
+      <c r="I7" s="14" t="n">
         <v>0.1644146790428073</v>
       </c>
-      <c r="J7" s="15" t="n">
+      <c r="J7" s="14" t="n">
         <v>0.1644146790428073</v>
       </c>
-      <c r="K7" s="15" t="n">
+      <c r="K7" s="14" t="n">
         <v>0.1644146790428073</v>
       </c>
     </row>
@@ -3485,43 +3485,43 @@
           <t>EBIT (mn)</t>
         </is>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="12">
         <f>B5*B7</f>
         <v/>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="12">
         <f>C5*C7</f>
         <v/>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="12">
         <f>D5*D7</f>
         <v/>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="12">
         <f>E5*E7</f>
         <v/>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="12">
         <f>F5*F7</f>
         <v/>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="12">
         <f>G5*G7</f>
         <v/>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="12">
         <f>H5*H7</f>
         <v/>
       </c>
-      <c r="I8" s="13">
+      <c r="I8" s="12">
         <f>I5*I7</f>
         <v/>
       </c>
-      <c r="J8" s="13">
+      <c r="J8" s="12">
         <f>J5*J7</f>
         <v/>
       </c>
-      <c r="K8" s="13">
+      <c r="K8" s="12">
         <f>K5*K7</f>
         <v/>
       </c>
@@ -3532,35 +3532,35 @@
           <t>Net income (mn)</t>
         </is>
       </c>
-      <c r="B9" s="12" t="n">
+      <c r="B9" s="15" t="n">
         <v>4850.52740997151</v>
       </c>
-      <c r="C9" s="13" t="n">
-        <v>3331.994762669628</v>
-      </c>
-      <c r="D9" s="13" t="n">
-        <v>3431.954605549717</v>
-      </c>
-      <c r="E9" s="13" t="n">
-        <v>3534.913243716208</v>
-      </c>
-      <c r="F9" s="13" t="n">
-        <v>3640.960641027694</v>
-      </c>
-      <c r="G9" s="13" t="n">
-        <v>3750.189460258525</v>
-      </c>
-      <c r="H9" s="13" t="n">
-        <v>3862.695144066281</v>
-      </c>
-      <c r="I9" s="13" t="n">
-        <v>3978.575998388269</v>
-      </c>
-      <c r="J9" s="13" t="n">
-        <v>4097.933278339917</v>
-      </c>
-      <c r="K9" s="13" t="n">
-        <v>4220.871276690114</v>
+      <c r="C9" s="12" t="n">
+        <v>2460.2271</v>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>2534.033913</v>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>2610.05493039</v>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>2688.3565783017</v>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>2769.007275650751</v>
+      </c>
+      <c r="H9" s="12" t="n">
+        <v>2852.077493920274</v>
+      </c>
+      <c r="I9" s="12" t="n">
+        <v>2937.639818737882</v>
+      </c>
+      <c r="J9" s="12" t="n">
+        <v>3025.769013300018</v>
+      </c>
+      <c r="K9" s="12" t="n">
+        <v>3116.542083699019</v>
       </c>
     </row>
     <row r="10">
@@ -3617,34 +3617,34 @@
         </is>
       </c>
       <c r="B12" s="17" t="n">
-        <v>1493.3072</v>
+        <v>2694.040234602546</v>
       </c>
       <c r="C12" s="17" t="n">
-        <v>1710.699543715556</v>
+        <v>2788.331642813635</v>
       </c>
       <c r="D12" s="17" t="n">
-        <v>1936.093712486434</v>
+        <v>2885.923250312112</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>2164.423697645668</v>
+        <v>2986.930564073036</v>
       </c>
       <c r="F12" s="17" t="n">
-        <v>2389.764253722778</v>
+        <v>3091.473133815592</v>
       </c>
       <c r="G12" s="17" t="n">
-        <v>2605.533412897792</v>
+        <v>3199.674693499138</v>
       </c>
       <c r="H12" s="17" t="n">
-        <v>2804.76986787071</v>
+        <v>3311.663307771607</v>
       </c>
       <c r="I12" s="17" t="n">
-        <v>2980.473118037989</v>
+        <v>3427.571523543613</v>
       </c>
       <c r="J12" s="17" t="n">
-        <v>3125.986438934199</v>
+        <v>3547.53652686764</v>
       </c>
       <c r="K12" s="17" t="n">
-        <v>3235.395964296896</v>
+        <v>3671.700305308007</v>
       </c>
     </row>
     <row r="13">
@@ -3653,43 +3653,43 @@
           <t>FCF margin</t>
         </is>
       </c>
-      <c r="B13" s="14">
+      <c r="B13" s="13">
         <f>B12/B5</f>
         <v/>
       </c>
-      <c r="C13" s="14">
+      <c r="C13" s="13">
         <f>C12/C5</f>
         <v/>
       </c>
-      <c r="D13" s="14">
+      <c r="D13" s="13">
         <f>D12/D5</f>
         <v/>
       </c>
-      <c r="E13" s="14">
+      <c r="E13" s="13">
         <f>E12/E5</f>
         <v/>
       </c>
-      <c r="F13" s="14">
+      <c r="F13" s="13">
         <f>F12/F5</f>
         <v/>
       </c>
-      <c r="G13" s="14">
+      <c r="G13" s="13">
         <f>G12/G5</f>
         <v/>
       </c>
-      <c r="H13" s="14">
+      <c r="H13" s="13">
         <f>H12/H5</f>
         <v/>
       </c>
-      <c r="I13" s="14">
+      <c r="I13" s="13">
         <f>I12/I5</f>
         <v/>
       </c>
-      <c r="J13" s="14">
+      <c r="J13" s="13">
         <f>J12/J5</f>
         <v/>
       </c>
-      <c r="K13" s="14">
+      <c r="K13" s="13">
         <f>K12/K5</f>
         <v/>
       </c>
@@ -3800,7 +3800,7 @@
           <t>Shares outstanding (mn)</t>
         </is>
       </c>
-      <c r="B11" s="12" t="n">
+      <c r="B11" s="15" t="n">
         <v>357.102017</v>
       </c>
     </row>
@@ -3842,8 +3842,8 @@
       <c r="A15" s="21" t="n">
         <v>2026</v>
       </c>
-      <c r="B15" s="12" t="n">
-        <v>1493.3072</v>
+      <c r="B15" s="15" t="n">
+        <v>2694.040234602546</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <f>1/(1+$B$8)^1</f>
         <v/>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="12">
         <f>B15*D15</f>
         <v/>
       </c>
@@ -3863,8 +3863,8 @@
       <c r="A16" s="21" t="n">
         <v>2027</v>
       </c>
-      <c r="B16" s="12" t="n">
-        <v>1710.699543715556</v>
+      <c r="B16" s="15" t="n">
+        <v>2788.331642813635</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <f>1/(1+$B$8)^2</f>
         <v/>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="12">
         <f>B16*D16</f>
         <v/>
       </c>
@@ -3884,8 +3884,8 @@
       <c r="A17" s="21" t="n">
         <v>2028</v>
       </c>
-      <c r="B17" s="12" t="n">
-        <v>1936.093712486434</v>
+      <c r="B17" s="15" t="n">
+        <v>2885.923250312112</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <f>1/(1+$B$8)^3</f>
         <v/>
       </c>
-      <c r="E17" s="13">
+      <c r="E17" s="12">
         <f>B17*D17</f>
         <v/>
       </c>
@@ -3905,8 +3905,8 @@
       <c r="A18" s="21" t="n">
         <v>2029</v>
       </c>
-      <c r="B18" s="12" t="n">
-        <v>2164.423697645668</v>
+      <c r="B18" s="15" t="n">
+        <v>2986.930564073036</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <f>1/(1+$B$8)^4</f>
         <v/>
       </c>
-      <c r="E18" s="13">
+      <c r="E18" s="12">
         <f>B18*D18</f>
         <v/>
       </c>
@@ -3926,8 +3926,8 @@
       <c r="A19" s="21" t="n">
         <v>2030</v>
       </c>
-      <c r="B19" s="12" t="n">
-        <v>2389.764253722778</v>
+      <c r="B19" s="15" t="n">
+        <v>3091.473133815592</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <f>1/(1+$B$8)^5</f>
         <v/>
       </c>
-      <c r="E19" s="13">
+      <c r="E19" s="12">
         <f>B19*D19</f>
         <v/>
       </c>
@@ -3947,8 +3947,8 @@
       <c r="A20" s="21" t="n">
         <v>2031</v>
       </c>
-      <c r="B20" s="12" t="n">
-        <v>2605.533412897792</v>
+      <c r="B20" s="15" t="n">
+        <v>3199.674693499138</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <f>1/(1+$B$8)^6</f>
         <v/>
       </c>
-      <c r="E20" s="13">
+      <c r="E20" s="12">
         <f>B20*D20</f>
         <v/>
       </c>
@@ -3968,8 +3968,8 @@
       <c r="A21" s="21" t="n">
         <v>2032</v>
       </c>
-      <c r="B21" s="12" t="n">
-        <v>2804.76986787071</v>
+      <c r="B21" s="15" t="n">
+        <v>3311.663307771607</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         <f>1/(1+$B$8)^7</f>
         <v/>
       </c>
-      <c r="E21" s="13">
+      <c r="E21" s="12">
         <f>B21*D21</f>
         <v/>
       </c>
@@ -3989,8 +3989,8 @@
       <c r="A22" s="21" t="n">
         <v>2033</v>
       </c>
-      <c r="B22" s="12" t="n">
-        <v>2980.473118037989</v>
+      <c r="B22" s="15" t="n">
+        <v>3427.571523543613</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <f>1/(1+$B$8)^8</f>
         <v/>
       </c>
-      <c r="E22" s="13">
+      <c r="E22" s="12">
         <f>B22*D22</f>
         <v/>
       </c>
@@ -4010,8 +4010,8 @@
       <c r="A23" s="21" t="n">
         <v>2034</v>
       </c>
-      <c r="B23" s="12" t="n">
-        <v>3125.986438934199</v>
+      <c r="B23" s="15" t="n">
+        <v>3547.53652686764</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <f>1/(1+$B$8)^9</f>
         <v/>
       </c>
-      <c r="E23" s="13">
+      <c r="E23" s="12">
         <f>B23*D23</f>
         <v/>
       </c>
@@ -4031,8 +4031,8 @@
       <c r="A24" s="21" t="n">
         <v>2035</v>
       </c>
-      <c r="B24" s="12" t="n">
-        <v>3235.395964296896</v>
+      <c r="B24" s="15" t="n">
+        <v>3671.700305308007</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <f>1/(1+$B$8)^10</f>
         <v/>
       </c>
-      <c r="E24" s="13">
+      <c r="E24" s="12">
         <f>B24*D24</f>
         <v/>
       </c>
@@ -4072,7 +4072,7 @@
           <t>Terminal value = CFn·(1+g)/(Ke−g)</t>
         </is>
       </c>
-      <c r="B28" s="13">
+      <c r="B28" s="12">
         <f>B24*(1+$B$10)/($B$8-$B$10)</f>
         <v/>
       </c>
@@ -4083,7 +4083,7 @@
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="B29" s="13">
+      <c r="B29" s="12">
         <f>$B$28/(1+$B$8)^10</f>
         <v/>
       </c>
@@ -4117,7 +4117,7 @@
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>242.1</v>
+        <v>244.52</v>
       </c>
     </row>
     <row r="34">
@@ -4126,7 +4126,7 @@
           <t>Upside / (downside)</t>
         </is>
       </c>
-      <c r="B34" s="14">
+      <c r="B34" s="13">
         <f>B32/$B$33-1</f>
         <v/>
       </c>
@@ -4186,7 +4186,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>242.1</v>
+        <v>244.52</v>
       </c>
     </row>
     <row r="6">
@@ -4195,7 +4195,7 @@
           <t>Diluted shares (mn)</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n">
+      <c r="B6" s="15" t="n">
         <v>357.102017</v>
       </c>
     </row>
@@ -4205,7 +4205,7 @@
           <t>Total debt (USDmm)</t>
         </is>
       </c>
-      <c r="B7" s="12" t="n">
+      <c r="B7" s="15" t="n">
         <v>8992</v>
       </c>
     </row>
@@ -4215,7 +4215,7 @@
           <t>Cash &amp; ST investments (USDmm)</t>
         </is>
       </c>
-      <c r="B8" s="12" t="n">
+      <c r="B8" s="15" t="n">
         <v>3641</v>
       </c>
     </row>
@@ -4225,7 +4225,7 @@
           <t>Minority interest (USDmm)</t>
         </is>
       </c>
-      <c r="B9" s="12" t="n">
+      <c r="B9" s="15" t="n">
         <v>336</v>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
           <t>Net debt (USDmm)</t>
         </is>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="12">
         <f>Assumptions!$B$7-Assumptions!$B$8</f>
         <v/>
       </c>
@@ -4313,7 +4313,7 @@
           <t>Tax rate</t>
         </is>
       </c>
-      <c r="B19" s="15" t="n">
+      <c r="B19" s="14" t="n">
         <v>0.286837674171915</v>
       </c>
     </row>
@@ -4379,19 +4379,19 @@
           <t>Revenue growth</t>
         </is>
       </c>
-      <c r="B26" s="15" t="n">
+      <c r="B26" s="14" t="n">
         <v>0.01469039149633189</v>
       </c>
-      <c r="C26" s="15" t="n">
+      <c r="C26" s="14" t="n">
         <v>0.01594039149633189</v>
       </c>
-      <c r="D26" s="15" t="n">
+      <c r="D26" s="14" t="n">
         <v>0.01719039149633189</v>
       </c>
-      <c r="E26" s="15" t="n">
+      <c r="E26" s="14" t="n">
         <v>0.01844039149633189</v>
       </c>
-      <c r="F26" s="15" t="n">
+      <c r="F26" s="14" t="n">
         <v>0.01969039149633189</v>
       </c>
     </row>
@@ -4401,19 +4401,19 @@
           <t>EBIT margin</t>
         </is>
       </c>
-      <c r="B27" s="15" t="n">
+      <c r="B27" s="14" t="n">
         <v>0.1644146790428073</v>
       </c>
-      <c r="C27" s="15" t="n">
+      <c r="C27" s="14" t="n">
         <v>0.1592026475312204</v>
       </c>
-      <c r="D27" s="15" t="n">
+      <c r="D27" s="14" t="n">
         <v>0.1539906160196335</v>
       </c>
-      <c r="E27" s="15" t="n">
+      <c r="E27" s="14" t="n">
         <v>0.1487785845080466</v>
       </c>
-      <c r="F27" s="15" t="n">
+      <c r="F27" s="14" t="n">
         <v>0.1435665529964597</v>
       </c>
     </row>
@@ -4423,19 +4423,19 @@
           <t>D&amp;A % of revenue</t>
         </is>
       </c>
-      <c r="B28" s="15" t="n">
+      <c r="B28" s="14" t="n">
         <v>0.07806074434667941</v>
       </c>
-      <c r="C28" s="15" t="n">
+      <c r="C28" s="14" t="n">
         <v>0.07806074434667941</v>
       </c>
-      <c r="D28" s="15" t="n">
+      <c r="D28" s="14" t="n">
         <v>0.07806074434667941</v>
       </c>
-      <c r="E28" s="15" t="n">
+      <c r="E28" s="14" t="n">
         <v>0.07806074434667941</v>
       </c>
-      <c r="F28" s="15" t="n">
+      <c r="F28" s="14" t="n">
         <v>0.07806074434667941</v>
       </c>
     </row>
@@ -4445,19 +4445,19 @@
           <t>Capex % of revenue</t>
         </is>
       </c>
-      <c r="B29" s="15" t="n">
+      <c r="B29" s="14" t="n">
         <v>0.09765960882899036</v>
       </c>
-      <c r="C29" s="15" t="n">
+      <c r="C29" s="14" t="n">
         <v>0.09765960882899036</v>
       </c>
-      <c r="D29" s="15" t="n">
+      <c r="D29" s="14" t="n">
         <v>0.09765960882899036</v>
       </c>
-      <c r="E29" s="15" t="n">
+      <c r="E29" s="14" t="n">
         <v>0.09765960882899036</v>
       </c>
-      <c r="F29" s="15" t="n">
+      <c r="F29" s="14" t="n">
         <v>0.09765960882899036</v>
       </c>
     </row>
@@ -4467,7 +4467,7 @@
           <t>ΔNWC % of Δrevenue</t>
         </is>
       </c>
-      <c r="B30" s="15" t="n">
+      <c r="B30" s="14" t="n">
         <v>0.00356234096692112</v>
       </c>
     </row>
@@ -4553,7 +4553,7 @@
           <t>Weight of equity</t>
         </is>
       </c>
-      <c r="B8" s="14">
+      <c r="B8" s="13">
         <f>WACC!$B$6/(WACC!$B$6+WACC!$B$7)</f>
         <v/>
       </c>
@@ -4564,7 +4564,7 @@
           <t>Weight of debt</t>
         </is>
       </c>
-      <c r="B9" s="14">
+      <c r="B9" s="13">
         <f>1-WACC!$B$8</f>
         <v/>
       </c>
@@ -4690,23 +4690,23 @@
       <c r="E5" s="29" t="n">
         <v>25533</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="12">
         <f>E5*(1+Assumptions!B$26)</f>
         <v/>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="12">
         <f>F5*(1+Assumptions!C$26)</f>
         <v/>
       </c>
-      <c r="H5" s="13">
+      <c r="H5" s="12">
         <f>G5*(1+Assumptions!D$26)</f>
         <v/>
       </c>
-      <c r="I5" s="13">
+      <c r="I5" s="12">
         <f>H5*(1+Assumptions!E$26)</f>
         <v/>
       </c>
-      <c r="J5" s="13">
+      <c r="J5" s="12">
         <f>I5*(1+Assumptions!F$26)</f>
         <v/>
       </c>
@@ -4729,23 +4729,23 @@
         <f>E5/D5-1</f>
         <v/>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="13">
         <f>F5/E5-1</f>
         <v/>
       </c>
-      <c r="G6" s="14">
+      <c r="G6" s="13">
         <f>G5/F5-1</f>
         <v/>
       </c>
-      <c r="H6" s="14">
+      <c r="H6" s="13">
         <f>H5/G5-1</f>
         <v/>
       </c>
-      <c r="I6" s="14">
+      <c r="I6" s="13">
         <f>I5/H5-1</f>
         <v/>
       </c>
-      <c r="J6" s="14">
+      <c r="J6" s="13">
         <f>J5/I5-1</f>
         <v/>
       </c>
@@ -4768,23 +4768,23 @@
       <c r="E7" s="29" t="n">
         <v>4198</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="12">
         <f>F5*Assumptions!B$27</f>
         <v/>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="12">
         <f>G5*Assumptions!C$27</f>
         <v/>
       </c>
-      <c r="H7" s="13">
+      <c r="H7" s="12">
         <f>H5*Assumptions!D$27</f>
         <v/>
       </c>
-      <c r="I7" s="13">
+      <c r="I7" s="12">
         <f>I5*Assumptions!E$27</f>
         <v/>
       </c>
-      <c r="J7" s="13">
+      <c r="J7" s="12">
         <f>J5*Assumptions!F$27</f>
         <v/>
       </c>
@@ -4811,23 +4811,23 @@
         <f>E7/E5</f>
         <v/>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="13">
         <f>F7/F5</f>
         <v/>
       </c>
-      <c r="G8" s="14">
+      <c r="G8" s="13">
         <f>G7/G5</f>
         <v/>
       </c>
-      <c r="H8" s="14">
+      <c r="H8" s="13">
         <f>H7/H5</f>
         <v/>
       </c>
-      <c r="I8" s="14">
+      <c r="I8" s="13">
         <f>I7/I5</f>
         <v/>
       </c>
-      <c r="J8" s="14">
+      <c r="J8" s="13">
         <f>J7/J5</f>
         <v/>
       </c>
@@ -4850,23 +4850,23 @@
       <c r="E9" s="29" t="n">
         <v>1937</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="12">
         <f>F5*Assumptions!B$28</f>
         <v/>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="12">
         <f>G5*Assumptions!C$28</f>
         <v/>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="12">
         <f>H5*Assumptions!D$28</f>
         <v/>
       </c>
-      <c r="I9" s="13">
+      <c r="I9" s="12">
         <f>I5*Assumptions!E$28</f>
         <v/>
       </c>
-      <c r="J9" s="13">
+      <c r="J9" s="12">
         <f>J5*Assumptions!F$28</f>
         <v/>
       </c>
@@ -4893,23 +4893,23 @@
         <f>E7+E9</f>
         <v/>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="12">
         <f>F7+F9</f>
         <v/>
       </c>
-      <c r="G10" s="13">
+      <c r="G10" s="12">
         <f>G7+G9</f>
         <v/>
       </c>
-      <c r="H10" s="13">
+      <c r="H10" s="12">
         <f>H7+H9</f>
         <v/>
       </c>
-      <c r="I10" s="13">
+      <c r="I10" s="12">
         <f>I7+I9</f>
         <v/>
       </c>
-      <c r="J10" s="13">
+      <c r="J10" s="12">
         <f>J7+J9</f>
         <v/>
       </c>
@@ -4975,23 +4975,23 @@
       <c r="E12" s="29" t="n">
         <v>2949</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="12">
         <f>F5*Assumptions!B$29</f>
         <v/>
       </c>
-      <c r="G12" s="13">
+      <c r="G12" s="12">
         <f>G5*Assumptions!C$29</f>
         <v/>
       </c>
-      <c r="H12" s="13">
+      <c r="H12" s="12">
         <f>H5*Assumptions!D$29</f>
         <v/>
       </c>
-      <c r="I12" s="13">
+      <c r="I12" s="12">
         <f>I5*Assumptions!E$29</f>
         <v/>
       </c>
-      <c r="J12" s="13">
+      <c r="J12" s="12">
         <f>J5*Assumptions!F$29</f>
         <v/>
       </c>
@@ -5014,23 +5014,23 @@
       <c r="E13" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="12">
         <f>(F5-E5)*Assumptions!$B$30</f>
         <v/>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="12">
         <f>(G5-F5)*Assumptions!$B$30</f>
         <v/>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="12">
         <f>(H5-G5)*Assumptions!$B$30</f>
         <v/>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="12">
         <f>(I5-H5)*Assumptions!$B$30</f>
         <v/>
       </c>
-      <c r="J13" s="13">
+      <c r="J13" s="12">
         <f>(J5-I5)*Assumptions!$B$30</f>
         <v/>
       </c>
@@ -5229,23 +5229,23 @@
           <t>PV of FCFF</t>
         </is>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="12">
         <f>B5*B7</f>
         <v/>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="12">
         <f>C5*C7</f>
         <v/>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="12">
         <f>D5*D7</f>
         <v/>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="12">
         <f>E5*E7</f>
         <v/>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="12">
         <f>F5*F7</f>
         <v/>
       </c>
@@ -5256,7 +5256,7 @@
           <t>PV of explicit FCFF</t>
         </is>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="12">
         <f>SUM(B8:F8)</f>
         <v/>
       </c>
@@ -5278,7 +5278,7 @@
           <t>Invested capital (mm)</t>
         </is>
       </c>
-      <c r="B12" s="12" t="n">
+      <c r="B12" s="15" t="n">
         <v>19868</v>
       </c>
     </row>
@@ -5299,7 +5299,7 @@
           <t>Terminal ROIC</t>
         </is>
       </c>
-      <c r="B14" s="14">
+      <c r="B14" s="13">
         <f>MAX($B$11/$B$13,WACC!$B$10)</f>
         <v/>
       </c>
@@ -5321,7 +5321,7 @@
           <t>Terminal value (Gordon)</t>
         </is>
       </c>
-      <c r="B16" s="13">
+      <c r="B16" s="12">
         <f>$B$11*(1+Assumptions!$B$22)*(1-$B$15)/(WACC!$B$10-Assumptions!$B$22)</f>
         <v/>
       </c>
@@ -5332,7 +5332,7 @@
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="B17" s="13">
+      <c r="B17" s="12">
         <f>$B$16/(1+WACC!$B$10)^(5-0.5)</f>
         <v/>
       </c>
@@ -5343,7 +5343,7 @@
           <t>TV as % of EV</t>
         </is>
       </c>
-      <c r="B18" s="14">
+      <c r="B18" s="13">
         <f>$B$17/($B$10+$B$17)</f>
         <v/>
       </c>
@@ -5456,25 +5456,25 @@
           <t>WACC \ g</t>
         </is>
       </c>
-      <c r="B4" s="15" t="n">
+      <c r="B4" s="14" t="n">
         <v>0.015</v>
       </c>
-      <c r="C4" s="15" t="n">
+      <c r="C4" s="14" t="n">
         <v>0.02</v>
       </c>
-      <c r="D4" s="15" t="n">
+      <c r="D4" s="14" t="n">
         <v>0.025</v>
       </c>
-      <c r="E4" s="15" t="n">
+      <c r="E4" s="14" t="n">
         <v>0.03</v>
       </c>
-      <c r="F4" s="15" t="n">
+      <c r="F4" s="14" t="n">
         <v>0.035</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="18" t="n">
-        <v>0.07408347873328337</v>
+        <v>0.07413267267876338</v>
       </c>
       <c r="B5" s="16">
         <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$5)^DCF!$B$6:$F$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$5-B$4)/(1+$A$5)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
@@ -5499,7 +5499,7 @@
     </row>
     <row r="6">
       <c r="A6" s="18" t="n">
-        <v>0.08158347873328337</v>
+        <v>0.08163267267876337</v>
       </c>
       <c r="B6" s="16">
         <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$6)^DCF!$B$6:$F$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$6-B$4)/(1+$A$6)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
@@ -5524,7 +5524,7 @@
     </row>
     <row r="7">
       <c r="A7" s="18" t="n">
-        <v>0.08908347873328337</v>
+        <v>0.08913267267876337</v>
       </c>
       <c r="B7" s="16">
         <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$7)^DCF!$B$6:$F$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$7-B$4)/(1+$A$7)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
@@ -5549,7 +5549,7 @@
     </row>
     <row r="8">
       <c r="A8" s="18" t="n">
-        <v>0.09658347873328338</v>
+        <v>0.09663267267876338</v>
       </c>
       <c r="B8" s="16">
         <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$8)^DCF!$B$6:$F$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$8-B$4)/(1+$A$8)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
@@ -5574,7 +5574,7 @@
     </row>
     <row r="9">
       <c r="A9" s="18" t="n">
-        <v>0.1040834787332834</v>
+        <v>0.1041326726787634</v>
       </c>
       <c r="B9" s="16">
         <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$9)^DCF!$B$6:$F$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$9-B$4)/(1+$A$9)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>

--- a/docs/reports/CEG.xlsx
+++ b/docs/reports/CEG.xlsx
@@ -161,10 +161,10 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="11" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3364,34 +3364,34 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>26298.99</v>
-      </c>
-      <c r="C5" s="12" t="n">
-        <v>27087.9597</v>
-      </c>
-      <c r="D5" s="12" t="n">
-        <v>27900.598491</v>
-      </c>
-      <c r="E5" s="12" t="n">
-        <v>28737.61644573</v>
-      </c>
-      <c r="F5" s="12" t="n">
-        <v>29599.7449391019</v>
-      </c>
-      <c r="G5" s="12" t="n">
-        <v>30487.73728727496</v>
-      </c>
-      <c r="H5" s="12" t="n">
-        <v>31402.36940589321</v>
-      </c>
-      <c r="I5" s="12" t="n">
-        <v>32344.44048807</v>
-      </c>
-      <c r="J5" s="12" t="n">
-        <v>33314.7737027121</v>
-      </c>
-      <c r="K5" s="12" t="n">
-        <v>34314.21691379347</v>
+        <v>35617.88948</v>
+      </c>
+      <c r="C5" s="13" t="n">
+        <v>36686.4261644</v>
+      </c>
+      <c r="D5" s="13" t="n">
+        <v>37787.018949332</v>
+      </c>
+      <c r="E5" s="13" t="n">
+        <v>38920.62951781196</v>
+      </c>
+      <c r="F5" s="13" t="n">
+        <v>40088.24840334632</v>
+      </c>
+      <c r="G5" s="13" t="n">
+        <v>41290.89585544671</v>
+      </c>
+      <c r="H5" s="13" t="n">
+        <v>42529.62273111011</v>
+      </c>
+      <c r="I5" s="13" t="n">
+        <v>43805.51141304341</v>
+      </c>
+      <c r="J5" s="13" t="n">
+        <v>45119.67675543472</v>
+      </c>
+      <c r="K5" s="13" t="n">
+        <v>46473.26705809776</v>
       </c>
     </row>
     <row r="6">
@@ -3405,39 +3405,39 @@
           <t>—</t>
         </is>
       </c>
-      <c r="C6" s="13">
+      <c r="C6" s="14">
         <f>C5/B5-1</f>
         <v/>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="14">
         <f>D5/C5-1</f>
         <v/>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="14">
         <f>E5/D5-1</f>
         <v/>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="14">
         <f>F5/E5-1</f>
         <v/>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="14">
         <f>G5/F5-1</f>
         <v/>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="14">
         <f>H5/G5-1</f>
         <v/>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="14">
         <f>I5/H5-1</f>
         <v/>
       </c>
-      <c r="J6" s="13">
+      <c r="J6" s="14">
         <f>J5/I5-1</f>
         <v/>
       </c>
-      <c r="K6" s="13">
+      <c r="K6" s="14">
         <f>K5/J5-1</f>
         <v/>
       </c>
@@ -3448,34 +3448,34 @@
           <t>EBIT margin</t>
         </is>
       </c>
-      <c r="B7" s="14" t="n">
+      <c r="B7" s="15" t="n">
         <v>0.1644146790428073</v>
       </c>
-      <c r="C7" s="14" t="n">
+      <c r="C7" s="15" t="n">
         <v>0.1644146790428073</v>
       </c>
-      <c r="D7" s="14" t="n">
+      <c r="D7" s="15" t="n">
         <v>0.1644146790428073</v>
       </c>
-      <c r="E7" s="14" t="n">
+      <c r="E7" s="15" t="n">
         <v>0.1644146790428073</v>
       </c>
-      <c r="F7" s="14" t="n">
+      <c r="F7" s="15" t="n">
         <v>0.1644146790428073</v>
       </c>
-      <c r="G7" s="14" t="n">
+      <c r="G7" s="15" t="n">
         <v>0.1644146790428073</v>
       </c>
-      <c r="H7" s="14" t="n">
+      <c r="H7" s="15" t="n">
         <v>0.1644146790428073</v>
       </c>
-      <c r="I7" s="14" t="n">
+      <c r="I7" s="15" t="n">
         <v>0.1644146790428073</v>
       </c>
-      <c r="J7" s="14" t="n">
+      <c r="J7" s="15" t="n">
         <v>0.1644146790428073</v>
       </c>
-      <c r="K7" s="14" t="n">
+      <c r="K7" s="15" t="n">
         <v>0.1644146790428073</v>
       </c>
     </row>
@@ -3485,43 +3485,43 @@
           <t>EBIT (mn)</t>
         </is>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="13">
         <f>B5*B7</f>
         <v/>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="13">
         <f>C5*C7</f>
         <v/>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="13">
         <f>D5*D7</f>
         <v/>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="13">
         <f>E5*E7</f>
         <v/>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="13">
         <f>F5*F7</f>
         <v/>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="13">
         <f>G5*G7</f>
         <v/>
       </c>
-      <c r="H8" s="12">
+      <c r="H8" s="13">
         <f>H5*H7</f>
         <v/>
       </c>
-      <c r="I8" s="12">
+      <c r="I8" s="13">
         <f>I5*I7</f>
         <v/>
       </c>
-      <c r="J8" s="12">
+      <c r="J8" s="13">
         <f>J5*J7</f>
         <v/>
       </c>
-      <c r="K8" s="12">
+      <c r="K8" s="13">
         <f>K5*K7</f>
         <v/>
       </c>
@@ -3532,35 +3532,35 @@
           <t>Net income (mn)</t>
         </is>
       </c>
-      <c r="B9" s="15" t="n">
+      <c r="B9" s="12" t="n">
         <v>4850.52740997151</v>
       </c>
-      <c r="C9" s="12" t="n">
-        <v>2460.2271</v>
-      </c>
-      <c r="D9" s="12" t="n">
-        <v>2534.033913</v>
-      </c>
-      <c r="E9" s="12" t="n">
-        <v>2610.05493039</v>
-      </c>
-      <c r="F9" s="12" t="n">
-        <v>2688.3565783017</v>
-      </c>
-      <c r="G9" s="12" t="n">
-        <v>2769.007275650751</v>
-      </c>
-      <c r="H9" s="12" t="n">
-        <v>2852.077493920274</v>
-      </c>
-      <c r="I9" s="12" t="n">
-        <v>2937.639818737882</v>
-      </c>
-      <c r="J9" s="12" t="n">
-        <v>3025.769013300018</v>
-      </c>
-      <c r="K9" s="12" t="n">
-        <v>3116.542083699019</v>
+      <c r="C9" s="13" t="n">
+        <v>3331.994762669628</v>
+      </c>
+      <c r="D9" s="13" t="n">
+        <v>3431.954605549717</v>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>3534.913243716208</v>
+      </c>
+      <c r="F9" s="13" t="n">
+        <v>3640.960641027694</v>
+      </c>
+      <c r="G9" s="13" t="n">
+        <v>3750.189460258525</v>
+      </c>
+      <c r="H9" s="13" t="n">
+        <v>3862.695144066281</v>
+      </c>
+      <c r="I9" s="13" t="n">
+        <v>3978.575998388269</v>
+      </c>
+      <c r="J9" s="13" t="n">
+        <v>4097.933278339917</v>
+      </c>
+      <c r="K9" s="13" t="n">
+        <v>4220.871276690114</v>
       </c>
     </row>
     <row r="10">
@@ -3653,43 +3653,43 @@
           <t>FCF margin</t>
         </is>
       </c>
-      <c r="B13" s="13">
+      <c r="B13" s="14">
         <f>B12/B5</f>
         <v/>
       </c>
-      <c r="C13" s="13">
+      <c r="C13" s="14">
         <f>C12/C5</f>
         <v/>
       </c>
-      <c r="D13" s="13">
+      <c r="D13" s="14">
         <f>D12/D5</f>
         <v/>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="14">
         <f>E12/E5</f>
         <v/>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="14">
         <f>F12/F5</f>
         <v/>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="14">
         <f>G12/G5</f>
         <v/>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="14">
         <f>H12/H5</f>
         <v/>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="14">
         <f>I12/I5</f>
         <v/>
       </c>
-      <c r="J13" s="13">
+      <c r="J13" s="14">
         <f>J12/J5</f>
         <v/>
       </c>
-      <c r="K13" s="13">
+      <c r="K13" s="14">
         <f>K12/K5</f>
         <v/>
       </c>
@@ -3800,7 +3800,7 @@
           <t>Shares outstanding (mn)</t>
         </is>
       </c>
-      <c r="B11" s="15" t="n">
+      <c r="B11" s="12" t="n">
         <v>357.102017</v>
       </c>
     </row>
@@ -3842,7 +3842,7 @@
       <c r="A15" s="21" t="n">
         <v>2026</v>
       </c>
-      <c r="B15" s="15" t="n">
+      <c r="B15" s="12" t="n">
         <v>2694.040234602546</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -3854,7 +3854,7 @@
         <f>1/(1+$B$8)^1</f>
         <v/>
       </c>
-      <c r="E15" s="12">
+      <c r="E15" s="13">
         <f>B15*D15</f>
         <v/>
       </c>
@@ -3863,7 +3863,7 @@
       <c r="A16" s="21" t="n">
         <v>2027</v>
       </c>
-      <c r="B16" s="15" t="n">
+      <c r="B16" s="12" t="n">
         <v>2788.331642813635</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -3875,7 +3875,7 @@
         <f>1/(1+$B$8)^2</f>
         <v/>
       </c>
-      <c r="E16" s="12">
+      <c r="E16" s="13">
         <f>B16*D16</f>
         <v/>
       </c>
@@ -3884,7 +3884,7 @@
       <c r="A17" s="21" t="n">
         <v>2028</v>
       </c>
-      <c r="B17" s="15" t="n">
+      <c r="B17" s="12" t="n">
         <v>2885.923250312112</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -3896,7 +3896,7 @@
         <f>1/(1+$B$8)^3</f>
         <v/>
       </c>
-      <c r="E17" s="12">
+      <c r="E17" s="13">
         <f>B17*D17</f>
         <v/>
       </c>
@@ -3905,7 +3905,7 @@
       <c r="A18" s="21" t="n">
         <v>2029</v>
       </c>
-      <c r="B18" s="15" t="n">
+      <c r="B18" s="12" t="n">
         <v>2986.930564073036</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -3917,7 +3917,7 @@
         <f>1/(1+$B$8)^4</f>
         <v/>
       </c>
-      <c r="E18" s="12">
+      <c r="E18" s="13">
         <f>B18*D18</f>
         <v/>
       </c>
@@ -3926,7 +3926,7 @@
       <c r="A19" s="21" t="n">
         <v>2030</v>
       </c>
-      <c r="B19" s="15" t="n">
+      <c r="B19" s="12" t="n">
         <v>3091.473133815592</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -3938,7 +3938,7 @@
         <f>1/(1+$B$8)^5</f>
         <v/>
       </c>
-      <c r="E19" s="12">
+      <c r="E19" s="13">
         <f>B19*D19</f>
         <v/>
       </c>
@@ -3947,7 +3947,7 @@
       <c r="A20" s="21" t="n">
         <v>2031</v>
       </c>
-      <c r="B20" s="15" t="n">
+      <c r="B20" s="12" t="n">
         <v>3199.674693499138</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -3959,7 +3959,7 @@
         <f>1/(1+$B$8)^6</f>
         <v/>
       </c>
-      <c r="E20" s="12">
+      <c r="E20" s="13">
         <f>B20*D20</f>
         <v/>
       </c>
@@ -3968,7 +3968,7 @@
       <c r="A21" s="21" t="n">
         <v>2032</v>
       </c>
-      <c r="B21" s="15" t="n">
+      <c r="B21" s="12" t="n">
         <v>3311.663307771607</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -3980,7 +3980,7 @@
         <f>1/(1+$B$8)^7</f>
         <v/>
       </c>
-      <c r="E21" s="12">
+      <c r="E21" s="13">
         <f>B21*D21</f>
         <v/>
       </c>
@@ -3989,7 +3989,7 @@
       <c r="A22" s="21" t="n">
         <v>2033</v>
       </c>
-      <c r="B22" s="15" t="n">
+      <c r="B22" s="12" t="n">
         <v>3427.571523543613</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -4001,7 +4001,7 @@
         <f>1/(1+$B$8)^8</f>
         <v/>
       </c>
-      <c r="E22" s="12">
+      <c r="E22" s="13">
         <f>B22*D22</f>
         <v/>
       </c>
@@ -4010,7 +4010,7 @@
       <c r="A23" s="21" t="n">
         <v>2034</v>
       </c>
-      <c r="B23" s="15" t="n">
+      <c r="B23" s="12" t="n">
         <v>3547.53652686764</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -4022,7 +4022,7 @@
         <f>1/(1+$B$8)^9</f>
         <v/>
       </c>
-      <c r="E23" s="12">
+      <c r="E23" s="13">
         <f>B23*D23</f>
         <v/>
       </c>
@@ -4031,7 +4031,7 @@
       <c r="A24" s="21" t="n">
         <v>2035</v>
       </c>
-      <c r="B24" s="15" t="n">
+      <c r="B24" s="12" t="n">
         <v>3671.700305308007</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -4043,7 +4043,7 @@
         <f>1/(1+$B$8)^10</f>
         <v/>
       </c>
-      <c r="E24" s="12">
+      <c r="E24" s="13">
         <f>B24*D24</f>
         <v/>
       </c>
@@ -4072,7 +4072,7 @@
           <t>Terminal value = CFn·(1+g)/(Ke−g)</t>
         </is>
       </c>
-      <c r="B28" s="12">
+      <c r="B28" s="13">
         <f>B24*(1+$B$10)/($B$8-$B$10)</f>
         <v/>
       </c>
@@ -4083,7 +4083,7 @@
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="B29" s="12">
+      <c r="B29" s="13">
         <f>$B$28/(1+$B$8)^10</f>
         <v/>
       </c>
@@ -4126,7 +4126,7 @@
           <t>Upside / (downside)</t>
         </is>
       </c>
-      <c r="B34" s="13">
+      <c r="B34" s="14">
         <f>B32/$B$33-1</f>
         <v/>
       </c>
@@ -4195,7 +4195,7 @@
           <t>Diluted shares (mn)</t>
         </is>
       </c>
-      <c r="B6" s="15" t="n">
+      <c r="B6" s="12" t="n">
         <v>357.102017</v>
       </c>
     </row>
@@ -4205,7 +4205,7 @@
           <t>Total debt (USDmm)</t>
         </is>
       </c>
-      <c r="B7" s="15" t="n">
+      <c r="B7" s="12" t="n">
         <v>8992</v>
       </c>
     </row>
@@ -4215,7 +4215,7 @@
           <t>Cash &amp; ST investments (USDmm)</t>
         </is>
       </c>
-      <c r="B8" s="15" t="n">
+      <c r="B8" s="12" t="n">
         <v>3641</v>
       </c>
     </row>
@@ -4225,7 +4225,7 @@
           <t>Minority interest (USDmm)</t>
         </is>
       </c>
-      <c r="B9" s="15" t="n">
+      <c r="B9" s="12" t="n">
         <v>336</v>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
           <t>Net debt (USDmm)</t>
         </is>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="13">
         <f>Assumptions!$B$7-Assumptions!$B$8</f>
         <v/>
       </c>
@@ -4313,7 +4313,7 @@
           <t>Tax rate</t>
         </is>
       </c>
-      <c r="B19" s="14" t="n">
+      <c r="B19" s="15" t="n">
         <v>0.286837674171915</v>
       </c>
     </row>
@@ -4379,19 +4379,19 @@
           <t>Revenue growth</t>
         </is>
       </c>
-      <c r="B26" s="14" t="n">
+      <c r="B26" s="15" t="n">
         <v>0.01469039149633189</v>
       </c>
-      <c r="C26" s="14" t="n">
+      <c r="C26" s="15" t="n">
         <v>0.01594039149633189</v>
       </c>
-      <c r="D26" s="14" t="n">
+      <c r="D26" s="15" t="n">
         <v>0.01719039149633189</v>
       </c>
-      <c r="E26" s="14" t="n">
+      <c r="E26" s="15" t="n">
         <v>0.01844039149633189</v>
       </c>
-      <c r="F26" s="14" t="n">
+      <c r="F26" s="15" t="n">
         <v>0.01969039149633189</v>
       </c>
     </row>
@@ -4401,19 +4401,19 @@
           <t>EBIT margin</t>
         </is>
       </c>
-      <c r="B27" s="14" t="n">
+      <c r="B27" s="15" t="n">
         <v>0.1644146790428073</v>
       </c>
-      <c r="C27" s="14" t="n">
+      <c r="C27" s="15" t="n">
         <v>0.1592026475312204</v>
       </c>
-      <c r="D27" s="14" t="n">
+      <c r="D27" s="15" t="n">
         <v>0.1539906160196335</v>
       </c>
-      <c r="E27" s="14" t="n">
+      <c r="E27" s="15" t="n">
         <v>0.1487785845080466</v>
       </c>
-      <c r="F27" s="14" t="n">
+      <c r="F27" s="15" t="n">
         <v>0.1435665529964597</v>
       </c>
     </row>
@@ -4423,19 +4423,19 @@
           <t>D&amp;A % of revenue</t>
         </is>
       </c>
-      <c r="B28" s="14" t="n">
+      <c r="B28" s="15" t="n">
         <v>0.07806074434667941</v>
       </c>
-      <c r="C28" s="14" t="n">
+      <c r="C28" s="15" t="n">
         <v>0.07806074434667941</v>
       </c>
-      <c r="D28" s="14" t="n">
+      <c r="D28" s="15" t="n">
         <v>0.07806074434667941</v>
       </c>
-      <c r="E28" s="14" t="n">
+      <c r="E28" s="15" t="n">
         <v>0.07806074434667941</v>
       </c>
-      <c r="F28" s="14" t="n">
+      <c r="F28" s="15" t="n">
         <v>0.07806074434667941</v>
       </c>
     </row>
@@ -4445,19 +4445,19 @@
           <t>Capex % of revenue</t>
         </is>
       </c>
-      <c r="B29" s="14" t="n">
+      <c r="B29" s="15" t="n">
         <v>0.09765960882899036</v>
       </c>
-      <c r="C29" s="14" t="n">
+      <c r="C29" s="15" t="n">
         <v>0.09765960882899036</v>
       </c>
-      <c r="D29" s="14" t="n">
+      <c r="D29" s="15" t="n">
         <v>0.09765960882899036</v>
       </c>
-      <c r="E29" s="14" t="n">
+      <c r="E29" s="15" t="n">
         <v>0.09765960882899036</v>
       </c>
-      <c r="F29" s="14" t="n">
+      <c r="F29" s="15" t="n">
         <v>0.09765960882899036</v>
       </c>
     </row>
@@ -4467,7 +4467,7 @@
           <t>ΔNWC % of Δrevenue</t>
         </is>
       </c>
-      <c r="B30" s="14" t="n">
+      <c r="B30" s="15" t="n">
         <v>0.00356234096692112</v>
       </c>
     </row>
@@ -4553,7 +4553,7 @@
           <t>Weight of equity</t>
         </is>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="14">
         <f>WACC!$B$6/(WACC!$B$6+WACC!$B$7)</f>
         <v/>
       </c>
@@ -4564,7 +4564,7 @@
           <t>Weight of debt</t>
         </is>
       </c>
-      <c r="B9" s="13">
+      <c r="B9" s="14">
         <f>1-WACC!$B$8</f>
         <v/>
       </c>
@@ -4690,23 +4690,23 @@
       <c r="E5" s="29" t="n">
         <v>25533</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="13">
         <f>E5*(1+Assumptions!B$26)</f>
         <v/>
       </c>
-      <c r="G5" s="12">
+      <c r="G5" s="13">
         <f>F5*(1+Assumptions!C$26)</f>
         <v/>
       </c>
-      <c r="H5" s="12">
+      <c r="H5" s="13">
         <f>G5*(1+Assumptions!D$26)</f>
         <v/>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="13">
         <f>H5*(1+Assumptions!E$26)</f>
         <v/>
       </c>
-      <c r="J5" s="12">
+      <c r="J5" s="13">
         <f>I5*(1+Assumptions!F$26)</f>
         <v/>
       </c>
@@ -4729,23 +4729,23 @@
         <f>E5/D5-1</f>
         <v/>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="14">
         <f>F5/E5-1</f>
         <v/>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="14">
         <f>G5/F5-1</f>
         <v/>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="14">
         <f>H5/G5-1</f>
         <v/>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="14">
         <f>I5/H5-1</f>
         <v/>
       </c>
-      <c r="J6" s="13">
+      <c r="J6" s="14">
         <f>J5/I5-1</f>
         <v/>
       </c>
@@ -4768,23 +4768,23 @@
       <c r="E7" s="29" t="n">
         <v>4198</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="13">
         <f>F5*Assumptions!B$27</f>
         <v/>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="13">
         <f>G5*Assumptions!C$27</f>
         <v/>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="13">
         <f>H5*Assumptions!D$27</f>
         <v/>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="13">
         <f>I5*Assumptions!E$27</f>
         <v/>
       </c>
-      <c r="J7" s="12">
+      <c r="J7" s="13">
         <f>J5*Assumptions!F$27</f>
         <v/>
       </c>
@@ -4811,23 +4811,23 @@
         <f>E7/E5</f>
         <v/>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="14">
         <f>F7/F5</f>
         <v/>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="14">
         <f>G7/G5</f>
         <v/>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="14">
         <f>H7/H5</f>
         <v/>
       </c>
-      <c r="I8" s="13">
+      <c r="I8" s="14">
         <f>I7/I5</f>
         <v/>
       </c>
-      <c r="J8" s="13">
+      <c r="J8" s="14">
         <f>J7/J5</f>
         <v/>
       </c>
@@ -4850,23 +4850,23 @@
       <c r="E9" s="29" t="n">
         <v>1937</v>
       </c>
-      <c r="F9" s="12">
+      <c r="F9" s="13">
         <f>F5*Assumptions!B$28</f>
         <v/>
       </c>
-      <c r="G9" s="12">
+      <c r="G9" s="13">
         <f>G5*Assumptions!C$28</f>
         <v/>
       </c>
-      <c r="H9" s="12">
+      <c r="H9" s="13">
         <f>H5*Assumptions!D$28</f>
         <v/>
       </c>
-      <c r="I9" s="12">
+      <c r="I9" s="13">
         <f>I5*Assumptions!E$28</f>
         <v/>
       </c>
-      <c r="J9" s="12">
+      <c r="J9" s="13">
         <f>J5*Assumptions!F$28</f>
         <v/>
       </c>
@@ -4893,23 +4893,23 @@
         <f>E7+E9</f>
         <v/>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="13">
         <f>F7+F9</f>
         <v/>
       </c>
-      <c r="G10" s="12">
+      <c r="G10" s="13">
         <f>G7+G9</f>
         <v/>
       </c>
-      <c r="H10" s="12">
+      <c r="H10" s="13">
         <f>H7+H9</f>
         <v/>
       </c>
-      <c r="I10" s="12">
+      <c r="I10" s="13">
         <f>I7+I9</f>
         <v/>
       </c>
-      <c r="J10" s="12">
+      <c r="J10" s="13">
         <f>J7+J9</f>
         <v/>
       </c>
@@ -4975,23 +4975,23 @@
       <c r="E12" s="29" t="n">
         <v>2949</v>
       </c>
-      <c r="F12" s="12">
+      <c r="F12" s="13">
         <f>F5*Assumptions!B$29</f>
         <v/>
       </c>
-      <c r="G12" s="12">
+      <c r="G12" s="13">
         <f>G5*Assumptions!C$29</f>
         <v/>
       </c>
-      <c r="H12" s="12">
+      <c r="H12" s="13">
         <f>H5*Assumptions!D$29</f>
         <v/>
       </c>
-      <c r="I12" s="12">
+      <c r="I12" s="13">
         <f>I5*Assumptions!E$29</f>
         <v/>
       </c>
-      <c r="J12" s="12">
+      <c r="J12" s="13">
         <f>J5*Assumptions!F$29</f>
         <v/>
       </c>
@@ -5014,23 +5014,23 @@
       <c r="E13" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="13">
         <f>(F5-E5)*Assumptions!$B$30</f>
         <v/>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="13">
         <f>(G5-F5)*Assumptions!$B$30</f>
         <v/>
       </c>
-      <c r="H13" s="12">
+      <c r="H13" s="13">
         <f>(H5-G5)*Assumptions!$B$30</f>
         <v/>
       </c>
-      <c r="I13" s="12">
+      <c r="I13" s="13">
         <f>(I5-H5)*Assumptions!$B$30</f>
         <v/>
       </c>
-      <c r="J13" s="12">
+      <c r="J13" s="13">
         <f>(J5-I5)*Assumptions!$B$30</f>
         <v/>
       </c>
@@ -5229,23 +5229,23 @@
           <t>PV of FCFF</t>
         </is>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="13">
         <f>B5*B7</f>
         <v/>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="13">
         <f>C5*C7</f>
         <v/>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="13">
         <f>D5*D7</f>
         <v/>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="13">
         <f>E5*E7</f>
         <v/>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="13">
         <f>F5*F7</f>
         <v/>
       </c>
@@ -5256,7 +5256,7 @@
           <t>PV of explicit FCFF</t>
         </is>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="13">
         <f>SUM(B8:F8)</f>
         <v/>
       </c>
@@ -5278,7 +5278,7 @@
           <t>Invested capital (mm)</t>
         </is>
       </c>
-      <c r="B12" s="15" t="n">
+      <c r="B12" s="12" t="n">
         <v>19868</v>
       </c>
     </row>
@@ -5299,7 +5299,7 @@
           <t>Terminal ROIC</t>
         </is>
       </c>
-      <c r="B14" s="13">
+      <c r="B14" s="14">
         <f>MAX($B$11/$B$13,WACC!$B$10)</f>
         <v/>
       </c>
@@ -5321,7 +5321,7 @@
           <t>Terminal value (Gordon)</t>
         </is>
       </c>
-      <c r="B16" s="12">
+      <c r="B16" s="13">
         <f>$B$11*(1+Assumptions!$B$22)*(1-$B$15)/(WACC!$B$10-Assumptions!$B$22)</f>
         <v/>
       </c>
@@ -5332,7 +5332,7 @@
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="B17" s="12">
+      <c r="B17" s="13">
         <f>$B$16/(1+WACC!$B$10)^(5-0.5)</f>
         <v/>
       </c>
@@ -5343,7 +5343,7 @@
           <t>TV as % of EV</t>
         </is>
       </c>
-      <c r="B18" s="13">
+      <c r="B18" s="14">
         <f>$B$17/($B$10+$B$17)</f>
         <v/>
       </c>
@@ -5456,19 +5456,19 @@
           <t>WACC \ g</t>
         </is>
       </c>
-      <c r="B4" s="14" t="n">
+      <c r="B4" s="15" t="n">
         <v>0.015</v>
       </c>
-      <c r="C4" s="14" t="n">
+      <c r="C4" s="15" t="n">
         <v>0.02</v>
       </c>
-      <c r="D4" s="14" t="n">
+      <c r="D4" s="15" t="n">
         <v>0.025</v>
       </c>
-      <c r="E4" s="14" t="n">
+      <c r="E4" s="15" t="n">
         <v>0.03</v>
       </c>
-      <c r="F4" s="14" t="n">
+      <c r="F4" s="15" t="n">
         <v>0.035</v>
       </c>
     </row>
